--- a/data/CUBICACION.xlsx
+++ b/data/CUBICACION.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LA CHACRA - copia\LA-CHACRA\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{866C8D3D-4198-4C40-A3D0-776EDB810EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7E8F0B-21A4-475C-A644-2CC45BFA1CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{1B80EFAC-68E4-47D9-BD21-B7D2BF09616E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="292">
   <si>
     <t>Tipo Partida</t>
   </si>
@@ -801,6 +802,120 @@
   </si>
   <si>
     <t>CANTIDAD PROMEDIO POR MODULO</t>
+  </si>
+  <si>
+    <t>PARTIDA</t>
+  </si>
+  <si>
+    <t>DESCRIPCION</t>
+  </si>
+  <si>
+    <t>UNIDAD</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t>UND</t>
+  </si>
+  <si>
+    <t>PZA</t>
+  </si>
+  <si>
+    <t>PINO NACIONAL GRADO C-16/C-24 IMPREGNADO DE 2" X 6" X 4,00 m (VIVIENDAS SOCIALES)</t>
+  </si>
+  <si>
+    <t>PINO NACIONAL ESTRUCTURAL CEPILLADO 4/CARAS  IMPREGNADO DE  2 X 8 X 4.00 (41 x 185 MM ) (VVSS)</t>
+  </si>
+  <si>
+    <t>PINO NACIONAL GRADO C-16/C-24 IMPREGNADO DE 2" x 4" x 2,44 m (41x90mm) (VIVIENDAS SOCIALES)</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>CONECTOR DENTADO 2X4 (4C2)</t>
+  </si>
+  <si>
+    <t>CJA</t>
+  </si>
+  <si>
+    <t>CLAVO HELICOIDAL EN ROLLO  2.5 x 50 MM ( CAJA DE 9.000 UNIDADES )</t>
+  </si>
+  <si>
+    <t>TIN</t>
+  </si>
+  <si>
+    <t>PINTURA EPOXICA POLIPOX 675 GRIS COD:6757040T33</t>
+  </si>
+  <si>
+    <t>GAL</t>
+  </si>
+  <si>
+    <t>LTS</t>
+  </si>
+  <si>
+    <t>RLL</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>FORRO FRENTE BALCON DS49 80/100  D: 220 MM L: 4000 MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORRO LATERAL BALCON DS49 100/100 D: 220 MM L: 3000 MM </t>
+  </si>
+  <si>
+    <t>KIT CERRADURA ACCESO ML/816 SS 1 MANILLA (SKU:023037)</t>
+  </si>
+  <si>
+    <t>KIT</t>
+  </si>
+  <si>
+    <t>KIT CERRADURA ACCESO ML/816 SS 2 MANILLAS (SKU: 023037A)</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>LLAVE DE PASO CAMPANA 1/2 LC17 6001 FAS</t>
+  </si>
+  <si>
+    <t>MANGUITO WC DISCAPACITADO RECTO 110MM</t>
+  </si>
+  <si>
+    <t>SIFON LAVAMANOS PP 1 1/4'' CON SALIDA RECTA (19ST3082500)</t>
+  </si>
+  <si>
+    <t>MANGUITO RECTO 110MM MOD. TUBE WASSER</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>JGO</t>
+  </si>
+  <si>
+    <t>MTS</t>
+  </si>
+  <si>
+    <t>080460X</t>
+  </si>
+  <si>
+    <t>MONOFILAMENTO POLYFLOR GRIS COD:3700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PINTURA </t>
+  </si>
+  <si>
+    <t>UNIDAD DE MEDIDA</t>
   </si>
 </sst>
 </file>
@@ -853,6 +968,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3A700C6-F0CA-453A-A934-AFDA491A5CB1}" name="Tabla1" displayName="Tabla1" ref="A1:D186" totalsRowShown="0">
+  <autoFilter ref="A1:D186" xr:uid="{D3A700C6-F0CA-453A-A934-AFDA491A5CB1}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6134504D-9BD9-4C70-9A21-B337EE2112D7}" name="PARTIDA"/>
+    <tableColumn id="2" xr3:uid="{D28348E6-170F-4D48-9AC0-3764BF4B6EB5}" name="DESCRIPCION"/>
+    <tableColumn id="3" xr3:uid="{1D0FE055-EB2D-4BC0-8BD9-79C05C9FF1D9}" name="UNIDAD"/>
+    <tableColumn id="4" xr3:uid="{D42DF3AE-8420-4822-99D0-442B0F49F38D}" name="WIP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1172,15 +1300,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B53EF89-EEEC-44DD-90B6-FEA3815616C5}">
-  <dimension ref="A1:G245"/>
+  <dimension ref="A1:H245"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="108" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1197,13 +1326,16 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1" t="s">
         <v>252</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1219,42 +1351,54 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <f>+_xlfn.XLOOKUP(D2,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G2">
         <v>80</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D3">
         <v>412280</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
+        <f>+_xlfn.XLOOKUP(D3,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G3">
         <v>136</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>4.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>412281</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
+        <f>+_xlfn.XLOOKUP(D4,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G4">
         <v>28</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.875</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>11</v>
       </c>
@@ -1264,154 +1408,198 @@
       <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
+        <f>+_xlfn.XLOOKUP(D5,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G5">
         <v>96</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>302046</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="str">
+        <f>+_xlfn.XLOOKUP(D6,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G6">
         <v>560</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>17.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>407423</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="str">
+        <f>+_xlfn.XLOOKUP(D7,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G7">
         <v>2864</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>89.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D8">
         <v>408014</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="str">
+        <f>+_xlfn.XLOOKUP(D8,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G8">
         <v>0.58239999999999992</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1.8199999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D9">
         <v>410046</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="str">
+        <f>+_xlfn.XLOOKUP(D9,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G9">
         <v>128</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D10">
         <v>412313</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="str">
+        <f>+_xlfn.XLOOKUP(D10,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G10">
         <v>0.76800000000000013</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>2.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D11">
         <v>701043</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="str">
+        <f>+_xlfn.XLOOKUP(D11,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G11">
         <v>108</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>3.375</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>1405006</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="str">
+        <f>+_xlfn.XLOOKUP(D12,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G12">
         <v>464</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>14.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D13">
         <v>1902013</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="str">
+        <f>+_xlfn.XLOOKUP(D13,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G13">
         <v>10.080000000000002</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.31500000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="str">
+        <f>+_xlfn.XLOOKUP(D14,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G14">
         <v>0.43200000000000016</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1.3500000000000005E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="str">
+        <f>+_xlfn.XLOOKUP(D15,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G15">
         <v>2.8560000000000012</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>8.9250000000000038E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>25</v>
       </c>
@@ -1424,42 +1612,54 @@
       <c r="E16" t="s">
         <v>26</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="str">
+        <f>+_xlfn.XLOOKUP(D16,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G16">
         <v>1000</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>31.25</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D17">
         <v>407011</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="str">
+        <f>+_xlfn.XLOOKUP(D17,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G17">
         <v>9280</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>290</v>
       </c>
     </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D18">
         <v>407307</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="str">
+        <f>+_xlfn.XLOOKUP(D18,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G18">
         <v>1000</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>31.25</v>
       </c>
     </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>29</v>
       </c>
@@ -1469,224 +1669,288 @@
       <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="str">
+        <f>+_xlfn.XLOOKUP(D19,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G19">
         <v>120</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>3.75</v>
       </c>
     </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D20">
         <v>302028</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="str">
+        <f>+_xlfn.XLOOKUP(D20,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G20">
         <v>674</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>21.0625</v>
       </c>
     </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D21">
         <v>304049</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="str">
+        <f>+_xlfn.XLOOKUP(D21,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G21">
         <v>8</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.25</v>
       </c>
     </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D22">
         <v>304101</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="str">
+        <f>+_xlfn.XLOOKUP(D22,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G22">
         <v>58</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>1.8125</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D23">
         <v>407423</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="str">
+        <f>+_xlfn.XLOOKUP(D23,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G23">
         <v>4016</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>125.5</v>
       </c>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D24">
         <v>408014</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="str">
+        <f>+_xlfn.XLOOKUP(D24,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G24">
         <v>0.26880000000000004</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>8.4000000000000012E-3</v>
       </c>
     </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D25">
         <v>408042</v>
       </c>
       <c r="E25" t="s">
         <v>33</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="str">
+        <f>+_xlfn.XLOOKUP(D25,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G25">
         <v>5.28</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D26">
         <v>410045</v>
       </c>
       <c r="E26" t="s">
         <v>34</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="str">
+        <f>+_xlfn.XLOOKUP(D26,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G26">
         <v>128</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D27">
         <v>412313</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="str">
+        <f>+_xlfn.XLOOKUP(D27,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G27">
         <v>6.4000000000000012</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D28">
         <v>701040</v>
       </c>
       <c r="E28" t="s">
         <v>35</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="str">
+        <f>+_xlfn.XLOOKUP(D28,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G28">
         <v>16</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D29">
         <v>701096</v>
       </c>
       <c r="E29" t="s">
         <v>36</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="str">
+        <f>+_xlfn.XLOOKUP(D29,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G29">
         <v>92</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>2.875</v>
       </c>
     </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D30">
         <v>707023</v>
       </c>
       <c r="E30" t="s">
         <v>37</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="str">
+        <f>+_xlfn.XLOOKUP(D30,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G30">
         <v>16</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D31">
         <v>1902013</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="str">
+        <f>+_xlfn.XLOOKUP(D31,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G31">
         <v>7.200000000000002</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.22500000000000006</v>
       </c>
     </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D32">
         <v>5309018</v>
       </c>
       <c r="E32" t="s">
         <v>38</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="str">
+        <f>+_xlfn.XLOOKUP(D32,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>MTS</v>
+      </c>
+      <c r="G32">
         <v>144</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>4.5</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>21</v>
       </c>
       <c r="E33" t="s">
         <v>22</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="str">
+        <f>+_xlfn.XLOOKUP(D33,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G33">
         <v>0.17919999999999994</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>5.5999999999999982E-3</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>23</v>
       </c>
       <c r="E34" t="s">
         <v>24</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="str">
+        <f>+_xlfn.XLOOKUP(D34,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G34">
         <v>10.608000000000002</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>0.33150000000000007</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>39</v>
       </c>
@@ -1696,224 +1960,288 @@
       <c r="E35" t="s">
         <v>12</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="str">
+        <f>+_xlfn.XLOOKUP(D35,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G35">
         <v>108</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>3.375</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D36">
         <v>302028</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="str">
+        <f>+_xlfn.XLOOKUP(D36,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G36">
         <v>672</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D37">
         <v>304101</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="str">
+        <f>+_xlfn.XLOOKUP(D37,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G37">
         <v>58</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>1.8125</v>
       </c>
     </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D38">
         <v>407170</v>
       </c>
       <c r="E38" t="s">
         <v>40</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="str">
+        <f>+_xlfn.XLOOKUP(D38,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G38">
         <v>1152</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D39">
         <v>407423</v>
       </c>
       <c r="E39" t="s">
         <v>14</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="str">
+        <f>+_xlfn.XLOOKUP(D39,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G39">
         <v>2864</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>89.5</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D40">
         <v>408014</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="str">
+        <f>+_xlfn.XLOOKUP(D40,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G40">
         <v>0.24960000000000002</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>7.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D41">
         <v>408042</v>
       </c>
       <c r="E41" t="s">
         <v>33</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="str">
+        <f>+_xlfn.XLOOKUP(D41,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G41">
         <v>5.28</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D42">
         <v>410045</v>
       </c>
       <c r="E42" t="s">
         <v>34</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="str">
+        <f>+_xlfn.XLOOKUP(D42,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G42">
         <v>128</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D43">
         <v>412313</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="str">
+        <f>+_xlfn.XLOOKUP(D43,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G43">
         <v>3.2000000000000006</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>0.10000000000000002</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D44">
         <v>701040</v>
       </c>
       <c r="E44" t="s">
         <v>35</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="str">
+        <f>+_xlfn.XLOOKUP(D44,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G44">
         <v>8</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>0.25</v>
       </c>
     </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D45">
         <v>701096</v>
       </c>
       <c r="E45" t="s">
         <v>36</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="str">
+        <f>+_xlfn.XLOOKUP(D45,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G45">
         <v>104</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>3.25</v>
       </c>
     </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D46">
         <v>707023</v>
       </c>
       <c r="E46" t="s">
         <v>37</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="str">
+        <f>+_xlfn.XLOOKUP(D46,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G46">
         <v>16</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D47">
         <v>1902013</v>
       </c>
       <c r="E47" t="s">
         <v>20</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="str">
+        <f>+_xlfn.XLOOKUP(D47,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G47">
         <v>7.200000000000002</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>0.22500000000000006</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D48">
         <v>5309018</v>
       </c>
       <c r="E48" t="s">
         <v>38</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="str">
+        <f>+_xlfn.XLOOKUP(D48,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>MTS</v>
+      </c>
+      <c r="G48">
         <v>144</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>4.5</v>
       </c>
     </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D49" t="s">
         <v>21</v>
       </c>
       <c r="E49" t="s">
         <v>22</v>
       </c>
-      <c r="F49">
+      <c r="F49" t="str">
+        <f>+_xlfn.XLOOKUP(D49,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G49">
         <v>0.17919999999999994</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>5.5999999999999982E-3</v>
       </c>
     </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
         <v>23</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
       </c>
-      <c r="F50">
+      <c r="F50" t="str">
+        <f>+_xlfn.XLOOKUP(D50,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G50">
         <v>10.608000000000002</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>0.33150000000000007</v>
       </c>
     </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>41</v>
       </c>
@@ -1923,210 +2251,270 @@
       <c r="E51" t="s">
         <v>12</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="str">
+        <f>+_xlfn.XLOOKUP(D51,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G51">
         <v>128</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D52">
         <v>302028</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="str">
+        <f>+_xlfn.XLOOKUP(D52,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G52">
         <v>518</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>16.1875</v>
       </c>
     </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D53">
         <v>304007</v>
       </c>
       <c r="E53" t="s">
         <v>42</v>
       </c>
-      <c r="F53">
+      <c r="F53" t="str">
+        <f>+_xlfn.XLOOKUP(D53,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G53">
         <v>84</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>2.625</v>
       </c>
     </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D54">
         <v>407170</v>
       </c>
       <c r="E54" t="s">
         <v>40</v>
       </c>
-      <c r="F54">
+      <c r="F54" t="str">
+        <f>+_xlfn.XLOOKUP(D54,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G54">
         <v>1152</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D55">
         <v>407423</v>
       </c>
       <c r="E55" t="s">
         <v>14</v>
       </c>
-      <c r="F55">
+      <c r="F55" t="str">
+        <f>+_xlfn.XLOOKUP(D55,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G55">
         <v>2272</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D56">
         <v>408014</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
       </c>
-      <c r="F56">
+      <c r="F56" t="str">
+        <f>+_xlfn.XLOOKUP(D56,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G56">
         <v>0.2112</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>6.6E-3</v>
       </c>
     </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D57">
         <v>408042</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
       </c>
-      <c r="F57">
+      <c r="F57" t="str">
+        <f>+_xlfn.XLOOKUP(D57,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G57">
         <v>3.2000000000000006</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>0.10000000000000002</v>
       </c>
     </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D58">
         <v>412313</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="str">
+        <f>+_xlfn.XLOOKUP(D58,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G58">
         <v>0.624</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>1.95E-2</v>
       </c>
     </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D59">
         <v>701040</v>
       </c>
       <c r="E59" t="s">
         <v>35</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="str">
+        <f>+_xlfn.XLOOKUP(D59,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G59">
         <v>20</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>0.625</v>
       </c>
     </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D60">
         <v>701096</v>
       </c>
       <c r="E60" t="s">
         <v>36</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="str">
+        <f>+_xlfn.XLOOKUP(D60,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G60">
         <v>68</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>2.125</v>
       </c>
     </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D61">
         <v>707023</v>
       </c>
       <c r="E61" t="s">
         <v>37</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="str">
+        <f>+_xlfn.XLOOKUP(D61,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G61">
         <v>16</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D62">
         <v>1902013</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="str">
+        <f>+_xlfn.XLOOKUP(D62,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G62">
         <v>5.12</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>0.16</v>
       </c>
     </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D63">
         <v>5309018</v>
       </c>
       <c r="E63" t="s">
         <v>38</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="str">
+        <f>+_xlfn.XLOOKUP(D63,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>MTS</v>
+      </c>
+      <c r="G63">
         <v>144</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>4.5</v>
       </c>
     </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D64" t="s">
         <v>21</v>
       </c>
       <c r="E64" t="s">
         <v>22</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="str">
+        <f>+_xlfn.XLOOKUP(D64,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G64">
         <v>0.14080000000000001</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>4.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D65" t="s">
         <v>23</v>
       </c>
       <c r="E65" t="s">
         <v>24</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="str">
+        <f>+_xlfn.XLOOKUP(D65,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G65">
         <v>10.608000000000002</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>0.33150000000000007</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>43</v>
       </c>
@@ -2136,84 +2524,108 @@
       <c r="E66" t="s">
         <v>12</v>
       </c>
-      <c r="F66">
+      <c r="F66" t="str">
+        <f>+_xlfn.XLOOKUP(D66,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G66">
         <v>8</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>0.25</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D67">
         <v>302028</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="str">
+        <f>+_xlfn.XLOOKUP(D67,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G67">
         <v>704</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D68">
         <v>302248</v>
       </c>
       <c r="E68" t="s">
         <v>44</v>
       </c>
-      <c r="F68">
+      <c r="F68" t="str">
+        <f>+_xlfn.XLOOKUP(D68,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G68">
         <v>136</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>4.25</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D69">
         <v>408014</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="str">
+        <f>+_xlfn.XLOOKUP(D69,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G69">
         <v>0.34560000000000007</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>1.0800000000000002E-2</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D70">
         <v>408034</v>
       </c>
       <c r="E70" t="s">
         <v>45</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="str">
+        <f>+_xlfn.XLOOKUP(D70,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G70">
         <v>4.3584000000000014</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>0.13620000000000004</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D71">
         <v>701015</v>
       </c>
       <c r="E71" t="s">
         <v>46</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="str">
+        <f>+_xlfn.XLOOKUP(D71,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G71">
         <v>72</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>2.25</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>47</v>
       </c>
@@ -2226,154 +2638,198 @@
       <c r="E72" t="s">
         <v>49</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="str">
+        <f>+_xlfn.XLOOKUP(D72,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G72">
         <v>8</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>0.25</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D73">
         <v>617057</v>
       </c>
       <c r="E73" t="s">
         <v>50</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="str">
+        <f>+_xlfn.XLOOKUP(D73,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G73">
         <v>8</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>0.25</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D74">
         <v>810007</v>
       </c>
       <c r="E74" t="s">
         <v>51</v>
       </c>
-      <c r="F74">
+      <c r="F74" t="str">
+        <f>+_xlfn.XLOOKUP(D74,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TRA</v>
+      </c>
+      <c r="G74">
         <v>16</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>0.5</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D75">
         <v>2302024</v>
       </c>
       <c r="E75" t="s">
         <v>52</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="str">
+        <f>+_xlfn.XLOOKUP(D75,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>GAL</v>
+      </c>
+      <c r="G75">
         <v>12</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>0.375</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D76">
         <v>2302044</v>
       </c>
       <c r="E76" t="s">
         <v>53</v>
       </c>
-      <c r="F76">
+      <c r="F76" t="str">
+        <f>+_xlfn.XLOOKUP(D76,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>SAC</v>
+      </c>
+      <c r="G76">
         <v>1.0204081632653061</v>
       </c>
-      <c r="G76">
+      <c r="H76">
         <v>3.1887755102040817E-2</v>
       </c>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D77">
         <v>2302045</v>
       </c>
       <c r="E77" t="s">
         <v>54</v>
       </c>
-      <c r="F77">
+      <c r="F77" t="str">
+        <f>+_xlfn.XLOOKUP(D77,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G77">
         <v>1.0204081632653061</v>
       </c>
-      <c r="G77">
+      <c r="H77">
         <v>3.1887755102040817E-2</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D78">
         <v>2302118</v>
       </c>
       <c r="E78" t="s">
         <v>55</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="str">
+        <f>+_xlfn.XLOOKUP(D78,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G78">
         <v>4.75</v>
       </c>
-      <c r="G78">
+      <c r="H78">
         <v>0.1484375</v>
       </c>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D79">
         <v>2304056</v>
       </c>
       <c r="E79" t="s">
         <v>56</v>
       </c>
-      <c r="F79">
+      <c r="F79" t="str">
+        <f>+_xlfn.XLOOKUP(D79,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G79">
         <v>12</v>
       </c>
-      <c r="G79">
+      <c r="H79">
         <v>0.375</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D80" t="s">
         <v>57</v>
       </c>
       <c r="E80" t="s">
         <v>58</v>
       </c>
-      <c r="F80">
+      <c r="F80" t="str">
+        <f>+_xlfn.XLOOKUP(D80,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G80">
         <v>116</v>
       </c>
-      <c r="G80">
+      <c r="H80">
         <v>3.625</v>
       </c>
     </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D81" t="s">
         <v>59</v>
       </c>
       <c r="E81" t="s">
         <v>60</v>
       </c>
-      <c r="F81">
+      <c r="F81" t="str">
+        <f>+_xlfn.XLOOKUP(D81,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>ML</v>
+      </c>
+      <c r="G81">
         <v>9.9039999999999981</v>
       </c>
-      <c r="G81">
+      <c r="H81">
         <v>0.30949999999999994</v>
       </c>
     </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
         <v>61</v>
       </c>
       <c r="E82" t="s">
         <v>62</v>
       </c>
-      <c r="F82">
+      <c r="F82" t="str">
+        <f>+_xlfn.XLOOKUP(D82,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G82">
         <v>0.13600000000000001</v>
       </c>
-      <c r="G82">
+      <c r="H82">
         <v>4.2500000000000003E-3</v>
       </c>
     </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>63</v>
       </c>
@@ -2383,322 +2839,414 @@
       <c r="E83" t="s">
         <v>12</v>
       </c>
-      <c r="F83">
+      <c r="F83" t="str">
+        <f>+_xlfn.XLOOKUP(D83,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G83">
         <v>72</v>
       </c>
-      <c r="G83">
+      <c r="H83">
         <v>2.25</v>
       </c>
     </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D84">
         <v>302028</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
       </c>
-      <c r="F84">
+      <c r="F84" t="str">
+        <f>+_xlfn.XLOOKUP(D84,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G84">
         <v>64</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D85">
         <v>302048</v>
       </c>
       <c r="E85" t="s">
         <v>64</v>
       </c>
-      <c r="F85">
+      <c r="F85" t="str">
+        <f>+_xlfn.XLOOKUP(D85,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G85">
         <v>536</v>
       </c>
-      <c r="G85">
+      <c r="H85">
         <v>16.75</v>
       </c>
     </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D86">
         <v>302249</v>
       </c>
       <c r="E86" t="s">
         <v>65</v>
       </c>
-      <c r="F86">
+      <c r="F86" t="str">
+        <f>+_xlfn.XLOOKUP(D86,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G86">
         <v>96</v>
       </c>
-      <c r="G86">
+      <c r="H86">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D87">
         <v>304049</v>
       </c>
       <c r="E87" t="s">
         <v>31</v>
       </c>
-      <c r="F87">
+      <c r="F87" t="str">
+        <f>+_xlfn.XLOOKUP(D87,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G87">
         <v>352</v>
       </c>
-      <c r="G87">
+      <c r="H87">
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D88">
         <v>304101</v>
       </c>
       <c r="E88" t="s">
         <v>32</v>
       </c>
-      <c r="F88">
+      <c r="F88" t="str">
+        <f>+_xlfn.XLOOKUP(D88,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G88">
         <v>168</v>
       </c>
-      <c r="G88">
+      <c r="H88">
         <v>5.25</v>
       </c>
     </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D89">
         <v>408017</v>
       </c>
       <c r="E89" t="s">
         <v>66</v>
       </c>
-      <c r="F89">
+      <c r="F89" t="str">
+        <f>+_xlfn.XLOOKUP(D89,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G89">
         <v>0.80000000000000016</v>
       </c>
-      <c r="G89">
+      <c r="H89">
         <v>2.5000000000000005E-2</v>
       </c>
     </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D90">
         <v>408042</v>
       </c>
       <c r="E90" t="s">
         <v>33</v>
       </c>
-      <c r="F90">
+      <c r="F90" t="str">
+        <f>+_xlfn.XLOOKUP(D90,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G90">
         <v>4.2</v>
       </c>
-      <c r="G90">
+      <c r="H90">
         <v>0.13125000000000001</v>
       </c>
     </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D91">
         <v>408088</v>
       </c>
       <c r="E91" t="s">
         <v>67</v>
       </c>
-      <c r="F91">
+      <c r="F91" t="str">
+        <f>+_xlfn.XLOOKUP(D91,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G91">
         <v>1.9200000000000008</v>
       </c>
-      <c r="G91">
+      <c r="H91">
         <v>6.0000000000000026E-2</v>
       </c>
     </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D92">
         <v>410126</v>
       </c>
       <c r="E92" t="s">
         <v>68</v>
       </c>
-      <c r="F92">
+      <c r="F92" t="str">
+        <f>+_xlfn.XLOOKUP(D92,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G92">
         <v>160</v>
       </c>
-      <c r="G92">
+      <c r="H92">
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D93">
         <v>412313</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
       </c>
-      <c r="F93">
+      <c r="F93" t="str">
+        <f>+_xlfn.XLOOKUP(D93,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G93">
         <v>2.1920000000000002</v>
       </c>
-      <c r="G93">
+      <c r="H93">
         <v>6.8500000000000005E-2</v>
       </c>
     </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D94">
         <v>1901008</v>
       </c>
       <c r="E94" t="s">
         <v>69</v>
       </c>
-      <c r="F94">
+      <c r="F94" t="str">
+        <f>+_xlfn.XLOOKUP(D94,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G94">
         <v>240.68</v>
       </c>
-      <c r="G94">
+      <c r="H94">
         <v>7.5212500000000002</v>
       </c>
     </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D95">
         <v>1901086</v>
       </c>
       <c r="E95" t="s">
         <v>70</v>
       </c>
-      <c r="F95">
+      <c r="F95" t="str">
+        <f>+_xlfn.XLOOKUP(D95,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G95">
         <v>361.02000000000004</v>
       </c>
-      <c r="G95">
+      <c r="H95">
         <v>11.281875000000001</v>
       </c>
     </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:8" x14ac:dyDescent="0.25">
       <c r="D96">
         <v>1901505</v>
       </c>
       <c r="E96" t="s">
         <v>71</v>
       </c>
-      <c r="F96">
+      <c r="F96" t="str">
+        <f>+_xlfn.XLOOKUP(D96,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KG</v>
+      </c>
+      <c r="G96">
         <v>18.8</v>
       </c>
-      <c r="G96">
+      <c r="H96">
         <v>0.58750000000000002</v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D97">
         <v>1902003</v>
       </c>
       <c r="E97" t="s">
         <v>72</v>
       </c>
-      <c r="F97">
+      <c r="F97" t="str">
+        <f>+_xlfn.XLOOKUP(D97,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G97">
         <v>0.87871999999999995</v>
       </c>
-      <c r="G97">
+      <c r="H97">
         <v>2.7459999999999998E-2</v>
       </c>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D98">
         <v>1902013</v>
       </c>
       <c r="E98" t="s">
         <v>20</v>
       </c>
-      <c r="F98">
+      <c r="F98" t="str">
+        <f>+_xlfn.XLOOKUP(D98,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G98">
         <v>2.52</v>
       </c>
-      <c r="G98">
+      <c r="H98">
         <v>7.8750000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D99">
         <v>1902014</v>
       </c>
       <c r="E99" t="s">
         <v>73</v>
       </c>
-      <c r="F99">
+      <c r="F99" t="str">
+        <f>+_xlfn.XLOOKUP(D99,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G99">
         <v>84</v>
       </c>
-      <c r="G99">
+      <c r="H99">
         <v>2.625</v>
       </c>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D100">
         <v>2302098</v>
       </c>
       <c r="E100" t="s">
         <v>74</v>
       </c>
-      <c r="F100">
+      <c r="F100" t="str">
+        <f>+_xlfn.XLOOKUP(D100,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G100">
         <v>8</v>
       </c>
-      <c r="G100">
+      <c r="H100">
         <v>0.25</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D101">
         <v>5309018</v>
       </c>
       <c r="E101" t="s">
         <v>38</v>
       </c>
-      <c r="F101">
+      <c r="F101" t="str">
+        <f>+_xlfn.XLOOKUP(D101,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>MTS</v>
+      </c>
+      <c r="G101">
         <v>96</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
         <v>75</v>
       </c>
       <c r="E102" t="s">
         <v>76</v>
       </c>
-      <c r="F102">
+      <c r="F102" t="str">
+        <f>+_xlfn.XLOOKUP(D102,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PZA</v>
+      </c>
+      <c r="G102">
         <v>96</v>
       </c>
-      <c r="G102">
+      <c r="H102">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
         <v>77</v>
       </c>
       <c r="E103" t="s">
         <v>78</v>
       </c>
-      <c r="F103">
+      <c r="F103" t="str">
+        <f>+_xlfn.XLOOKUP(D103,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G103">
         <v>10.488888888888887</v>
       </c>
-      <c r="G103">
+      <c r="H103">
         <v>0.32777777777777772</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D104" t="s">
         <v>79</v>
       </c>
       <c r="E104" t="s">
         <v>80</v>
       </c>
-      <c r="F104">
+      <c r="F104" t="str">
+        <f>+_xlfn.XLOOKUP(D104,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G104">
         <v>0.83333333333333326</v>
       </c>
-      <c r="G104">
+      <c r="H104">
         <v>2.6041666666666664E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D105" t="s">
         <v>23</v>
       </c>
       <c r="E105" t="s">
         <v>24</v>
       </c>
-      <c r="F105">
+      <c r="F105" t="str">
+        <f>+_xlfn.XLOOKUP(D105,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G105">
         <v>17.952000000000002</v>
       </c>
-      <c r="G105">
+      <c r="H105">
         <v>0.56100000000000005</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>81</v>
       </c>
@@ -2711,112 +3259,144 @@
       <c r="E106" t="s">
         <v>31</v>
       </c>
-      <c r="F106">
+      <c r="F106" t="str">
+        <f>+_xlfn.XLOOKUP(D106,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G106">
         <v>10.64</v>
       </c>
-      <c r="G106">
+      <c r="H106">
         <v>0.33250000000000002</v>
       </c>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D107">
         <v>407049</v>
       </c>
       <c r="E107" t="s">
         <v>82</v>
       </c>
-      <c r="F107">
+      <c r="F107" t="str">
+        <f>+_xlfn.XLOOKUP(D107,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G107">
         <v>480</v>
       </c>
-      <c r="G107">
+      <c r="H107">
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D108">
         <v>407115</v>
       </c>
       <c r="E108" t="s">
         <v>83</v>
       </c>
-      <c r="F108">
+      <c r="F108" t="str">
+        <f>+_xlfn.XLOOKUP(D108,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G108">
         <v>64</v>
       </c>
-      <c r="G108">
+      <c r="H108">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D109">
         <v>407427</v>
       </c>
       <c r="E109" t="s">
         <v>84</v>
       </c>
-      <c r="F109">
+      <c r="F109" t="str">
+        <f>+_xlfn.XLOOKUP(D109,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G109">
         <v>1.5999999999999999</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D110">
         <v>412301</v>
       </c>
       <c r="E110" t="s">
         <v>85</v>
       </c>
-      <c r="F110">
+      <c r="F110" t="str">
+        <f>+_xlfn.XLOOKUP(D110,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G110">
         <v>256</v>
       </c>
-      <c r="G110">
+      <c r="H110">
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D111">
         <v>412302</v>
       </c>
       <c r="E111" t="s">
         <v>86</v>
       </c>
-      <c r="F111">
+      <c r="F111" t="str">
+        <f>+_xlfn.XLOOKUP(D111,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G111">
         <v>16</v>
       </c>
-      <c r="G111">
+      <c r="H111">
         <v>0.5</v>
       </c>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D112">
         <v>701084</v>
       </c>
       <c r="E112" t="s">
         <v>87</v>
       </c>
-      <c r="F112">
+      <c r="F112" t="str">
+        <f>+_xlfn.XLOOKUP(D112,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G112">
         <v>10.64</v>
       </c>
-      <c r="G112">
+      <c r="H112">
         <v>0.33250000000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D113">
         <v>1902014</v>
       </c>
       <c r="E113" t="s">
         <v>73</v>
       </c>
-      <c r="F113">
+      <c r="F113" t="str">
+        <f>+_xlfn.XLOOKUP(D113,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G113">
         <v>5.32</v>
       </c>
-      <c r="G113">
+      <c r="H113">
         <v>0.16625000000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>88</v>
       </c>
@@ -2832,28 +3412,36 @@
       <c r="E114" t="s">
         <v>91</v>
       </c>
-      <c r="F114">
+      <c r="F114" t="str">
+        <f>+_xlfn.XLOOKUP(D114,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G114">
         <v>8</v>
       </c>
-      <c r="G114">
+      <c r="H114">
         <v>0.25</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D115">
         <v>2508169</v>
       </c>
       <c r="E115" t="s">
         <v>92</v>
       </c>
-      <c r="F115">
+      <c r="F115" t="str">
+        <f>+_xlfn.XLOOKUP(D115,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G115">
         <v>8</v>
       </c>
-      <c r="G115">
+      <c r="H115">
         <v>0.25</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C116" t="s">
         <v>93</v>
       </c>
@@ -2863,14 +3451,18 @@
       <c r="E116" t="s">
         <v>94</v>
       </c>
-      <c r="F116">
+      <c r="F116" t="str">
+        <f>+_xlfn.XLOOKUP(D116,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G116">
         <v>8</v>
       </c>
-      <c r="G116">
+      <c r="H116">
         <v>0.25</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
         <v>95</v>
       </c>
@@ -2880,14 +3472,18 @@
       <c r="E117" t="s">
         <v>96</v>
       </c>
-      <c r="F117">
+      <c r="F117" t="str">
+        <f>+_xlfn.XLOOKUP(D117,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G117">
         <v>44.666666666666671</v>
       </c>
-      <c r="G117">
+      <c r="H117">
         <v>1.3958333333333335</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>97</v>
       </c>
@@ -2900,140 +3496,180 @@
       <c r="E118" t="s">
         <v>99</v>
       </c>
-      <c r="F118">
+      <c r="F118" t="str">
+        <f>+_xlfn.XLOOKUP(D118,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G118">
         <v>8</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>0.25</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D119">
         <v>412132</v>
       </c>
       <c r="E119" t="s">
         <v>100</v>
       </c>
-      <c r="F119">
+      <c r="F119" t="str">
+        <f>+_xlfn.XLOOKUP(D119,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G119">
         <v>8</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>0.25</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D120">
         <v>1206002</v>
       </c>
       <c r="E120" t="s">
         <v>101</v>
       </c>
-      <c r="F120">
+      <c r="F120" t="str">
+        <f>+_xlfn.XLOOKUP(D120,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G120">
         <v>8</v>
       </c>
-      <c r="G120">
+      <c r="H120">
         <v>0.25</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D121">
         <v>1802171</v>
       </c>
       <c r="E121" t="s">
         <v>102</v>
       </c>
-      <c r="F121">
+      <c r="F121" t="str">
+        <f>+_xlfn.XLOOKUP(D121,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G121">
         <v>8</v>
       </c>
-      <c r="G121">
+      <c r="H121">
         <v>0.25</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D122">
         <v>1802172</v>
       </c>
       <c r="E122" t="s">
         <v>103</v>
       </c>
-      <c r="F122">
+      <c r="F122" t="str">
+        <f>+_xlfn.XLOOKUP(D122,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G122">
         <v>8</v>
       </c>
-      <c r="G122">
+      <c r="H122">
         <v>0.25</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D123">
         <v>1802517</v>
       </c>
       <c r="E123" t="s">
         <v>104</v>
       </c>
-      <c r="F123">
+      <c r="F123" t="str">
+        <f>+_xlfn.XLOOKUP(D123,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G123">
         <v>8</v>
       </c>
-      <c r="G123">
+      <c r="H123">
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D124">
         <v>1808003</v>
       </c>
       <c r="E124" t="s">
         <v>105</v>
       </c>
-      <c r="F124">
+      <c r="F124" t="str">
+        <f>+_xlfn.XLOOKUP(D124,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G124">
         <v>14</v>
       </c>
-      <c r="G124">
+      <c r="H124">
         <v>0.4375</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D125">
         <v>1808006</v>
       </c>
       <c r="E125" t="s">
         <v>106</v>
       </c>
-      <c r="F125">
+      <c r="F125" t="str">
+        <f>+_xlfn.XLOOKUP(D125,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G125">
         <v>10</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>0.3125</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D126">
         <v>1808146</v>
       </c>
       <c r="E126" t="s">
         <v>107</v>
       </c>
-      <c r="F126">
+      <c r="F126" t="str">
+        <f>+_xlfn.XLOOKUP(D126,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G126">
         <v>8</v>
       </c>
-      <c r="G126">
+      <c r="H126">
         <v>0.25</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D127">
         <v>1808156</v>
       </c>
       <c r="E127" t="s">
         <v>108</v>
       </c>
-      <c r="F127">
+      <c r="F127" t="str">
+        <f>+_xlfn.XLOOKUP(D127,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G127">
         <v>8</v>
       </c>
-      <c r="G127">
+      <c r="H127">
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>109</v>
       </c>
@@ -3046,70 +3682,90 @@
       <c r="E128" t="s">
         <v>111</v>
       </c>
-      <c r="F128">
+      <c r="F128" t="str">
+        <f>+_xlfn.XLOOKUP(D128,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G128">
         <v>8</v>
       </c>
-      <c r="G128">
+      <c r="H128">
         <v>0.25</v>
       </c>
     </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D129">
         <v>1801229</v>
       </c>
       <c r="E129" t="s">
         <v>112</v>
       </c>
-      <c r="F129">
+      <c r="F129" t="str">
+        <f>+_xlfn.XLOOKUP(D129,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G129">
         <v>8</v>
       </c>
-      <c r="G129">
+      <c r="H129">
         <v>0.25</v>
       </c>
     </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D130">
         <v>1801230</v>
       </c>
       <c r="E130" t="s">
         <v>113</v>
       </c>
-      <c r="F130">
+      <c r="F130" t="str">
+        <f>+_xlfn.XLOOKUP(D130,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G130">
         <v>8</v>
       </c>
-      <c r="G130">
+      <c r="H130">
         <v>0.25</v>
       </c>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D131">
         <v>1801735</v>
       </c>
       <c r="E131" t="s">
         <v>114</v>
       </c>
-      <c r="F131">
+      <c r="F131" t="str">
+        <f>+_xlfn.XLOOKUP(D131,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G131">
         <v>8</v>
       </c>
-      <c r="G131">
+      <c r="H131">
         <v>0.25</v>
       </c>
     </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D132">
         <v>1802162</v>
       </c>
       <c r="E132" t="s">
         <v>115</v>
       </c>
-      <c r="F132">
+      <c r="F132" t="str">
+        <f>+_xlfn.XLOOKUP(D132,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G132">
         <v>8</v>
       </c>
-      <c r="G132">
+      <c r="H132">
         <v>0.25</v>
       </c>
     </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C133" t="s">
         <v>116</v>
       </c>
@@ -3119,14 +3775,18 @@
       <c r="E133" t="s">
         <v>117</v>
       </c>
-      <c r="F133">
+      <c r="F133" t="str">
+        <f>+_xlfn.XLOOKUP(D133,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G133">
         <v>8</v>
       </c>
-      <c r="G133">
+      <c r="H133">
         <v>0.25</v>
       </c>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>118</v>
       </c>
@@ -3139,28 +3799,36 @@
       <c r="E134" t="s">
         <v>119</v>
       </c>
-      <c r="F134">
+      <c r="F134" t="str">
+        <f>+_xlfn.XLOOKUP(D134,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G134">
         <v>8</v>
       </c>
-      <c r="G134">
+      <c r="H134">
         <v>0.25</v>
       </c>
     </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D135">
         <v>1802170</v>
       </c>
       <c r="E135" t="s">
         <v>120</v>
       </c>
-      <c r="F135">
+      <c r="F135" t="str">
+        <f>+_xlfn.XLOOKUP(D135,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G135">
         <v>8</v>
       </c>
-      <c r="G135">
+      <c r="H135">
         <v>0.25</v>
       </c>
     </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C136" t="s">
         <v>116</v>
       </c>
@@ -3170,28 +3838,36 @@
       <c r="E136" t="s">
         <v>121</v>
       </c>
-      <c r="F136">
+      <c r="F136" t="str">
+        <f>+_xlfn.XLOOKUP(D136,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G136">
         <v>16</v>
       </c>
-      <c r="G136">
+      <c r="H136">
         <v>0.5</v>
       </c>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D137">
         <v>5316484</v>
       </c>
       <c r="E137" t="s">
         <v>122</v>
       </c>
-      <c r="F137">
+      <c r="F137" t="str">
+        <f>+_xlfn.XLOOKUP(D137,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G137">
         <v>16</v>
       </c>
-      <c r="G137">
+      <c r="H137">
         <v>0.5</v>
       </c>
     </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>123</v>
       </c>
@@ -3204,42 +3880,54 @@
       <c r="E138" t="s">
         <v>124</v>
       </c>
-      <c r="F138">
+      <c r="F138" t="str">
+        <f>+_xlfn.XLOOKUP(D138,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G138">
         <v>8</v>
       </c>
-      <c r="G138">
+      <c r="H138">
         <v>0.25</v>
       </c>
     </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D139">
         <v>1802174</v>
       </c>
       <c r="E139" t="s">
         <v>125</v>
       </c>
-      <c r="F139">
+      <c r="F139" t="str">
+        <f>+_xlfn.XLOOKUP(D139,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G139">
         <v>8</v>
       </c>
-      <c r="G139">
+      <c r="H139">
         <v>0.25</v>
       </c>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D140">
         <v>1802175</v>
       </c>
       <c r="E140" t="s">
         <v>126</v>
       </c>
-      <c r="F140">
+      <c r="F140" t="str">
+        <f>+_xlfn.XLOOKUP(D140,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G140">
         <v>8</v>
       </c>
-      <c r="G140">
+      <c r="H140">
         <v>0.25</v>
       </c>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
         <v>116</v>
       </c>
@@ -3249,56 +3937,72 @@
       <c r="E141" t="s">
         <v>127</v>
       </c>
-      <c r="F141">
+      <c r="F141" t="str">
+        <f>+_xlfn.XLOOKUP(D141,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G141">
         <v>8</v>
       </c>
-      <c r="G141">
+      <c r="H141">
         <v>0.25</v>
       </c>
     </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D142">
         <v>1802165</v>
       </c>
       <c r="E142" t="s">
         <v>128</v>
       </c>
-      <c r="F142">
+      <c r="F142" t="str">
+        <f>+_xlfn.XLOOKUP(D142,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G142">
         <v>8</v>
       </c>
-      <c r="G142">
+      <c r="H142">
         <v>0.25</v>
       </c>
     </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D143">
         <v>1802176</v>
       </c>
       <c r="E143" t="s">
         <v>129</v>
       </c>
-      <c r="F143">
+      <c r="F143" t="str">
+        <f>+_xlfn.XLOOKUP(D143,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G143">
         <v>8</v>
       </c>
-      <c r="G143">
+      <c r="H143">
         <v>0.25</v>
       </c>
     </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D144">
         <v>2505426</v>
       </c>
       <c r="E144" t="s">
         <v>130</v>
       </c>
-      <c r="F144">
+      <c r="F144" t="str">
+        <f>+_xlfn.XLOOKUP(D144,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G144">
         <v>8</v>
       </c>
-      <c r="G144">
+      <c r="H144">
         <v>0.25</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>131</v>
       </c>
@@ -3311,42 +4015,54 @@
       <c r="E145" t="s">
         <v>133</v>
       </c>
-      <c r="F145">
+      <c r="F145" t="str">
+        <f>+_xlfn.XLOOKUP(D145,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G145">
         <v>8</v>
       </c>
-      <c r="G145">
+      <c r="H145">
         <v>0.25</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D146">
         <v>5316508</v>
       </c>
       <c r="E146" t="s">
         <v>134</v>
       </c>
-      <c r="F146">
+      <c r="F146" t="str">
+        <f>+_xlfn.XLOOKUP(D146,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G146">
         <v>4</v>
       </c>
-      <c r="G146">
+      <c r="H146">
         <v>0.125</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D147">
         <v>5316509</v>
       </c>
       <c r="E147" t="s">
         <v>135</v>
       </c>
-      <c r="F147">
+      <c r="F147" t="str">
+        <f>+_xlfn.XLOOKUP(D147,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G147">
         <v>4</v>
       </c>
-      <c r="G147">
+      <c r="H147">
         <v>0.125</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C148" t="s">
         <v>116</v>
       </c>
@@ -3356,28 +4072,36 @@
       <c r="E148" t="s">
         <v>136</v>
       </c>
-      <c r="F148">
+      <c r="F148" t="str">
+        <f>+_xlfn.XLOOKUP(D148,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G148">
         <v>8</v>
       </c>
-      <c r="G148">
+      <c r="H148">
         <v>0.25</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D149">
         <v>1802166</v>
       </c>
       <c r="E149" t="s">
         <v>137</v>
       </c>
-      <c r="F149">
+      <c r="F149" t="str">
+        <f>+_xlfn.XLOOKUP(D149,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G149">
         <v>8</v>
       </c>
-      <c r="G149">
+      <c r="H149">
         <v>0.25</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C150" t="s">
         <v>95</v>
       </c>
@@ -3387,14 +4111,18 @@
       <c r="E150" t="s">
         <v>138</v>
       </c>
-      <c r="F150">
+      <c r="F150" t="str">
+        <f>+_xlfn.XLOOKUP(D150,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G150">
         <v>0.86666666666666692</v>
       </c>
-      <c r="G150">
+      <c r="H150">
         <v>2.7083333333333341E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>139</v>
       </c>
@@ -3407,70 +4135,90 @@
       <c r="E151" t="s">
         <v>140</v>
       </c>
-      <c r="F151">
+      <c r="F151" t="str">
+        <f>+_xlfn.XLOOKUP(D151,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G151">
         <v>8</v>
       </c>
-      <c r="G151">
+      <c r="H151">
         <v>0.25</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D152">
         <v>1808144</v>
       </c>
       <c r="E152" t="s">
         <v>141</v>
       </c>
-      <c r="F152">
+      <c r="F152" t="str">
+        <f>+_xlfn.XLOOKUP(D152,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G152">
         <v>8</v>
       </c>
-      <c r="G152">
+      <c r="H152">
         <v>0.25</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D153">
         <v>1808145</v>
       </c>
       <c r="E153" t="s">
         <v>142</v>
       </c>
-      <c r="F153">
+      <c r="F153" t="str">
+        <f>+_xlfn.XLOOKUP(D153,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G153">
         <v>8</v>
       </c>
-      <c r="G153">
+      <c r="H153">
         <v>0.25</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D154">
         <v>1808147</v>
       </c>
       <c r="E154" t="s">
         <v>143</v>
       </c>
-      <c r="F154">
+      <c r="F154" t="str">
+        <f>+_xlfn.XLOOKUP(D154,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G154">
         <v>8</v>
       </c>
-      <c r="G154">
+      <c r="H154">
         <v>0.25</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D155">
         <v>1808148</v>
       </c>
       <c r="E155" t="s">
         <v>144</v>
       </c>
-      <c r="F155">
+      <c r="F155" t="str">
+        <f>+_xlfn.XLOOKUP(D155,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G155">
         <v>8</v>
       </c>
-      <c r="G155">
+      <c r="H155">
         <v>0.25</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>145</v>
       </c>
@@ -3486,56 +4234,72 @@
       <c r="E156" t="s">
         <v>42</v>
       </c>
-      <c r="F156">
+      <c r="F156" t="str">
+        <f>+_xlfn.XLOOKUP(D156,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G156">
         <v>42</v>
       </c>
-      <c r="G156">
+      <c r="H156">
         <v>1.3125</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D157">
         <v>408014</v>
       </c>
       <c r="E157" t="s">
         <v>15</v>
       </c>
-      <c r="F157">
+      <c r="F157" t="str">
+        <f>+_xlfn.XLOOKUP(D157,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G157">
         <v>0.51839999999999986</v>
       </c>
-      <c r="G157">
+      <c r="H157">
         <v>1.6199999999999996E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D158">
         <v>701096</v>
       </c>
       <c r="E158" t="s">
         <v>36</v>
       </c>
-      <c r="F158">
+      <c r="F158" t="str">
+        <f>+_xlfn.XLOOKUP(D158,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G158">
         <v>212</v>
       </c>
-      <c r="G158">
+      <c r="H158">
         <v>6.625</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D159" t="s">
         <v>21</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
       </c>
-      <c r="F159">
+      <c r="F159" t="str">
+        <f>+_xlfn.XLOOKUP(D159,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>CJA</v>
+      </c>
+      <c r="G159">
         <v>0.34560000000000002</v>
       </c>
-      <c r="G159">
+      <c r="H159">
         <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>148</v>
       </c>
@@ -3548,84 +4312,108 @@
       <c r="E160" t="s">
         <v>150</v>
       </c>
-      <c r="F160">
+      <c r="F160" t="str">
+        <f>+_xlfn.XLOOKUP(D160,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G160">
         <v>32</v>
       </c>
-      <c r="G160">
+      <c r="H160">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D161">
         <v>608013</v>
       </c>
       <c r="E161" t="s">
         <v>151</v>
       </c>
-      <c r="F161">
+      <c r="F161" t="str">
+        <f>+_xlfn.XLOOKUP(D161,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G161">
         <v>1.6000000000000003</v>
       </c>
-      <c r="G161">
+      <c r="H161">
         <v>5.000000000000001E-2</v>
       </c>
     </row>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D162">
         <v>609008</v>
       </c>
       <c r="E162" t="s">
         <v>152</v>
       </c>
-      <c r="F162">
+      <c r="F162" t="str">
+        <f>+_xlfn.XLOOKUP(D162,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>LTS</v>
+      </c>
+      <c r="G162">
         <v>16</v>
       </c>
-      <c r="G162">
+      <c r="H162">
         <v>0.5</v>
       </c>
     </row>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D163">
         <v>1610007</v>
       </c>
       <c r="E163" t="s">
         <v>153</v>
       </c>
-      <c r="F163">
+      <c r="F163" t="str">
+        <f>+_xlfn.XLOOKUP(D163,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KG</v>
+      </c>
+      <c r="G163">
         <v>16</v>
       </c>
-      <c r="G163">
+      <c r="H163">
         <v>0.5</v>
       </c>
     </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D164">
         <v>1610023</v>
       </c>
       <c r="E164" t="s">
         <v>154</v>
       </c>
-      <c r="F164">
+      <c r="F164" t="str">
+        <f>+_xlfn.XLOOKUP(D164,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KG</v>
+      </c>
+      <c r="G164">
         <v>8</v>
       </c>
-      <c r="G164">
+      <c r="H164">
         <v>0.25</v>
       </c>
     </row>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D165">
         <v>5314002</v>
       </c>
       <c r="E165" t="s">
         <v>155</v>
       </c>
-      <c r="F165">
+      <c r="F165" t="str">
+        <f>+_xlfn.XLOOKUP(D165,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G165">
         <v>4</v>
       </c>
-      <c r="G165">
+      <c r="H165">
         <v>0.125</v>
       </c>
     </row>
-    <row r="166" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
         <v>156</v>
       </c>
@@ -3638,28 +4426,36 @@
       <c r="E166" t="s">
         <v>157</v>
       </c>
-      <c r="F166">
+      <c r="F166" t="str">
+        <f>+_xlfn.XLOOKUP(D166,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G166">
         <v>10.836772983114448</v>
       </c>
-      <c r="G166">
+      <c r="H166">
         <v>0.33864915572232651</v>
       </c>
     </row>
-    <row r="167" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D167">
         <v>2302017</v>
       </c>
       <c r="E167" t="s">
         <v>158</v>
       </c>
-      <c r="F167">
+      <c r="F167" t="str">
+        <f>+_xlfn.XLOOKUP(D167,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G167">
         <v>12.000000000000002</v>
       </c>
-      <c r="G167">
+      <c r="H167">
         <v>0.37500000000000006</v>
       </c>
     </row>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
         <v>159</v>
       </c>
@@ -3672,28 +4468,36 @@
       <c r="E168" t="s">
         <v>161</v>
       </c>
-      <c r="F168">
+      <c r="F168" t="str">
+        <f>+_xlfn.XLOOKUP(D168,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TRA</v>
+      </c>
+      <c r="G168">
         <v>128</v>
       </c>
-      <c r="G168">
+      <c r="H168">
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D169">
         <v>307096</v>
       </c>
       <c r="E169" t="s">
         <v>162</v>
       </c>
-      <c r="F169">
+      <c r="F169" t="str">
+        <f>+_xlfn.XLOOKUP(D169,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TRA</v>
+      </c>
+      <c r="G169">
         <v>992</v>
       </c>
-      <c r="G169">
+      <c r="H169">
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C170" t="s">
         <v>163</v>
       </c>
@@ -3703,14 +4507,18 @@
       <c r="E170" t="s">
         <v>164</v>
       </c>
-      <c r="F170">
+      <c r="F170" t="str">
+        <f>+_xlfn.XLOOKUP(D170,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G170">
         <v>241.76</v>
       </c>
-      <c r="G170">
+      <c r="H170">
         <v>7.5549999999999997</v>
       </c>
     </row>
-    <row r="171" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D171">
         <v>704022</v>
       </c>
@@ -3718,13 +4526,17 @@
         <v>165</v>
       </c>
       <c r="F171">
+        <f>+_xlfn.XLOOKUP(D171,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G171">
         <v>216</v>
       </c>
-      <c r="G171">
+      <c r="H171">
         <v>6.75</v>
       </c>
     </row>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D172">
         <v>704024</v>
       </c>
@@ -3732,13 +4544,17 @@
         <v>166</v>
       </c>
       <c r="F172">
+        <f>+_xlfn.XLOOKUP(D172,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G172">
         <v>64</v>
       </c>
-      <c r="G172">
+      <c r="H172">
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C173" t="s">
         <v>167</v>
       </c>
@@ -3748,14 +4564,18 @@
       <c r="E173" t="s">
         <v>168</v>
       </c>
-      <c r="F173">
+      <c r="F173" t="str">
+        <f>+_xlfn.XLOOKUP(D173,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G173">
         <v>112</v>
       </c>
-      <c r="G173">
+      <c r="H173">
         <v>3.5</v>
       </c>
     </row>
-    <row r="174" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D174">
         <v>704023</v>
       </c>
@@ -3763,13 +4583,17 @@
         <v>169</v>
       </c>
       <c r="F174">
+        <f>+_xlfn.XLOOKUP(D174,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G174">
         <v>360</v>
       </c>
-      <c r="G174">
+      <c r="H174">
         <v>11.25</v>
       </c>
     </row>
-    <row r="175" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D175">
         <v>704025</v>
       </c>
@@ -3777,13 +4601,17 @@
         <v>170</v>
       </c>
       <c r="F175">
+        <f>+_xlfn.XLOOKUP(D175,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G175">
         <v>64</v>
       </c>
-      <c r="G175">
+      <c r="H175">
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C176" t="s">
         <v>171</v>
       </c>
@@ -3793,14 +4621,18 @@
       <c r="E176" t="s">
         <v>172</v>
       </c>
-      <c r="F176">
+      <c r="F176" t="str">
+        <f>+_xlfn.XLOOKUP(D176,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G176">
         <v>56</v>
       </c>
-      <c r="G176">
+      <c r="H176">
         <v>1.75</v>
       </c>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>173</v>
       </c>
@@ -3813,56 +4645,72 @@
       <c r="E177" t="s">
         <v>69</v>
       </c>
-      <c r="F177">
+      <c r="F177" t="str">
+        <f>+_xlfn.XLOOKUP(D177,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G177">
         <v>710.63924799999995</v>
       </c>
-      <c r="G177">
+      <c r="H177">
         <v>22.207476499999999</v>
       </c>
     </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D178">
         <v>1901038</v>
       </c>
       <c r="E178" t="s">
         <v>175</v>
       </c>
-      <c r="F178">
+      <c r="F178" t="str">
+        <f>+_xlfn.XLOOKUP(D178,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G178">
         <v>259.19999999999993</v>
       </c>
-      <c r="G178">
+      <c r="H178">
         <v>8.0999999999999979</v>
       </c>
     </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D179">
         <v>1901086</v>
       </c>
       <c r="E179" t="s">
         <v>70</v>
       </c>
-      <c r="F179">
+      <c r="F179" t="str">
+        <f>+_xlfn.XLOOKUP(D179,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G179">
         <v>123.466624</v>
       </c>
-      <c r="G179">
+      <c r="H179">
         <v>3.8583319999999999</v>
       </c>
     </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D180">
         <v>1901466</v>
       </c>
       <c r="E180" t="s">
         <v>176</v>
       </c>
-      <c r="F180">
+      <c r="F180" t="str">
+        <f>+_xlfn.XLOOKUP(D180,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>M2</v>
+      </c>
+      <c r="G180">
         <v>449.96991999999995</v>
       </c>
-      <c r="G180">
+      <c r="H180">
         <v>14.061559999999998</v>
       </c>
     </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
         <v>173</v>
       </c>
@@ -3872,28 +4720,36 @@
       <c r="E181" t="s">
         <v>32</v>
       </c>
-      <c r="F181">
+      <c r="F181" t="str">
+        <f>+_xlfn.XLOOKUP(D181,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G181">
         <v>272</v>
       </c>
-      <c r="G181">
+      <c r="H181">
         <v>8.5</v>
       </c>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D182">
         <v>2302119</v>
       </c>
       <c r="E182" t="s">
         <v>177</v>
       </c>
-      <c r="F182">
+      <c r="F182" t="str">
+        <f>+_xlfn.XLOOKUP(D182,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G182">
         <v>24</v>
       </c>
-      <c r="G182">
+      <c r="H182">
         <v>0.75</v>
       </c>
     </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>178</v>
       </c>
@@ -3906,14 +4762,18 @@
       <c r="E183" t="s">
         <v>180</v>
       </c>
-      <c r="F183">
+      <c r="F183" t="str">
+        <f>+_xlfn.XLOOKUP(D183,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G183">
         <v>120</v>
       </c>
-      <c r="G183">
+      <c r="H183">
         <v>3.75</v>
       </c>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D184">
         <v>704021</v>
       </c>
@@ -3921,13 +4781,17 @@
         <v>181</v>
       </c>
       <c r="F184">
+        <f>+_xlfn.XLOOKUP(D184,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G184">
         <v>320</v>
       </c>
-      <c r="G184">
+      <c r="H184">
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>182</v>
       </c>
@@ -3940,112 +4804,144 @@
       <c r="E185" t="s">
         <v>184</v>
       </c>
-      <c r="F185">
+      <c r="F185" t="str">
+        <f>+_xlfn.XLOOKUP(D185,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G185">
         <v>2.4</v>
       </c>
-      <c r="G185">
+      <c r="H185">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D186">
         <v>602254</v>
       </c>
       <c r="E186" t="s">
         <v>185</v>
       </c>
-      <c r="F186">
+      <c r="F186" t="str">
+        <f>+_xlfn.XLOOKUP(D186,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G186">
         <v>5.4736500000000001</v>
       </c>
-      <c r="G186">
+      <c r="H186">
         <v>0.1710515625</v>
       </c>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D187">
         <v>602255</v>
       </c>
       <c r="E187" t="s">
         <v>186</v>
       </c>
-      <c r="F187">
+      <c r="F187" t="str">
+        <f>+_xlfn.XLOOKUP(D187,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G187">
         <v>4.6010999999999997</v>
       </c>
-      <c r="G187">
+      <c r="H187">
         <v>0.14378437499999999</v>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D188">
         <v>617016</v>
       </c>
       <c r="E188" t="s">
         <v>187</v>
       </c>
-      <c r="F188">
+      <c r="F188" t="str">
+        <f>+_xlfn.XLOOKUP(D188,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G188">
         <v>64</v>
       </c>
-      <c r="G188">
+      <c r="H188">
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D189">
         <v>617055</v>
       </c>
       <c r="E189" t="s">
         <v>188</v>
       </c>
-      <c r="F189">
+      <c r="F189" t="str">
+        <f>+_xlfn.XLOOKUP(D189,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G189">
         <v>32</v>
       </c>
-      <c r="G189">
+      <c r="H189">
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D190">
         <v>617057</v>
       </c>
       <c r="E190" t="s">
         <v>50</v>
       </c>
-      <c r="F190">
+      <c r="F190" t="str">
+        <f>+_xlfn.XLOOKUP(D190,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G190">
         <v>16</v>
       </c>
-      <c r="G190">
+      <c r="H190">
         <v>0.5</v>
       </c>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D191">
         <v>704079</v>
       </c>
       <c r="E191" t="s">
         <v>189</v>
       </c>
-      <c r="F191">
+      <c r="F191" t="str">
+        <f>+_xlfn.XLOOKUP(D191,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G191">
         <v>6.8333333333333321</v>
       </c>
-      <c r="G191">
+      <c r="H191">
         <v>0.21354166666666663</v>
       </c>
     </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D192">
         <v>2304053</v>
       </c>
       <c r="E192" t="s">
         <v>190</v>
       </c>
-      <c r="F192">
+      <c r="F192" t="str">
+        <f>+_xlfn.XLOOKUP(D192,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G192">
         <v>64</v>
       </c>
-      <c r="G192">
+      <c r="H192">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
         <v>191</v>
       </c>
@@ -4058,56 +4954,72 @@
       <c r="E193" t="s">
         <v>192</v>
       </c>
-      <c r="F193">
+      <c r="F193" t="str">
+        <f>+_xlfn.XLOOKUP(D193,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G193">
         <v>51</v>
       </c>
-      <c r="G193">
+      <c r="H193">
         <v>1.59375</v>
       </c>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D194">
         <v>1103074</v>
       </c>
       <c r="E194" t="s">
         <v>193</v>
       </c>
-      <c r="F194">
+      <c r="F194" t="str">
+        <f>+_xlfn.XLOOKUP(D194,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G194">
         <v>32</v>
       </c>
-      <c r="G194">
+      <c r="H194">
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D195">
         <v>1103076</v>
       </c>
       <c r="E195" t="s">
         <v>194</v>
       </c>
-      <c r="F195">
+      <c r="F195" t="str">
+        <f>+_xlfn.XLOOKUP(D195,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G195">
         <v>48</v>
       </c>
-      <c r="G195">
+      <c r="H195">
         <v>1.5</v>
       </c>
     </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D196">
         <v>2304008</v>
       </c>
       <c r="E196" t="s">
         <v>195</v>
       </c>
-      <c r="F196">
+      <c r="F196" t="str">
+        <f>+_xlfn.XLOOKUP(D196,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G196">
         <v>16</v>
       </c>
-      <c r="G196">
+      <c r="H196">
         <v>0.5</v>
       </c>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
         <v>196</v>
       </c>
@@ -4120,42 +5032,54 @@
       <c r="E197" t="s">
         <v>198</v>
       </c>
-      <c r="F197">
+      <c r="F197" t="str">
+        <f>+_xlfn.XLOOKUP(D197,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G197">
         <v>8</v>
       </c>
-      <c r="G197">
+      <c r="H197">
         <v>0.25</v>
       </c>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D198">
         <v>1805340</v>
       </c>
       <c r="E198" t="s">
         <v>199</v>
       </c>
-      <c r="F198">
+      <c r="F198" t="str">
+        <f>+_xlfn.XLOOKUP(D198,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G198">
         <v>16</v>
       </c>
-      <c r="G198">
+      <c r="H198">
         <v>0.5</v>
       </c>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D199">
         <v>2505058</v>
       </c>
       <c r="E199" t="s">
         <v>200</v>
       </c>
-      <c r="F199">
+      <c r="F199" t="str">
+        <f>+_xlfn.XLOOKUP(D199,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G199">
         <v>32</v>
       </c>
-      <c r="G199">
+      <c r="H199">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>201</v>
       </c>
@@ -4168,14 +5092,18 @@
       <c r="E200" t="s">
         <v>203</v>
       </c>
-      <c r="F200">
+      <c r="F200" t="str">
+        <f>+_xlfn.XLOOKUP(D200,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TRA</v>
+      </c>
+      <c r="G200">
         <v>208</v>
       </c>
-      <c r="G200">
+      <c r="H200">
         <v>6.5</v>
       </c>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C201" t="s">
         <v>201</v>
       </c>
@@ -4185,56 +5113,72 @@
       <c r="E201" t="s">
         <v>204</v>
       </c>
-      <c r="F201">
+      <c r="F201" t="str">
+        <f>+_xlfn.XLOOKUP(D201,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G201">
         <v>320</v>
       </c>
-      <c r="G201">
+      <c r="H201">
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D202">
         <v>407185</v>
       </c>
       <c r="E202" t="s">
         <v>205</v>
       </c>
-      <c r="F202">
+      <c r="F202" t="str">
+        <f>+_xlfn.XLOOKUP(D202,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G202">
         <v>14720</v>
       </c>
-      <c r="G202">
+      <c r="H202">
         <v>460</v>
       </c>
     </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D203">
         <v>1902003</v>
       </c>
       <c r="E203" t="s">
         <v>72</v>
       </c>
-      <c r="F203">
+      <c r="F203" t="str">
+        <f>+_xlfn.XLOOKUP(D203,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G203">
         <v>5.44</v>
       </c>
-      <c r="G203">
+      <c r="H203">
         <v>0.17</v>
       </c>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D204" t="s">
         <v>206</v>
       </c>
       <c r="E204" t="s">
         <v>207</v>
       </c>
-      <c r="F204">
+      <c r="F204" t="str">
+        <f>+_xlfn.XLOOKUP(D204,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G204">
         <v>268</v>
       </c>
-      <c r="G204">
+      <c r="H204">
         <v>8.375</v>
       </c>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
         <v>81</v>
       </c>
@@ -4247,14 +5191,18 @@
       <c r="E205" t="s">
         <v>209</v>
       </c>
-      <c r="F205">
+      <c r="F205" t="str">
+        <f>+_xlfn.XLOOKUP(D205,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G205">
         <v>8</v>
       </c>
-      <c r="G205">
+      <c r="H205">
         <v>0.25</v>
       </c>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C206" t="s">
         <v>202</v>
       </c>
@@ -4264,42 +5212,54 @@
       <c r="E206" t="s">
         <v>210</v>
       </c>
-      <c r="F206">
+      <c r="F206" t="str">
+        <f>+_xlfn.XLOOKUP(D206,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G206">
         <v>8</v>
       </c>
-      <c r="G206">
+      <c r="H206">
         <v>0.25</v>
       </c>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D207">
         <v>1103087</v>
       </c>
       <c r="E207" t="s">
         <v>211</v>
       </c>
-      <c r="F207">
+      <c r="F207" t="str">
+        <f>+_xlfn.XLOOKUP(D207,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G207">
         <v>8</v>
       </c>
-      <c r="G207">
+      <c r="H207">
         <v>0.25</v>
       </c>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D208">
         <v>1103088</v>
       </c>
       <c r="E208" t="s">
         <v>212</v>
       </c>
-      <c r="F208">
+      <c r="F208" t="str">
+        <f>+_xlfn.XLOOKUP(D208,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TRA</v>
+      </c>
+      <c r="G208">
         <v>16</v>
       </c>
-      <c r="G208">
+      <c r="H208">
         <v>0.5</v>
       </c>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
         <v>183</v>
       </c>
@@ -4309,42 +5269,54 @@
       <c r="E209" t="s">
         <v>213</v>
       </c>
-      <c r="F209">
+      <c r="F209" t="str">
+        <f>+_xlfn.XLOOKUP(D209,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G209">
         <v>0.39999999999999997</v>
       </c>
-      <c r="G209">
+      <c r="H209">
         <v>1.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D210">
         <v>602257</v>
       </c>
       <c r="E210" t="s">
         <v>214</v>
       </c>
-      <c r="F210">
+      <c r="F210" t="str">
+        <f>+_xlfn.XLOOKUP(D210,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G210">
         <v>3.1999999999999997</v>
       </c>
-      <c r="G210">
+      <c r="H210">
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D211">
         <v>602258</v>
       </c>
       <c r="E211" t="s">
         <v>215</v>
       </c>
-      <c r="F211">
+      <c r="F211" t="str">
+        <f>+_xlfn.XLOOKUP(D211,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TIN</v>
+      </c>
+      <c r="G211">
         <v>1.4000000000000001</v>
       </c>
-      <c r="G211">
+      <c r="H211">
         <v>4.3750000000000004E-2</v>
       </c>
     </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C212" t="s">
         <v>98</v>
       </c>
@@ -4354,14 +5326,18 @@
       <c r="E212" t="s">
         <v>216</v>
       </c>
-      <c r="F212">
+      <c r="F212" t="str">
+        <f>+_xlfn.XLOOKUP(D212,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>TRA</v>
+      </c>
+      <c r="G212">
         <v>2</v>
       </c>
-      <c r="G212">
+      <c r="H212">
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C213" t="s">
         <v>63</v>
       </c>
@@ -4371,14 +5347,18 @@
       <c r="E213" t="s">
         <v>204</v>
       </c>
-      <c r="F213">
+      <c r="F213" t="str">
+        <f>+_xlfn.XLOOKUP(D213,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G213">
         <v>32</v>
       </c>
-      <c r="G213">
+      <c r="H213">
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
         <v>217</v>
       </c>
@@ -4391,84 +5371,108 @@
       <c r="E214" t="s">
         <v>111</v>
       </c>
-      <c r="F214">
+      <c r="F214" t="str">
+        <f>+_xlfn.XLOOKUP(D214,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G214">
         <v>32</v>
       </c>
-      <c r="G214">
+      <c r="H214">
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D215">
         <v>412630</v>
       </c>
       <c r="E215" t="s">
         <v>218</v>
       </c>
-      <c r="F215">
+      <c r="F215" t="str">
+        <f>+_xlfn.XLOOKUP(D215,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G215">
         <v>8</v>
       </c>
-      <c r="G215">
+      <c r="H215">
         <v>0.25</v>
       </c>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D216">
         <v>704046</v>
       </c>
       <c r="E216" t="s">
         <v>219</v>
       </c>
-      <c r="F216">
+      <c r="F216" t="str">
+        <f>+_xlfn.XLOOKUP(D216,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>RLL</v>
+      </c>
+      <c r="G216">
         <v>13.481967213114757</v>
       </c>
-      <c r="G216">
+      <c r="H216">
         <v>0.42131147540983616</v>
       </c>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D217" t="s">
         <v>220</v>
       </c>
       <c r="E217" t="s">
         <v>221</v>
       </c>
-      <c r="F217">
+      <c r="F217" t="str">
+        <f>+_xlfn.XLOOKUP(D217,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G217">
         <v>24</v>
       </c>
-      <c r="G217">
+      <c r="H217">
         <v>0.75</v>
       </c>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D218" t="s">
         <v>222</v>
       </c>
       <c r="E218" t="s">
         <v>223</v>
       </c>
-      <c r="F218">
+      <c r="F218" t="str">
+        <f>+_xlfn.XLOOKUP(D218,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G218">
         <v>8</v>
       </c>
-      <c r="G218">
+      <c r="H218">
         <v>0.25</v>
       </c>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D219" t="s">
         <v>224</v>
       </c>
       <c r="E219" t="s">
         <v>225</v>
       </c>
-      <c r="F219">
+      <c r="F219" t="str">
+        <f>+_xlfn.XLOOKUP(D219,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G219">
         <v>8</v>
       </c>
-      <c r="G219">
+      <c r="H219">
         <v>0.25</v>
       </c>
     </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
         <v>226</v>
       </c>
@@ -4481,14 +5485,18 @@
       <c r="E220" t="s">
         <v>32</v>
       </c>
-      <c r="F220">
+      <c r="F220" t="str">
+        <f>+_xlfn.XLOOKUP(D220,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>PL</v>
+      </c>
+      <c r="G220">
         <v>160</v>
       </c>
-      <c r="G220">
+      <c r="H220">
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
         <v>227</v>
       </c>
@@ -4501,28 +5509,36 @@
       <c r="E221" t="s">
         <v>228</v>
       </c>
-      <c r="F221">
+      <c r="F221" t="str">
+        <f>+_xlfn.XLOOKUP(D221,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G221">
         <v>8</v>
       </c>
-      <c r="G221">
+      <c r="H221">
         <v>0.25</v>
       </c>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D222">
         <v>1101307</v>
       </c>
       <c r="E222" t="s">
         <v>229</v>
       </c>
-      <c r="F222">
+      <c r="F222" t="str">
+        <f>+_xlfn.XLOOKUP(D222,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>ML</v>
+      </c>
+      <c r="G222">
         <v>8</v>
       </c>
-      <c r="G222">
+      <c r="H222">
         <v>0.25</v>
       </c>
     </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C223" t="s">
         <v>230</v>
       </c>
@@ -4532,84 +5548,108 @@
       <c r="E223" t="s">
         <v>231</v>
       </c>
-      <c r="F223">
+      <c r="F223" t="str">
+        <f>+_xlfn.XLOOKUP(D223,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G223">
         <v>8</v>
       </c>
-      <c r="G223">
+      <c r="H223">
         <v>0.25</v>
       </c>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D224">
         <v>2508990</v>
       </c>
       <c r="E224" t="s">
         <v>232</v>
       </c>
-      <c r="F224">
+      <c r="F224" t="str">
+        <f>+_xlfn.XLOOKUP(D224,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G224">
         <v>8</v>
       </c>
-      <c r="G224">
+      <c r="H224">
         <v>0.25</v>
       </c>
     </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D225">
         <v>2508991</v>
       </c>
       <c r="E225" t="s">
         <v>233</v>
       </c>
-      <c r="F225">
+      <c r="F225" t="str">
+        <f>+_xlfn.XLOOKUP(D225,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G225">
         <v>8</v>
       </c>
-      <c r="G225">
+      <c r="H225">
         <v>0.25</v>
       </c>
     </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D226">
         <v>2508992</v>
       </c>
       <c r="E226" t="s">
         <v>234</v>
       </c>
-      <c r="F226">
+      <c r="F226" t="str">
+        <f>+_xlfn.XLOOKUP(D226,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>JGO</v>
+      </c>
+      <c r="G226">
         <v>4</v>
       </c>
-      <c r="G226">
+      <c r="H226">
         <v>0.125</v>
       </c>
     </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D227">
         <v>2508993</v>
       </c>
       <c r="E227" t="s">
         <v>235</v>
       </c>
-      <c r="F227">
+      <c r="F227" t="str">
+        <f>+_xlfn.XLOOKUP(D227,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>JGO</v>
+      </c>
+      <c r="G227">
         <v>8</v>
       </c>
-      <c r="G227">
+      <c r="H227">
         <v>0.25</v>
       </c>
     </row>
-    <row r="228" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D228">
         <v>2508994</v>
       </c>
       <c r="E228" t="s">
         <v>236</v>
       </c>
-      <c r="F228">
+      <c r="F228" t="str">
+        <f>+_xlfn.XLOOKUP(D228,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G228">
         <v>8</v>
       </c>
-      <c r="G228">
+      <c r="H228">
         <v>0.25</v>
       </c>
     </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
         <v>237</v>
       </c>
@@ -4619,28 +5659,36 @@
       <c r="E229" t="s">
         <v>238</v>
       </c>
-      <c r="F229">
+      <c r="F229" t="str">
+        <f>+_xlfn.XLOOKUP(D229,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G229">
         <v>4</v>
       </c>
-      <c r="G229">
+      <c r="H229">
         <v>0.125</v>
       </c>
     </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D230">
         <v>2508986</v>
       </c>
       <c r="E230" t="s">
         <v>239</v>
       </c>
-      <c r="F230">
+      <c r="F230" t="str">
+        <f>+_xlfn.XLOOKUP(D230,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G230">
         <v>4</v>
       </c>
-      <c r="G230">
+      <c r="H230">
         <v>0.125</v>
       </c>
     </row>
-    <row r="231" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>237</v>
       </c>
@@ -4653,14 +5701,18 @@
       <c r="E231" t="s">
         <v>241</v>
       </c>
-      <c r="F231">
+      <c r="F231" t="str">
+        <f>+_xlfn.XLOOKUP(D231,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G231">
         <v>48</v>
       </c>
-      <c r="G231">
+      <c r="H231">
         <v>1.5</v>
       </c>
     </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
         <v>242</v>
       </c>
@@ -4670,14 +5722,18 @@
       <c r="E232" t="s">
         <v>111</v>
       </c>
-      <c r="F232">
+      <c r="F232" t="str">
+        <f>+_xlfn.XLOOKUP(D232,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G232">
         <v>24</v>
       </c>
-      <c r="G232">
+      <c r="H232">
         <v>0.75</v>
       </c>
     </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>243</v>
       </c>
@@ -4690,56 +5746,72 @@
       <c r="E233" t="s">
         <v>232</v>
       </c>
-      <c r="F233">
+      <c r="F233" t="str">
+        <f>+_xlfn.XLOOKUP(D233,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G233">
         <v>8</v>
       </c>
-      <c r="G233">
+      <c r="H233">
         <v>0.25</v>
       </c>
     </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D234">
         <v>2508991</v>
       </c>
       <c r="E234" t="s">
         <v>233</v>
       </c>
-      <c r="F234">
+      <c r="F234" t="str">
+        <f>+_xlfn.XLOOKUP(D234,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G234">
         <v>8</v>
       </c>
-      <c r="G234">
+      <c r="H234">
         <v>0.25</v>
       </c>
     </row>
-    <row r="235" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D235">
         <v>2508992</v>
       </c>
       <c r="E235" t="s">
         <v>234</v>
       </c>
-      <c r="F235">
+      <c r="F235" t="str">
+        <f>+_xlfn.XLOOKUP(D235,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>JGO</v>
+      </c>
+      <c r="G235">
         <v>8</v>
       </c>
-      <c r="G235">
+      <c r="H235">
         <v>0.25</v>
       </c>
     </row>
-    <row r="236" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D236">
         <v>2508993</v>
       </c>
       <c r="E236" t="s">
         <v>235</v>
       </c>
-      <c r="F236">
+      <c r="F236" t="str">
+        <f>+_xlfn.XLOOKUP(D236,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>JGO</v>
+      </c>
+      <c r="G236">
         <v>8</v>
       </c>
-      <c r="G236">
+      <c r="H236">
         <v>0.25</v>
       </c>
     </row>
-    <row r="237" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C237" t="s">
         <v>237</v>
       </c>
@@ -4749,28 +5821,36 @@
       <c r="E237" t="s">
         <v>244</v>
       </c>
-      <c r="F237">
+      <c r="F237" t="str">
+        <f>+_xlfn.XLOOKUP(D237,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G237">
         <v>4</v>
       </c>
-      <c r="G237">
+      <c r="H237">
         <v>0.125</v>
       </c>
     </row>
-    <row r="238" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D238">
         <v>2508988</v>
       </c>
       <c r="E238" t="s">
         <v>245</v>
       </c>
-      <c r="F238">
+      <c r="F238" t="str">
+        <f>+_xlfn.XLOOKUP(D238,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G238">
         <v>4</v>
       </c>
-      <c r="G238">
+      <c r="H238">
         <v>0.125</v>
       </c>
     </row>
-    <row r="239" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>246</v>
       </c>
@@ -4783,14 +5863,18 @@
       <c r="E239" t="s">
         <v>247</v>
       </c>
-      <c r="F239">
+      <c r="F239" t="str">
+        <f>+_xlfn.XLOOKUP(D239,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G239">
         <v>8</v>
       </c>
-      <c r="G239">
+      <c r="H239">
         <v>0.25</v>
       </c>
     </row>
-    <row r="240" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C240" t="s">
         <v>237</v>
       </c>
@@ -4800,28 +5884,36 @@
       <c r="E240" t="s">
         <v>248</v>
       </c>
-      <c r="F240">
+      <c r="F240" t="str">
+        <f>+_xlfn.XLOOKUP(D240,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G240">
         <v>4</v>
       </c>
-      <c r="G240">
+      <c r="H240">
         <v>0.125</v>
       </c>
     </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D241">
         <v>1803045</v>
       </c>
       <c r="E241" t="s">
         <v>249</v>
       </c>
-      <c r="F241">
+      <c r="F241" t="str">
+        <f>+_xlfn.XLOOKUP(D241,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G241">
         <v>4</v>
       </c>
-      <c r="G241">
+      <c r="H241">
         <v>0.125</v>
       </c>
     </row>
-    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
         <v>250</v>
       </c>
@@ -4834,28 +5926,36 @@
       <c r="E242" t="s">
         <v>251</v>
       </c>
-      <c r="F242">
+      <c r="F242" t="str">
+        <f>+_xlfn.XLOOKUP(D242,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G242">
         <v>8</v>
       </c>
-      <c r="G242">
+      <c r="H242">
         <v>0.25</v>
       </c>
     </row>
-    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D243">
         <v>1405040</v>
       </c>
       <c r="E243" t="s">
         <v>247</v>
       </c>
-      <c r="F243">
+      <c r="F243" t="str">
+        <f>+_xlfn.XLOOKUP(D243,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>UND</v>
+      </c>
+      <c r="G243">
         <v>16</v>
       </c>
-      <c r="G243">
+      <c r="H243">
         <v>0.5</v>
       </c>
     </row>
-    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
         <v>237</v>
       </c>
@@ -4865,28 +5965,3075 @@
       <c r="E244" t="s">
         <v>248</v>
       </c>
-      <c r="F244">
+      <c r="F244" t="str">
+        <f>+_xlfn.XLOOKUP(D244,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G244">
         <v>12</v>
       </c>
-      <c r="G244">
+      <c r="H244">
         <v>0.375</v>
       </c>
     </row>
-    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D245">
         <v>1803045</v>
       </c>
       <c r="E245" t="s">
         <v>249</v>
       </c>
-      <c r="F245">
+      <c r="F245" t="str">
+        <f>+_xlfn.XLOOKUP(D245,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <v>KIT</v>
+      </c>
+      <c r="G245">
         <v>12</v>
       </c>
-      <c r="G245">
+      <c r="H245">
         <v>0.375</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D21CD9-5B6C-44F0-BB08-EDDC057A186D}">
+  <dimension ref="A1:D611"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>106022</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>302010</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>302028</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>302046</v>
+      </c>
+      <c r="B5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>302048</v>
+      </c>
+      <c r="B6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>302054</v>
+      </c>
+      <c r="B7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>302248</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>302249</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>304002</v>
+      </c>
+      <c r="B10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>304007</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>304012</v>
+      </c>
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>304049</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D13">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>304101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>307030</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>307031</v>
+      </c>
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>307032</v>
+      </c>
+      <c r="B17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>307033</v>
+      </c>
+      <c r="B18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D18">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>307096</v>
+      </c>
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>403024</v>
+      </c>
+      <c r="B20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" t="s">
+        <v>258</v>
+      </c>
+      <c r="D20">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>404252</v>
+      </c>
+      <c r="B21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>404745</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>404793</v>
+      </c>
+      <c r="B23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" t="s">
+        <v>258</v>
+      </c>
+      <c r="D23">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>407010</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>407011</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>407049</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>258</v>
+      </c>
+      <c r="D26">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>407115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>258</v>
+      </c>
+      <c r="D27">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>407170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>258</v>
+      </c>
+      <c r="D28">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>407185</v>
+      </c>
+      <c r="B29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" t="s">
+        <v>258</v>
+      </c>
+      <c r="D29">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>407307</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>258</v>
+      </c>
+      <c r="D30">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>407423</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D31">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>407427</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D32">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>407795</v>
+      </c>
+      <c r="B33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>408014</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="s">
+        <v>266</v>
+      </c>
+      <c r="D34">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>408017</v>
+      </c>
+      <c r="B35" t="s">
+        <v>267</v>
+      </c>
+      <c r="C35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D35">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>408034</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>408042</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>266</v>
+      </c>
+      <c r="D37">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>408088</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>266</v>
+      </c>
+      <c r="D38">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>409011</v>
+      </c>
+      <c r="B39" t="s">
+        <v>216</v>
+      </c>
+      <c r="C39" t="s">
+        <v>264</v>
+      </c>
+      <c r="D39">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>410045</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" t="s">
+        <v>258</v>
+      </c>
+      <c r="D40">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>410046</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>258</v>
+      </c>
+      <c r="D41">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>410126</v>
+      </c>
+      <c r="B42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D42">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>412016</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>258</v>
+      </c>
+      <c r="D43">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>412132</v>
+      </c>
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>412260</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D45">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>412280</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>258</v>
+      </c>
+      <c r="D46">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>412281</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>258</v>
+      </c>
+      <c r="D47">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>412301</v>
+      </c>
+      <c r="B48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" t="s">
+        <v>258</v>
+      </c>
+      <c r="D48">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>412302</v>
+      </c>
+      <c r="B49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>412313</v>
+      </c>
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>266</v>
+      </c>
+      <c r="D50">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>412630</v>
+      </c>
+      <c r="B51" t="s">
+        <v>218</v>
+      </c>
+      <c r="C51" t="s">
+        <v>258</v>
+      </c>
+      <c r="D51">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>601047</v>
+      </c>
+      <c r="B52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" t="s">
+        <v>268</v>
+      </c>
+      <c r="D52">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>601121</v>
+      </c>
+      <c r="B53" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>602254</v>
+      </c>
+      <c r="B54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C54" t="s">
+        <v>268</v>
+      </c>
+      <c r="D54">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>602255</v>
+      </c>
+      <c r="B55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" t="s">
+        <v>268</v>
+      </c>
+      <c r="D55">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>602256</v>
+      </c>
+      <c r="B56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" t="s">
+        <v>268</v>
+      </c>
+      <c r="D56">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>602257</v>
+      </c>
+      <c r="B57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" t="s">
+        <v>268</v>
+      </c>
+      <c r="D57">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>602258</v>
+      </c>
+      <c r="B58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" t="s">
+        <v>268</v>
+      </c>
+      <c r="D58">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>608013</v>
+      </c>
+      <c r="B59" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" t="s">
+        <v>258</v>
+      </c>
+      <c r="D59">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>609008</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" t="s">
+        <v>271</v>
+      </c>
+      <c r="D60">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>617016</v>
+      </c>
+      <c r="B61" t="s">
+        <v>187</v>
+      </c>
+      <c r="C61" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>617055</v>
+      </c>
+      <c r="B62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C62" t="s">
+        <v>258</v>
+      </c>
+      <c r="D62">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>617057</v>
+      </c>
+      <c r="B63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>701015</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" t="s">
+        <v>263</v>
+      </c>
+      <c r="D64">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>701040</v>
+      </c>
+      <c r="B65" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" t="s">
+        <v>263</v>
+      </c>
+      <c r="D65">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>701043</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>701084</v>
+      </c>
+      <c r="B67" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" t="s">
+        <v>263</v>
+      </c>
+      <c r="D67">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>701096</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" t="s">
+        <v>263</v>
+      </c>
+      <c r="D68">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>704021</v>
+      </c>
+      <c r="B69" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>704022</v>
+      </c>
+      <c r="B70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>704023</v>
+      </c>
+      <c r="B71" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>704024</v>
+      </c>
+      <c r="B72" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>704025</v>
+      </c>
+      <c r="B73" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>704046</v>
+      </c>
+      <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>272</v>
+      </c>
+      <c r="D74">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>704079</v>
+      </c>
+      <c r="B75" t="s">
+        <v>189</v>
+      </c>
+      <c r="C75" t="s">
+        <v>272</v>
+      </c>
+      <c r="D75">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>705028</v>
+      </c>
+      <c r="B76" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" t="s">
+        <v>263</v>
+      </c>
+      <c r="D76">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>707023</v>
+      </c>
+      <c r="B77" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" t="s">
+        <v>258</v>
+      </c>
+      <c r="D77">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>810007</v>
+      </c>
+      <c r="B78" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" t="s">
+        <v>264</v>
+      </c>
+      <c r="D78">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>907031</v>
+      </c>
+      <c r="B79" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" t="s">
+        <v>272</v>
+      </c>
+      <c r="D79">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1003500</v>
+      </c>
+      <c r="B80" t="s">
+        <v>203</v>
+      </c>
+      <c r="C80" t="s">
+        <v>264</v>
+      </c>
+      <c r="D80">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1101307</v>
+      </c>
+      <c r="B81" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" t="s">
+        <v>273</v>
+      </c>
+      <c r="D81">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1103074</v>
+      </c>
+      <c r="B82" t="s">
+        <v>193</v>
+      </c>
+      <c r="C82" t="s">
+        <v>258</v>
+      </c>
+      <c r="D82">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1103076</v>
+      </c>
+      <c r="B83" t="s">
+        <v>194</v>
+      </c>
+      <c r="C83" t="s">
+        <v>258</v>
+      </c>
+      <c r="D83">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1103086</v>
+      </c>
+      <c r="B84" t="s">
+        <v>274</v>
+      </c>
+      <c r="C84" t="s">
+        <v>258</v>
+      </c>
+      <c r="D84">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1103087</v>
+      </c>
+      <c r="B85" t="s">
+        <v>275</v>
+      </c>
+      <c r="C85" t="s">
+        <v>258</v>
+      </c>
+      <c r="D85">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1103088</v>
+      </c>
+      <c r="B86" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1206002</v>
+      </c>
+      <c r="B87" t="s">
+        <v>101</v>
+      </c>
+      <c r="C87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1405006</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>258</v>
+      </c>
+      <c r="D88">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1405025</v>
+      </c>
+      <c r="B89" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" t="s">
+        <v>258</v>
+      </c>
+      <c r="D89">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1405026</v>
+      </c>
+      <c r="B90" t="s">
+        <v>276</v>
+      </c>
+      <c r="C90" t="s">
+        <v>277</v>
+      </c>
+      <c r="D90">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1405027</v>
+      </c>
+      <c r="B91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" t="s">
+        <v>277</v>
+      </c>
+      <c r="D91">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1405039</v>
+      </c>
+      <c r="B92" t="s">
+        <v>251</v>
+      </c>
+      <c r="C92" t="s">
+        <v>258</v>
+      </c>
+      <c r="D92">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1405040</v>
+      </c>
+      <c r="B93" t="s">
+        <v>247</v>
+      </c>
+      <c r="C93" t="s">
+        <v>258</v>
+      </c>
+      <c r="D93">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1610007</v>
+      </c>
+      <c r="B94" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" t="s">
+        <v>279</v>
+      </c>
+      <c r="D94">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1610023</v>
+      </c>
+      <c r="B95" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" t="s">
+        <v>279</v>
+      </c>
+      <c r="D95">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1701071</v>
+      </c>
+      <c r="B96" t="s">
+        <v>280</v>
+      </c>
+      <c r="C96" t="s">
+        <v>258</v>
+      </c>
+      <c r="D96">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1701154</v>
+      </c>
+      <c r="B97" t="s">
+        <v>127</v>
+      </c>
+      <c r="C97" t="s">
+        <v>258</v>
+      </c>
+      <c r="D97">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1703006</v>
+      </c>
+      <c r="B98" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" t="s">
+        <v>258</v>
+      </c>
+      <c r="D98">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1801161</v>
+      </c>
+      <c r="B99" t="s">
+        <v>281</v>
+      </c>
+      <c r="C99" t="s">
+        <v>258</v>
+      </c>
+      <c r="D99">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1801229</v>
+      </c>
+      <c r="B100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C100" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1801230</v>
+      </c>
+      <c r="B101" t="s">
+        <v>113</v>
+      </c>
+      <c r="C101" t="s">
+        <v>258</v>
+      </c>
+      <c r="D101">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1801735</v>
+      </c>
+      <c r="B102" t="s">
+        <v>114</v>
+      </c>
+      <c r="C102" t="s">
+        <v>258</v>
+      </c>
+      <c r="D102">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1802162</v>
+      </c>
+      <c r="B103" t="s">
+        <v>115</v>
+      </c>
+      <c r="C103" t="s">
+        <v>258</v>
+      </c>
+      <c r="D103">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1802164</v>
+      </c>
+      <c r="B104" t="s">
+        <v>91</v>
+      </c>
+      <c r="C104" t="s">
+        <v>258</v>
+      </c>
+      <c r="D104">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1802165</v>
+      </c>
+      <c r="B105" t="s">
+        <v>128</v>
+      </c>
+      <c r="C105" t="s">
+        <v>258</v>
+      </c>
+      <c r="D105">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1802166</v>
+      </c>
+      <c r="B106" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" t="s">
+        <v>258</v>
+      </c>
+      <c r="D106">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1802167</v>
+      </c>
+      <c r="B107" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107" t="s">
+        <v>258</v>
+      </c>
+      <c r="D107">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1802169</v>
+      </c>
+      <c r="B108" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" t="s">
+        <v>258</v>
+      </c>
+      <c r="D108">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1802170</v>
+      </c>
+      <c r="B109" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" t="s">
+        <v>258</v>
+      </c>
+      <c r="D109">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1802171</v>
+      </c>
+      <c r="B110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C110" t="s">
+        <v>258</v>
+      </c>
+      <c r="D110">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1802172</v>
+      </c>
+      <c r="B111" t="s">
+        <v>103</v>
+      </c>
+      <c r="C111" t="s">
+        <v>258</v>
+      </c>
+      <c r="D111">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1802173</v>
+      </c>
+      <c r="B112" t="s">
+        <v>124</v>
+      </c>
+      <c r="C112" t="s">
+        <v>258</v>
+      </c>
+      <c r="D112">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1802174</v>
+      </c>
+      <c r="B113" t="s">
+        <v>125</v>
+      </c>
+      <c r="C113" t="s">
+        <v>258</v>
+      </c>
+      <c r="D113">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1802175</v>
+      </c>
+      <c r="B114" t="s">
+        <v>126</v>
+      </c>
+      <c r="C114" t="s">
+        <v>258</v>
+      </c>
+      <c r="D114">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1802176</v>
+      </c>
+      <c r="B115" t="s">
+        <v>129</v>
+      </c>
+      <c r="C115" t="s">
+        <v>258</v>
+      </c>
+      <c r="D115">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1802177</v>
+      </c>
+      <c r="B116" t="s">
+        <v>282</v>
+      </c>
+      <c r="C116" t="s">
+        <v>258</v>
+      </c>
+      <c r="D116">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1802517</v>
+      </c>
+      <c r="B117" t="s">
+        <v>104</v>
+      </c>
+      <c r="C117" t="s">
+        <v>258</v>
+      </c>
+      <c r="D117">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1802659</v>
+      </c>
+      <c r="B118" t="s">
+        <v>198</v>
+      </c>
+      <c r="C118" t="s">
+        <v>258</v>
+      </c>
+      <c r="D118">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1803044</v>
+      </c>
+      <c r="B119" t="s">
+        <v>248</v>
+      </c>
+      <c r="C119" t="s">
+        <v>277</v>
+      </c>
+      <c r="D119">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1803045</v>
+      </c>
+      <c r="B120" t="s">
+        <v>249</v>
+      </c>
+      <c r="C120" t="s">
+        <v>277</v>
+      </c>
+      <c r="D120">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1805340</v>
+      </c>
+      <c r="B121" t="s">
+        <v>199</v>
+      </c>
+      <c r="C121" t="s">
+        <v>258</v>
+      </c>
+      <c r="D121">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1808003</v>
+      </c>
+      <c r="B122" t="s">
+        <v>105</v>
+      </c>
+      <c r="C122" t="s">
+        <v>258</v>
+      </c>
+      <c r="D122">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1808006</v>
+      </c>
+      <c r="B123" t="s">
+        <v>106</v>
+      </c>
+      <c r="C123" t="s">
+        <v>258</v>
+      </c>
+      <c r="D123">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1808083</v>
+      </c>
+      <c r="B124" t="s">
+        <v>283</v>
+      </c>
+      <c r="C124" t="s">
+        <v>258</v>
+      </c>
+      <c r="D124">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>1808144</v>
+      </c>
+      <c r="B125" t="s">
+        <v>141</v>
+      </c>
+      <c r="C125" t="s">
+        <v>258</v>
+      </c>
+      <c r="D125">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>1808145</v>
+      </c>
+      <c r="B126" t="s">
+        <v>142</v>
+      </c>
+      <c r="C126" t="s">
+        <v>258</v>
+      </c>
+      <c r="D126">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>1808146</v>
+      </c>
+      <c r="B127" t="s">
+        <v>107</v>
+      </c>
+      <c r="C127" t="s">
+        <v>258</v>
+      </c>
+      <c r="D127">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>1808147</v>
+      </c>
+      <c r="B128" t="s">
+        <v>143</v>
+      </c>
+      <c r="C128" t="s">
+        <v>258</v>
+      </c>
+      <c r="D128">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>1808148</v>
+      </c>
+      <c r="B129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C129" t="s">
+        <v>258</v>
+      </c>
+      <c r="D129">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>1808156</v>
+      </c>
+      <c r="B130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C130" t="s">
+        <v>258</v>
+      </c>
+      <c r="D130">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>1901008</v>
+      </c>
+      <c r="B131" t="s">
+        <v>69</v>
+      </c>
+      <c r="C131" t="s">
+        <v>284</v>
+      </c>
+      <c r="D131">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>1901038</v>
+      </c>
+      <c r="B132" t="s">
+        <v>175</v>
+      </c>
+      <c r="C132" t="s">
+        <v>284</v>
+      </c>
+      <c r="D132">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>1901086</v>
+      </c>
+      <c r="B133" t="s">
+        <v>70</v>
+      </c>
+      <c r="C133" t="s">
+        <v>284</v>
+      </c>
+      <c r="D133">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>1901466</v>
+      </c>
+      <c r="B134" t="s">
+        <v>176</v>
+      </c>
+      <c r="C134" t="s">
+        <v>284</v>
+      </c>
+      <c r="D134">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>1901505</v>
+      </c>
+      <c r="B135" t="s">
+        <v>71</v>
+      </c>
+      <c r="C135" t="s">
+        <v>279</v>
+      </c>
+      <c r="D135">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>1902003</v>
+      </c>
+      <c r="B136" t="s">
+        <v>72</v>
+      </c>
+      <c r="C136" t="s">
+        <v>272</v>
+      </c>
+      <c r="D136">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>1902013</v>
+      </c>
+      <c r="B137" t="s">
+        <v>20</v>
+      </c>
+      <c r="C137" t="s">
+        <v>272</v>
+      </c>
+      <c r="D137">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>1902014</v>
+      </c>
+      <c r="B138" t="s">
+        <v>73</v>
+      </c>
+      <c r="C138" t="s">
+        <v>263</v>
+      </c>
+      <c r="D138">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>2302017</v>
+      </c>
+      <c r="B139" t="s">
+        <v>158</v>
+      </c>
+      <c r="C139" t="s">
+        <v>268</v>
+      </c>
+      <c r="D139">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>2302024</v>
+      </c>
+      <c r="B140" t="s">
+        <v>52</v>
+      </c>
+      <c r="C140" t="s">
+        <v>270</v>
+      </c>
+      <c r="D140">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>2302044</v>
+      </c>
+      <c r="B141" t="s">
+        <v>53</v>
+      </c>
+      <c r="C141" t="s">
+        <v>285</v>
+      </c>
+      <c r="D141">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2302045</v>
+      </c>
+      <c r="B142" t="s">
+        <v>54</v>
+      </c>
+      <c r="C142" t="s">
+        <v>268</v>
+      </c>
+      <c r="D142">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>2302098</v>
+      </c>
+      <c r="B143" t="s">
+        <v>74</v>
+      </c>
+      <c r="C143" t="s">
+        <v>268</v>
+      </c>
+      <c r="D143">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>2302118</v>
+      </c>
+      <c r="B144" t="s">
+        <v>55</v>
+      </c>
+      <c r="C144" t="s">
+        <v>258</v>
+      </c>
+      <c r="D144">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>2302119</v>
+      </c>
+      <c r="B145" t="s">
+        <v>177</v>
+      </c>
+      <c r="C145" t="s">
+        <v>258</v>
+      </c>
+      <c r="D145">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>2304002</v>
+      </c>
+      <c r="B146" t="s">
+        <v>96</v>
+      </c>
+      <c r="C146" t="s">
+        <v>258</v>
+      </c>
+      <c r="D146">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>2304003</v>
+      </c>
+      <c r="B147" t="s">
+        <v>138</v>
+      </c>
+      <c r="C147" t="s">
+        <v>258</v>
+      </c>
+      <c r="D147">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>2304008</v>
+      </c>
+      <c r="B148" t="s">
+        <v>195</v>
+      </c>
+      <c r="C148" t="s">
+        <v>258</v>
+      </c>
+      <c r="D148">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>2304053</v>
+      </c>
+      <c r="B149" t="s">
+        <v>190</v>
+      </c>
+      <c r="C149" t="s">
+        <v>258</v>
+      </c>
+      <c r="D149">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>2304056</v>
+      </c>
+      <c r="B150" t="s">
+        <v>56</v>
+      </c>
+      <c r="C150" t="s">
+        <v>258</v>
+      </c>
+      <c r="D150">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>2505058</v>
+      </c>
+      <c r="B151" t="s">
+        <v>200</v>
+      </c>
+      <c r="C151" t="s">
+        <v>258</v>
+      </c>
+      <c r="D151">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>2505426</v>
+      </c>
+      <c r="B152" t="s">
+        <v>130</v>
+      </c>
+      <c r="C152" t="s">
+        <v>258</v>
+      </c>
+      <c r="D152">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>2508169</v>
+      </c>
+      <c r="B153" t="s">
+        <v>92</v>
+      </c>
+      <c r="C153" t="s">
+        <v>258</v>
+      </c>
+      <c r="D153">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>2508985</v>
+      </c>
+      <c r="B154" t="s">
+        <v>238</v>
+      </c>
+      <c r="C154" t="s">
+        <v>277</v>
+      </c>
+      <c r="D154">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>2508986</v>
+      </c>
+      <c r="B155" t="s">
+        <v>239</v>
+      </c>
+      <c r="C155" t="s">
+        <v>277</v>
+      </c>
+      <c r="D155">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>2508987</v>
+      </c>
+      <c r="B156" t="s">
+        <v>244</v>
+      </c>
+      <c r="C156" t="s">
+        <v>277</v>
+      </c>
+      <c r="D156">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>2508988</v>
+      </c>
+      <c r="B157" t="s">
+        <v>245</v>
+      </c>
+      <c r="C157" t="s">
+        <v>277</v>
+      </c>
+      <c r="D157">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>2508990</v>
+      </c>
+      <c r="B158" t="s">
+        <v>232</v>
+      </c>
+      <c r="C158" t="s">
+        <v>258</v>
+      </c>
+      <c r="D158">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>2508991</v>
+      </c>
+      <c r="B159" t="s">
+        <v>233</v>
+      </c>
+      <c r="C159" t="s">
+        <v>258</v>
+      </c>
+      <c r="D159">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>2508992</v>
+      </c>
+      <c r="B160" t="s">
+        <v>234</v>
+      </c>
+      <c r="C160" t="s">
+        <v>286</v>
+      </c>
+      <c r="D160">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>2508993</v>
+      </c>
+      <c r="B161" t="s">
+        <v>235</v>
+      </c>
+      <c r="C161" t="s">
+        <v>286</v>
+      </c>
+      <c r="D161">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>2508994</v>
+      </c>
+      <c r="B162" t="s">
+        <v>236</v>
+      </c>
+      <c r="C162" t="s">
+        <v>258</v>
+      </c>
+      <c r="D162">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>4212234</v>
+      </c>
+      <c r="B163" t="s">
+        <v>209</v>
+      </c>
+      <c r="C163" t="s">
+        <v>258</v>
+      </c>
+      <c r="D163">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>4212254</v>
+      </c>
+      <c r="B164" t="s">
+        <v>94</v>
+      </c>
+      <c r="C164" t="s">
+        <v>258</v>
+      </c>
+      <c r="D164">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>5309018</v>
+      </c>
+      <c r="B165" t="s">
+        <v>38</v>
+      </c>
+      <c r="C165" t="s">
+        <v>287</v>
+      </c>
+      <c r="D165">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>5314002</v>
+      </c>
+      <c r="B166" t="s">
+        <v>155</v>
+      </c>
+      <c r="C166" t="s">
+        <v>258</v>
+      </c>
+      <c r="D166">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>5316483</v>
+      </c>
+      <c r="B167" t="s">
+        <v>121</v>
+      </c>
+      <c r="C167" t="s">
+        <v>258</v>
+      </c>
+      <c r="D167">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>5316484</v>
+      </c>
+      <c r="B168" t="s">
+        <v>122</v>
+      </c>
+      <c r="C168" t="s">
+        <v>258</v>
+      </c>
+      <c r="D168">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>5316507</v>
+      </c>
+      <c r="B169" t="s">
+        <v>133</v>
+      </c>
+      <c r="C169" t="s">
+        <v>258</v>
+      </c>
+      <c r="D169">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>5316508</v>
+      </c>
+      <c r="B170" t="s">
+        <v>134</v>
+      </c>
+      <c r="C170" t="s">
+        <v>258</v>
+      </c>
+      <c r="D170">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>5316509</v>
+      </c>
+      <c r="B171" t="s">
+        <v>135</v>
+      </c>
+      <c r="C171" t="s">
+        <v>258</v>
+      </c>
+      <c r="D171">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>75</v>
+      </c>
+      <c r="B172" t="s">
+        <v>76</v>
+      </c>
+      <c r="C172" t="s">
+        <v>259</v>
+      </c>
+      <c r="D172">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>77</v>
+      </c>
+      <c r="B173" t="s">
+        <v>78</v>
+      </c>
+      <c r="C173" t="s">
+        <v>266</v>
+      </c>
+      <c r="D173">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" t="s">
+        <v>266</v>
+      </c>
+      <c r="D174">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>79</v>
+      </c>
+      <c r="B175" t="s">
+        <v>80</v>
+      </c>
+      <c r="C175" t="s">
+        <v>266</v>
+      </c>
+      <c r="D175">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>23</v>
+      </c>
+      <c r="B176" t="s">
+        <v>24</v>
+      </c>
+      <c r="C176" t="s">
+        <v>266</v>
+      </c>
+      <c r="D176">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>288</v>
+      </c>
+      <c r="B177" t="s">
+        <v>289</v>
+      </c>
+      <c r="C177" t="s">
+        <v>272</v>
+      </c>
+      <c r="D177">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>57</v>
+      </c>
+      <c r="B178" t="s">
+        <v>58</v>
+      </c>
+      <c r="C178" t="s">
+        <v>284</v>
+      </c>
+      <c r="D178">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>59</v>
+      </c>
+      <c r="B179" t="s">
+        <v>60</v>
+      </c>
+      <c r="C179" t="s">
+        <v>273</v>
+      </c>
+      <c r="D179">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>240</v>
+      </c>
+      <c r="B180" t="s">
+        <v>241</v>
+      </c>
+      <c r="C180" t="s">
+        <v>258</v>
+      </c>
+      <c r="D180">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>61</v>
+      </c>
+      <c r="B181" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C181" t="s">
+        <v>272</v>
+      </c>
+      <c r="D181">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>290</v>
+      </c>
+      <c r="B182" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C182" t="s">
+        <v>270</v>
+      </c>
+      <c r="D182">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>220</v>
+      </c>
+      <c r="B183" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C183" t="s">
+        <v>258</v>
+      </c>
+      <c r="D183">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>222</v>
+      </c>
+      <c r="B184" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C184" t="s">
+        <v>258</v>
+      </c>
+      <c r="D184">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>224</v>
+      </c>
+      <c r="B185" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C185" t="s">
+        <v>258</v>
+      </c>
+      <c r="D185">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>206</v>
+      </c>
+      <c r="B186" t="s">
+        <v>207</v>
+      </c>
+      <c r="C186" t="s">
+        <v>263</v>
+      </c>
+      <c r="D186">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="193" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="194" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="195" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="196" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="197" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="198" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="199" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="200" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="201" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="202" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="203" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="204" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="205" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="206" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="207" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="208" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="209" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="210" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="211" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="212" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="213" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="214" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="215" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="216" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="217" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="218" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="219" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="220" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="221" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="222" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="223" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="224" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="225" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="226" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="227" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="228" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="229" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="230" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="231" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="232" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="233" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="234" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="235" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="236" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="237" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="238" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="239" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="240" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="241" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="242" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="243" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="244" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="245" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="246" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="247" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="248" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="249" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="250" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="251" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="252" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="253" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="254" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="255" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="256" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="257" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="258" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="259" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="260" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="261" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="262" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="263" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="264" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="265" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="266" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="267" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="268" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="269" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="270" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="271" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="272" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="273" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="274" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="275" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="276" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="277" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="278" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="279" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="280" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="281" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="282" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="283" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="284" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="285" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="286" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="287" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="288" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="289" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="290" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="291" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="292" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="293" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="294" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="295" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="296" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="297" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="298" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="299" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="300" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="301" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="302" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="303" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="304" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="305" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="306" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="307" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="308" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="309" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="310" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="311" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="312" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="313" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="314" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="315" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="316" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="317" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="318" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="319" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="320" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="321" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="322" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="323" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="324" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="325" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="326" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="327" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="328" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="329" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="330" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="331" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="332" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="333" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="334" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="335" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="336" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="337" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="338" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="339" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="340" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="341" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="342" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="343" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="344" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="345" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="346" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="347" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="348" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="349" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="350" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="351" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="352" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="353" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="354" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="355" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="356" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="357" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="358" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="359" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="360" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="361" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="362" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="363" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="364" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="365" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="366" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="367" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="368" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="369" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="370" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="371" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="372" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="373" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="374" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="375" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="376" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="377" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="378" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="379" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="380" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="381" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="382" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="383" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="384" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="385" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="386" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="387" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="388" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="389" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="390" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="391" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="392" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="393" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="394" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="395" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="396" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="397" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="398" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="399" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="400" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="401" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="402" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="403" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="404" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="405" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="406" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="407" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="408" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="409" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="410" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="411" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="412" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="413" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="414" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="415" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="416" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="417" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="418" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="419" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="420" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="421" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="422" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="423" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="424" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="425" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="426" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="427" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="428" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="429" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="430" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="431" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="432" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="433" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="434" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="435" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="436" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="437" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="438" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="439" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="440" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="441" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="442" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="443" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="444" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="445" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="446" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="447" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="448" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="449" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="450" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="451" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="452" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="453" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="454" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="455" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="456" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="457" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="458" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="459" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="460" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="461" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="462" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="463" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="464" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="465" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="466" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="467" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="468" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="469" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="470" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="471" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="472" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="473" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="474" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="475" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="476" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="477" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="478" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="479" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="480" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="481" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="482" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="483" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="484" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="485" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="486" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="487" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="488" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="489" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="490" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="491" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="492" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="493" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="494" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="495" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="496" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="497" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="498" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="499" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="500" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="501" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="502" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="503" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="504" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="505" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="506" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="507" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="508" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="509" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="510" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="511" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="512" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="513" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="514" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="515" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="516" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="517" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="518" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="519" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="520" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="521" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="522" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="523" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="524" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="525" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="526" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="527" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="528" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="529" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="530" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="531" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="532" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="533" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="534" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="535" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="536" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="537" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="538" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="539" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="540" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="541" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="542" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="543" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="544" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="545" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="546" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="547" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="548" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="549" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="550" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="551" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="552" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="553" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="554" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="555" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="556" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="557" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="558" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="559" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="560" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="561" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="562" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="563" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="564" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="565" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="566" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="567" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="568" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="569" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="570" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="571" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="572" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="573" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="574" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="575" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="576" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="577" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="578" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="579" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="580" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="581" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="582" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="583" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="584" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="585" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="586" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="587" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="588" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="589" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="590" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="591" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="592" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="593" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="594" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="595" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="596" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="597" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="598" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="599" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="600" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="601" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="602" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="603" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="604" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="605" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="606" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="607" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="608" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="609" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="610" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="611" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/data/CUBICACION.xlsx
+++ b/data/CUBICACION.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LA CHACRA - copia\LA-CHACRA\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7E8F0B-21A4-475C-A644-2CC45BFA1CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA4FE90-D779-41B5-9D8D-0A2B37A0CC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{1B80EFAC-68E4-47D9-BD21-B7D2BF09616E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{1B80EFAC-68E4-47D9-BD21-B7D2BF09616E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="cubi" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$245</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="282">
   <si>
     <t>Tipo Partida</t>
   </si>
@@ -804,18 +807,12 @@
     <t>CANTIDAD PROMEDIO POR MODULO</t>
   </si>
   <si>
-    <t>PARTIDA</t>
-  </si>
-  <si>
     <t>DESCRIPCION</t>
   </si>
   <si>
     <t>UNIDAD</t>
   </si>
   <si>
-    <t>WIP</t>
-  </si>
-  <si>
     <t>UND</t>
   </si>
   <si>
@@ -837,9 +834,6 @@
     <t>TRA</t>
   </si>
   <si>
-    <t>CONECTOR DENTADO 2X4 (4C2)</t>
-  </si>
-  <si>
     <t>CJA</t>
   </si>
   <si>
@@ -849,9 +843,6 @@
     <t>TIN</t>
   </si>
   <si>
-    <t>PINTURA EPOXICA POLIPOX 675 GRIS COD:6757040T33</t>
-  </si>
-  <si>
     <t>GAL</t>
   </si>
   <si>
@@ -870,30 +861,12 @@
     <t xml:space="preserve">FORRO LATERAL BALCON DS49 100/100 D: 220 MM L: 3000 MM </t>
   </si>
   <si>
-    <t>KIT CERRADURA ACCESO ML/816 SS 1 MANILLA (SKU:023037)</t>
-  </si>
-  <si>
     <t>KIT</t>
   </si>
   <si>
-    <t>KIT CERRADURA ACCESO ML/816 SS 2 MANILLAS (SKU: 023037A)</t>
-  </si>
-  <si>
     <t>KG</t>
   </si>
   <si>
-    <t>LLAVE DE PASO CAMPANA 1/2 LC17 6001 FAS</t>
-  </si>
-  <si>
-    <t>MANGUITO WC DISCAPACITADO RECTO 110MM</t>
-  </si>
-  <si>
-    <t>SIFON LAVAMANOS PP 1 1/4'' CON SALIDA RECTA (19ST3082500)</t>
-  </si>
-  <si>
-    <t>MANGUITO RECTO 110MM MOD. TUBE WASSER</t>
-  </si>
-  <si>
     <t>M2</t>
   </si>
   <si>
@@ -906,16 +879,16 @@
     <t>MTS</t>
   </si>
   <si>
-    <t>080460X</t>
-  </si>
-  <si>
-    <t>MONOFILAMENTO POLYFLOR GRIS COD:3700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINTURA </t>
-  </si>
-  <si>
     <t>UNIDAD DE MEDIDA</t>
+  </si>
+  <si>
+    <t>PROMEDIO MR</t>
+  </si>
+  <si>
+    <t>PROMEDIO GP</t>
+  </si>
+  <si>
+    <t>CODIGO</t>
   </si>
 </sst>
 </file>
@@ -957,7 +930,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -971,13 +951,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3A700C6-F0CA-453A-A934-AFDA491A5CB1}" name="Tabla1" displayName="Tabla1" ref="A1:D186" totalsRowShown="0">
-  <autoFilter ref="A1:D186" xr:uid="{D3A700C6-F0CA-453A-A934-AFDA491A5CB1}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6134504D-9BD9-4C70-9A21-B337EE2112D7}" name="PARTIDA"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3A700C6-F0CA-453A-A934-AFDA491A5CB1}" name="Tabla1" displayName="Tabla1" ref="A1:E175" totalsRowShown="0">
+  <autoFilter ref="A1:E175" xr:uid="{D3A700C6-F0CA-453A-A934-AFDA491A5CB1}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{6134504D-9BD9-4C70-9A21-B337EE2112D7}" name="CODIGO"/>
     <tableColumn id="2" xr3:uid="{D28348E6-170F-4D48-9AC0-3764BF4B6EB5}" name="DESCRIPCION"/>
     <tableColumn id="3" xr3:uid="{1D0FE055-EB2D-4BC0-8BD9-79C05C9FF1D9}" name="UNIDAD"/>
-    <tableColumn id="4" xr3:uid="{D42DF3AE-8420-4822-99D0-442B0F49F38D}" name="WIP"/>
+    <tableColumn id="6" xr3:uid="{E777B60C-DF6A-4E27-9D80-E2BE1B6C66ED}" name="PROMEDIO MR" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{FAC807FB-B74B-4868-92E6-78AD02F4AC0F}" name="PROMEDIO GP" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1326,7 +1307,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="G1" t="s">
         <v>252</v>
@@ -1352,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="str">
-        <f>+_xlfn.XLOOKUP(D2,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D2,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G2">
@@ -1370,7 +1351,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="str">
-        <f>+_xlfn.XLOOKUP(D3,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D3,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G3">
@@ -1388,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="str">
-        <f>+_xlfn.XLOOKUP(D4,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D4,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G4">
@@ -1409,7 +1390,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="str">
-        <f>+_xlfn.XLOOKUP(D5,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D5,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G5">
@@ -1427,7 +1408,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="str">
-        <f>+_xlfn.XLOOKUP(D6,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D6,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G6">
@@ -1445,7 +1426,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="str">
-        <f>+_xlfn.XLOOKUP(D7,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D7,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G7">
@@ -1463,7 +1444,7 @@
         <v>15</v>
       </c>
       <c r="F8" t="str">
-        <f>+_xlfn.XLOOKUP(D8,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D8,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G8">
@@ -1481,7 +1462,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="str">
-        <f>+_xlfn.XLOOKUP(D9,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D9,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G9">
@@ -1499,7 +1480,7 @@
         <v>17</v>
       </c>
       <c r="F10" t="str">
-        <f>+_xlfn.XLOOKUP(D10,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D10,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G10">
@@ -1517,7 +1498,7 @@
         <v>18</v>
       </c>
       <c r="F11" t="str">
-        <f>+_xlfn.XLOOKUP(D11,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D11,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G11">
@@ -1535,7 +1516,7 @@
         <v>19</v>
       </c>
       <c r="F12" t="str">
-        <f>+_xlfn.XLOOKUP(D12,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D12,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G12">
@@ -1553,7 +1534,7 @@
         <v>20</v>
       </c>
       <c r="F13" t="str">
-        <f>+_xlfn.XLOOKUP(D13,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D13,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G13">
@@ -1571,7 +1552,7 @@
         <v>22</v>
       </c>
       <c r="F14" t="str">
-        <f>+_xlfn.XLOOKUP(D14,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D14,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G14">
@@ -1589,7 +1570,7 @@
         <v>24</v>
       </c>
       <c r="F15" t="str">
-        <f>+_xlfn.XLOOKUP(D15,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D15,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G15">
@@ -1613,7 +1594,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="str">
-        <f>+_xlfn.XLOOKUP(D16,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D16,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G16">
@@ -1631,7 +1612,7 @@
         <v>27</v>
       </c>
       <c r="F17" t="str">
-        <f>+_xlfn.XLOOKUP(D17,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D17,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G17">
@@ -1649,7 +1630,7 @@
         <v>28</v>
       </c>
       <c r="F18" t="str">
-        <f>+_xlfn.XLOOKUP(D18,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D18,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G18">
@@ -1670,7 +1651,7 @@
         <v>12</v>
       </c>
       <c r="F19" t="str">
-        <f>+_xlfn.XLOOKUP(D19,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D19,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G19">
@@ -1688,7 +1669,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="str">
-        <f>+_xlfn.XLOOKUP(D20,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D20,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G20">
@@ -1706,7 +1687,7 @@
         <v>31</v>
       </c>
       <c r="F21" t="str">
-        <f>+_xlfn.XLOOKUP(D21,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D21,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G21">
@@ -1724,7 +1705,7 @@
         <v>32</v>
       </c>
       <c r="F22" t="str">
-        <f>+_xlfn.XLOOKUP(D22,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D22,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G22">
@@ -1742,7 +1723,7 @@
         <v>14</v>
       </c>
       <c r="F23" t="str">
-        <f>+_xlfn.XLOOKUP(D23,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D23,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G23">
@@ -1760,7 +1741,7 @@
         <v>15</v>
       </c>
       <c r="F24" t="str">
-        <f>+_xlfn.XLOOKUP(D24,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D24,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G24">
@@ -1778,7 +1759,7 @@
         <v>33</v>
       </c>
       <c r="F25" t="str">
-        <f>+_xlfn.XLOOKUP(D25,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D25,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G25">
@@ -1796,7 +1777,7 @@
         <v>34</v>
       </c>
       <c r="F26" t="str">
-        <f>+_xlfn.XLOOKUP(D26,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D26,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G26">
@@ -1814,7 +1795,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="str">
-        <f>+_xlfn.XLOOKUP(D27,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D27,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G27">
@@ -1832,7 +1813,7 @@
         <v>35</v>
       </c>
       <c r="F28" t="str">
-        <f>+_xlfn.XLOOKUP(D28,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D28,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G28">
@@ -1850,7 +1831,7 @@
         <v>36</v>
       </c>
       <c r="F29" t="str">
-        <f>+_xlfn.XLOOKUP(D29,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D29,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G29">
@@ -1868,7 +1849,7 @@
         <v>37</v>
       </c>
       <c r="F30" t="str">
-        <f>+_xlfn.XLOOKUP(D30,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D30,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G30">
@@ -1886,7 +1867,7 @@
         <v>20</v>
       </c>
       <c r="F31" t="str">
-        <f>+_xlfn.XLOOKUP(D31,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D31,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G31">
@@ -1904,7 +1885,7 @@
         <v>38</v>
       </c>
       <c r="F32" t="str">
-        <f>+_xlfn.XLOOKUP(D32,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D32,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>MTS</v>
       </c>
       <c r="G32">
@@ -1922,7 +1903,7 @@
         <v>22</v>
       </c>
       <c r="F33" t="str">
-        <f>+_xlfn.XLOOKUP(D33,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D33,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G33">
@@ -1940,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="F34" t="str">
-        <f>+_xlfn.XLOOKUP(D34,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D34,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G34">
@@ -1961,7 +1942,7 @@
         <v>12</v>
       </c>
       <c r="F35" t="str">
-        <f>+_xlfn.XLOOKUP(D35,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D35,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G35">
@@ -1979,7 +1960,7 @@
         <v>30</v>
       </c>
       <c r="F36" t="str">
-        <f>+_xlfn.XLOOKUP(D36,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D36,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G36">
@@ -1997,7 +1978,7 @@
         <v>32</v>
       </c>
       <c r="F37" t="str">
-        <f>+_xlfn.XLOOKUP(D37,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D37,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G37">
@@ -2015,7 +1996,7 @@
         <v>40</v>
       </c>
       <c r="F38" t="str">
-        <f>+_xlfn.XLOOKUP(D38,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D38,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G38">
@@ -2033,7 +2014,7 @@
         <v>14</v>
       </c>
       <c r="F39" t="str">
-        <f>+_xlfn.XLOOKUP(D39,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D39,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G39">
@@ -2051,7 +2032,7 @@
         <v>15</v>
       </c>
       <c r="F40" t="str">
-        <f>+_xlfn.XLOOKUP(D40,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D40,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G40">
@@ -2069,7 +2050,7 @@
         <v>33</v>
       </c>
       <c r="F41" t="str">
-        <f>+_xlfn.XLOOKUP(D41,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D41,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G41">
@@ -2087,7 +2068,7 @@
         <v>34</v>
       </c>
       <c r="F42" t="str">
-        <f>+_xlfn.XLOOKUP(D42,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D42,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G42">
@@ -2105,7 +2086,7 @@
         <v>17</v>
       </c>
       <c r="F43" t="str">
-        <f>+_xlfn.XLOOKUP(D43,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D43,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G43">
@@ -2123,7 +2104,7 @@
         <v>35</v>
       </c>
       <c r="F44" t="str">
-        <f>+_xlfn.XLOOKUP(D44,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D44,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G44">
@@ -2141,7 +2122,7 @@
         <v>36</v>
       </c>
       <c r="F45" t="str">
-        <f>+_xlfn.XLOOKUP(D45,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D45,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G45">
@@ -2159,7 +2140,7 @@
         <v>37</v>
       </c>
       <c r="F46" t="str">
-        <f>+_xlfn.XLOOKUP(D46,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D46,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G46">
@@ -2177,7 +2158,7 @@
         <v>20</v>
       </c>
       <c r="F47" t="str">
-        <f>+_xlfn.XLOOKUP(D47,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D47,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G47">
@@ -2195,7 +2176,7 @@
         <v>38</v>
       </c>
       <c r="F48" t="str">
-        <f>+_xlfn.XLOOKUP(D48,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D48,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>MTS</v>
       </c>
       <c r="G48">
@@ -2213,7 +2194,7 @@
         <v>22</v>
       </c>
       <c r="F49" t="str">
-        <f>+_xlfn.XLOOKUP(D49,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D49,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G49">
@@ -2231,7 +2212,7 @@
         <v>24</v>
       </c>
       <c r="F50" t="str">
-        <f>+_xlfn.XLOOKUP(D50,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D50,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G50">
@@ -2252,7 +2233,7 @@
         <v>12</v>
       </c>
       <c r="F51" t="str">
-        <f>+_xlfn.XLOOKUP(D51,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D51,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G51">
@@ -2270,7 +2251,7 @@
         <v>30</v>
       </c>
       <c r="F52" t="str">
-        <f>+_xlfn.XLOOKUP(D52,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D52,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G52">
@@ -2288,7 +2269,7 @@
         <v>42</v>
       </c>
       <c r="F53" t="str">
-        <f>+_xlfn.XLOOKUP(D53,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D53,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G53">
@@ -2306,7 +2287,7 @@
         <v>40</v>
       </c>
       <c r="F54" t="str">
-        <f>+_xlfn.XLOOKUP(D54,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D54,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G54">
@@ -2324,7 +2305,7 @@
         <v>14</v>
       </c>
       <c r="F55" t="str">
-        <f>+_xlfn.XLOOKUP(D55,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D55,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G55">
@@ -2342,7 +2323,7 @@
         <v>15</v>
       </c>
       <c r="F56" t="str">
-        <f>+_xlfn.XLOOKUP(D56,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D56,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G56">
@@ -2360,7 +2341,7 @@
         <v>33</v>
       </c>
       <c r="F57" t="str">
-        <f>+_xlfn.XLOOKUP(D57,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D57,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G57">
@@ -2378,7 +2359,7 @@
         <v>17</v>
       </c>
       <c r="F58" t="str">
-        <f>+_xlfn.XLOOKUP(D58,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D58,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G58">
@@ -2396,7 +2377,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="str">
-        <f>+_xlfn.XLOOKUP(D59,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D59,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G59">
@@ -2414,7 +2395,7 @@
         <v>36</v>
       </c>
       <c r="F60" t="str">
-        <f>+_xlfn.XLOOKUP(D60,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D60,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G60">
@@ -2432,7 +2413,7 @@
         <v>37</v>
       </c>
       <c r="F61" t="str">
-        <f>+_xlfn.XLOOKUP(D61,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D61,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G61">
@@ -2450,7 +2431,7 @@
         <v>20</v>
       </c>
       <c r="F62" t="str">
-        <f>+_xlfn.XLOOKUP(D62,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D62,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G62">
@@ -2468,7 +2449,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="str">
-        <f>+_xlfn.XLOOKUP(D63,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D63,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>MTS</v>
       </c>
       <c r="G63">
@@ -2486,7 +2467,7 @@
         <v>22</v>
       </c>
       <c r="F64" t="str">
-        <f>+_xlfn.XLOOKUP(D64,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D64,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G64">
@@ -2504,7 +2485,7 @@
         <v>24</v>
       </c>
       <c r="F65" t="str">
-        <f>+_xlfn.XLOOKUP(D65,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D65,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G65">
@@ -2525,7 +2506,7 @@
         <v>12</v>
       </c>
       <c r="F66" t="str">
-        <f>+_xlfn.XLOOKUP(D66,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D66,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G66">
@@ -2543,7 +2524,7 @@
         <v>30</v>
       </c>
       <c r="F67" t="str">
-        <f>+_xlfn.XLOOKUP(D67,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D67,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G67">
@@ -2561,7 +2542,7 @@
         <v>44</v>
       </c>
       <c r="F68" t="str">
-        <f>+_xlfn.XLOOKUP(D68,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D68,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G68">
@@ -2579,7 +2560,7 @@
         <v>15</v>
       </c>
       <c r="F69" t="str">
-        <f>+_xlfn.XLOOKUP(D69,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D69,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G69">
@@ -2597,7 +2578,7 @@
         <v>45</v>
       </c>
       <c r="F70" t="str">
-        <f>+_xlfn.XLOOKUP(D70,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D70,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G70">
@@ -2615,7 +2596,7 @@
         <v>46</v>
       </c>
       <c r="F71" t="str">
-        <f>+_xlfn.XLOOKUP(D71,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D71,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G71">
@@ -2639,7 +2620,7 @@
         <v>49</v>
       </c>
       <c r="F72" t="str">
-        <f>+_xlfn.XLOOKUP(D72,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D72,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G72">
@@ -2657,7 +2638,7 @@
         <v>50</v>
       </c>
       <c r="F73" t="str">
-        <f>+_xlfn.XLOOKUP(D73,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D73,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G73">
@@ -2675,7 +2656,7 @@
         <v>51</v>
       </c>
       <c r="F74" t="str">
-        <f>+_xlfn.XLOOKUP(D74,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D74,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TRA</v>
       </c>
       <c r="G74">
@@ -2693,7 +2674,7 @@
         <v>52</v>
       </c>
       <c r="F75" t="str">
-        <f>+_xlfn.XLOOKUP(D75,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D75,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>GAL</v>
       </c>
       <c r="G75">
@@ -2711,7 +2692,7 @@
         <v>53</v>
       </c>
       <c r="F76" t="str">
-        <f>+_xlfn.XLOOKUP(D76,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D76,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>SAC</v>
       </c>
       <c r="G76">
@@ -2729,7 +2710,7 @@
         <v>54</v>
       </c>
       <c r="F77" t="str">
-        <f>+_xlfn.XLOOKUP(D77,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D77,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G77">
@@ -2747,7 +2728,7 @@
         <v>55</v>
       </c>
       <c r="F78" t="str">
-        <f>+_xlfn.XLOOKUP(D78,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D78,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G78">
@@ -2765,7 +2746,7 @@
         <v>56</v>
       </c>
       <c r="F79" t="str">
-        <f>+_xlfn.XLOOKUP(D79,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D79,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G79">
@@ -2783,7 +2764,7 @@
         <v>58</v>
       </c>
       <c r="F80" t="str">
-        <f>+_xlfn.XLOOKUP(D80,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D80,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G80">
@@ -2801,7 +2782,7 @@
         <v>60</v>
       </c>
       <c r="F81" t="str">
-        <f>+_xlfn.XLOOKUP(D81,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D81,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>ML</v>
       </c>
       <c r="G81">
@@ -2819,7 +2800,7 @@
         <v>62</v>
       </c>
       <c r="F82" t="str">
-        <f>+_xlfn.XLOOKUP(D82,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D82,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G82">
@@ -2840,7 +2821,7 @@
         <v>12</v>
       </c>
       <c r="F83" t="str">
-        <f>+_xlfn.XLOOKUP(D83,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D83,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G83">
@@ -2858,7 +2839,7 @@
         <v>30</v>
       </c>
       <c r="F84" t="str">
-        <f>+_xlfn.XLOOKUP(D84,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D84,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G84">
@@ -2876,7 +2857,7 @@
         <v>64</v>
       </c>
       <c r="F85" t="str">
-        <f>+_xlfn.XLOOKUP(D85,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D85,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G85">
@@ -2894,7 +2875,7 @@
         <v>65</v>
       </c>
       <c r="F86" t="str">
-        <f>+_xlfn.XLOOKUP(D86,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D86,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G86">
@@ -2912,7 +2893,7 @@
         <v>31</v>
       </c>
       <c r="F87" t="str">
-        <f>+_xlfn.XLOOKUP(D87,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D87,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G87">
@@ -2930,7 +2911,7 @@
         <v>32</v>
       </c>
       <c r="F88" t="str">
-        <f>+_xlfn.XLOOKUP(D88,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D88,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G88">
@@ -2948,7 +2929,7 @@
         <v>66</v>
       </c>
       <c r="F89" t="str">
-        <f>+_xlfn.XLOOKUP(D89,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D89,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G89">
@@ -2966,7 +2947,7 @@
         <v>33</v>
       </c>
       <c r="F90" t="str">
-        <f>+_xlfn.XLOOKUP(D90,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D90,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G90">
@@ -2984,7 +2965,7 @@
         <v>67</v>
       </c>
       <c r="F91" t="str">
-        <f>+_xlfn.XLOOKUP(D91,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D91,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G91">
@@ -3002,7 +2983,7 @@
         <v>68</v>
       </c>
       <c r="F92" t="str">
-        <f>+_xlfn.XLOOKUP(D92,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D92,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G92">
@@ -3020,7 +3001,7 @@
         <v>17</v>
       </c>
       <c r="F93" t="str">
-        <f>+_xlfn.XLOOKUP(D93,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D93,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G93">
@@ -3038,7 +3019,7 @@
         <v>69</v>
       </c>
       <c r="F94" t="str">
-        <f>+_xlfn.XLOOKUP(D94,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D94,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G94">
@@ -3056,7 +3037,7 @@
         <v>70</v>
       </c>
       <c r="F95" t="str">
-        <f>+_xlfn.XLOOKUP(D95,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D95,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G95">
@@ -3074,7 +3055,7 @@
         <v>71</v>
       </c>
       <c r="F96" t="str">
-        <f>+_xlfn.XLOOKUP(D96,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D96,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KG</v>
       </c>
       <c r="G96">
@@ -3092,7 +3073,7 @@
         <v>72</v>
       </c>
       <c r="F97" t="str">
-        <f>+_xlfn.XLOOKUP(D97,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D97,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G97">
@@ -3110,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="F98" t="str">
-        <f>+_xlfn.XLOOKUP(D98,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D98,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G98">
@@ -3128,7 +3109,7 @@
         <v>73</v>
       </c>
       <c r="F99" t="str">
-        <f>+_xlfn.XLOOKUP(D99,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D99,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G99">
@@ -3146,7 +3127,7 @@
         <v>74</v>
       </c>
       <c r="F100" t="str">
-        <f>+_xlfn.XLOOKUP(D100,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D100,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G100">
@@ -3164,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="F101" t="str">
-        <f>+_xlfn.XLOOKUP(D101,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D101,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>MTS</v>
       </c>
       <c r="G101">
@@ -3182,7 +3163,7 @@
         <v>76</v>
       </c>
       <c r="F102" t="str">
-        <f>+_xlfn.XLOOKUP(D102,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D102,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PZA</v>
       </c>
       <c r="G102">
@@ -3200,7 +3181,7 @@
         <v>78</v>
       </c>
       <c r="F103" t="str">
-        <f>+_xlfn.XLOOKUP(D103,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D103,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G103">
@@ -3218,7 +3199,7 @@
         <v>80</v>
       </c>
       <c r="F104" t="str">
-        <f>+_xlfn.XLOOKUP(D104,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D104,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G104">
@@ -3236,7 +3217,7 @@
         <v>24</v>
       </c>
       <c r="F105" t="str">
-        <f>+_xlfn.XLOOKUP(D105,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D105,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G105">
@@ -3260,7 +3241,7 @@
         <v>31</v>
       </c>
       <c r="F106" t="str">
-        <f>+_xlfn.XLOOKUP(D106,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D106,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G106">
@@ -3278,7 +3259,7 @@
         <v>82</v>
       </c>
       <c r="F107" t="str">
-        <f>+_xlfn.XLOOKUP(D107,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D107,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G107">
@@ -3296,7 +3277,7 @@
         <v>83</v>
       </c>
       <c r="F108" t="str">
-        <f>+_xlfn.XLOOKUP(D108,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D108,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G108">
@@ -3314,7 +3295,7 @@
         <v>84</v>
       </c>
       <c r="F109" t="str">
-        <f>+_xlfn.XLOOKUP(D109,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D109,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G109">
@@ -3332,7 +3313,7 @@
         <v>85</v>
       </c>
       <c r="F110" t="str">
-        <f>+_xlfn.XLOOKUP(D110,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D110,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G110">
@@ -3350,7 +3331,7 @@
         <v>86</v>
       </c>
       <c r="F111" t="str">
-        <f>+_xlfn.XLOOKUP(D111,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D111,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G111">
@@ -3368,7 +3349,7 @@
         <v>87</v>
       </c>
       <c r="F112" t="str">
-        <f>+_xlfn.XLOOKUP(D112,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D112,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G112">
@@ -3386,7 +3367,7 @@
         <v>73</v>
       </c>
       <c r="F113" t="str">
-        <f>+_xlfn.XLOOKUP(D113,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D113,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G113">
@@ -3413,7 +3394,7 @@
         <v>91</v>
       </c>
       <c r="F114" t="str">
-        <f>+_xlfn.XLOOKUP(D114,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D114,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G114">
@@ -3431,7 +3412,7 @@
         <v>92</v>
       </c>
       <c r="F115" t="str">
-        <f>+_xlfn.XLOOKUP(D115,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D115,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G115">
@@ -3452,7 +3433,7 @@
         <v>94</v>
       </c>
       <c r="F116" t="str">
-        <f>+_xlfn.XLOOKUP(D116,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D116,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G116">
@@ -3473,7 +3454,7 @@
         <v>96</v>
       </c>
       <c r="F117" t="str">
-        <f>+_xlfn.XLOOKUP(D117,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D117,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G117">
@@ -3497,7 +3478,7 @@
         <v>99</v>
       </c>
       <c r="F118" t="str">
-        <f>+_xlfn.XLOOKUP(D118,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D118,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G118">
@@ -3515,7 +3496,7 @@
         <v>100</v>
       </c>
       <c r="F119" t="str">
-        <f>+_xlfn.XLOOKUP(D119,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D119,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G119">
@@ -3533,7 +3514,7 @@
         <v>101</v>
       </c>
       <c r="F120" t="str">
-        <f>+_xlfn.XLOOKUP(D120,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D120,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G120">
@@ -3551,7 +3532,7 @@
         <v>102</v>
       </c>
       <c r="F121" t="str">
-        <f>+_xlfn.XLOOKUP(D121,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D121,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G121">
@@ -3569,7 +3550,7 @@
         <v>103</v>
       </c>
       <c r="F122" t="str">
-        <f>+_xlfn.XLOOKUP(D122,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D122,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G122">
@@ -3587,7 +3568,7 @@
         <v>104</v>
       </c>
       <c r="F123" t="str">
-        <f>+_xlfn.XLOOKUP(D123,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D123,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G123">
@@ -3605,7 +3586,7 @@
         <v>105</v>
       </c>
       <c r="F124" t="str">
-        <f>+_xlfn.XLOOKUP(D124,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D124,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G124">
@@ -3623,7 +3604,7 @@
         <v>106</v>
       </c>
       <c r="F125" t="str">
-        <f>+_xlfn.XLOOKUP(D125,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D125,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G125">
@@ -3641,7 +3622,7 @@
         <v>107</v>
       </c>
       <c r="F126" t="str">
-        <f>+_xlfn.XLOOKUP(D126,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D126,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G126">
@@ -3659,7 +3640,7 @@
         <v>108</v>
       </c>
       <c r="F127" t="str">
-        <f>+_xlfn.XLOOKUP(D127,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D127,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G127">
@@ -3683,7 +3664,7 @@
         <v>111</v>
       </c>
       <c r="F128" t="str">
-        <f>+_xlfn.XLOOKUP(D128,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D128,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G128">
@@ -3701,7 +3682,7 @@
         <v>112</v>
       </c>
       <c r="F129" t="str">
-        <f>+_xlfn.XLOOKUP(D129,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D129,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G129">
@@ -3719,7 +3700,7 @@
         <v>113</v>
       </c>
       <c r="F130" t="str">
-        <f>+_xlfn.XLOOKUP(D130,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D130,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G130">
@@ -3737,7 +3718,7 @@
         <v>114</v>
       </c>
       <c r="F131" t="str">
-        <f>+_xlfn.XLOOKUP(D131,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D131,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G131">
@@ -3755,7 +3736,7 @@
         <v>115</v>
       </c>
       <c r="F132" t="str">
-        <f>+_xlfn.XLOOKUP(D132,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D132,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G132">
@@ -3776,7 +3757,7 @@
         <v>117</v>
       </c>
       <c r="F133" t="str">
-        <f>+_xlfn.XLOOKUP(D133,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D133,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G133">
@@ -3800,7 +3781,7 @@
         <v>119</v>
       </c>
       <c r="F134" t="str">
-        <f>+_xlfn.XLOOKUP(D134,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D134,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G134">
@@ -3818,7 +3799,7 @@
         <v>120</v>
       </c>
       <c r="F135" t="str">
-        <f>+_xlfn.XLOOKUP(D135,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D135,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G135">
@@ -3839,7 +3820,7 @@
         <v>121</v>
       </c>
       <c r="F136" t="str">
-        <f>+_xlfn.XLOOKUP(D136,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D136,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G136">
@@ -3857,7 +3838,7 @@
         <v>122</v>
       </c>
       <c r="F137" t="str">
-        <f>+_xlfn.XLOOKUP(D137,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D137,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G137">
@@ -3881,7 +3862,7 @@
         <v>124</v>
       </c>
       <c r="F138" t="str">
-        <f>+_xlfn.XLOOKUP(D138,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D138,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G138">
@@ -3899,7 +3880,7 @@
         <v>125</v>
       </c>
       <c r="F139" t="str">
-        <f>+_xlfn.XLOOKUP(D139,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D139,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G139">
@@ -3917,7 +3898,7 @@
         <v>126</v>
       </c>
       <c r="F140" t="str">
-        <f>+_xlfn.XLOOKUP(D140,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D140,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G140">
@@ -3938,7 +3919,7 @@
         <v>127</v>
       </c>
       <c r="F141" t="str">
-        <f>+_xlfn.XLOOKUP(D141,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D141,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G141">
@@ -3956,7 +3937,7 @@
         <v>128</v>
       </c>
       <c r="F142" t="str">
-        <f>+_xlfn.XLOOKUP(D142,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D142,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G142">
@@ -3974,7 +3955,7 @@
         <v>129</v>
       </c>
       <c r="F143" t="str">
-        <f>+_xlfn.XLOOKUP(D143,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D143,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G143">
@@ -3992,7 +3973,7 @@
         <v>130</v>
       </c>
       <c r="F144" t="str">
-        <f>+_xlfn.XLOOKUP(D144,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D144,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G144">
@@ -4016,7 +3997,7 @@
         <v>133</v>
       </c>
       <c r="F145" t="str">
-        <f>+_xlfn.XLOOKUP(D145,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D145,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G145">
@@ -4034,7 +4015,7 @@
         <v>134</v>
       </c>
       <c r="F146" t="str">
-        <f>+_xlfn.XLOOKUP(D146,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D146,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G146">
@@ -4052,7 +4033,7 @@
         <v>135</v>
       </c>
       <c r="F147" t="str">
-        <f>+_xlfn.XLOOKUP(D147,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D147,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G147">
@@ -4073,7 +4054,7 @@
         <v>136</v>
       </c>
       <c r="F148" t="str">
-        <f>+_xlfn.XLOOKUP(D148,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D148,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G148">
@@ -4091,7 +4072,7 @@
         <v>137</v>
       </c>
       <c r="F149" t="str">
-        <f>+_xlfn.XLOOKUP(D149,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D149,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G149">
@@ -4112,7 +4093,7 @@
         <v>138</v>
       </c>
       <c r="F150" t="str">
-        <f>+_xlfn.XLOOKUP(D150,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D150,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G150">
@@ -4136,7 +4117,7 @@
         <v>140</v>
       </c>
       <c r="F151" t="str">
-        <f>+_xlfn.XLOOKUP(D151,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D151,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G151">
@@ -4154,7 +4135,7 @@
         <v>141</v>
       </c>
       <c r="F152" t="str">
-        <f>+_xlfn.XLOOKUP(D152,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D152,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G152">
@@ -4172,7 +4153,7 @@
         <v>142</v>
       </c>
       <c r="F153" t="str">
-        <f>+_xlfn.XLOOKUP(D153,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D153,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G153">
@@ -4190,7 +4171,7 @@
         <v>143</v>
       </c>
       <c r="F154" t="str">
-        <f>+_xlfn.XLOOKUP(D154,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D154,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G154">
@@ -4208,7 +4189,7 @@
         <v>144</v>
       </c>
       <c r="F155" t="str">
-        <f>+_xlfn.XLOOKUP(D155,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D155,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G155">
@@ -4235,7 +4216,7 @@
         <v>42</v>
       </c>
       <c r="F156" t="str">
-        <f>+_xlfn.XLOOKUP(D156,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D156,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G156">
@@ -4253,7 +4234,7 @@
         <v>15</v>
       </c>
       <c r="F157" t="str">
-        <f>+_xlfn.XLOOKUP(D157,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D157,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G157">
@@ -4271,7 +4252,7 @@
         <v>36</v>
       </c>
       <c r="F158" t="str">
-        <f>+_xlfn.XLOOKUP(D158,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D158,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G158">
@@ -4289,7 +4270,7 @@
         <v>22</v>
       </c>
       <c r="F159" t="str">
-        <f>+_xlfn.XLOOKUP(D159,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D159,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>CJA</v>
       </c>
       <c r="G159">
@@ -4313,7 +4294,7 @@
         <v>150</v>
       </c>
       <c r="F160" t="str">
-        <f>+_xlfn.XLOOKUP(D160,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D160,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G160">
@@ -4331,7 +4312,7 @@
         <v>151</v>
       </c>
       <c r="F161" t="str">
-        <f>+_xlfn.XLOOKUP(D161,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D161,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G161">
@@ -4349,7 +4330,7 @@
         <v>152</v>
       </c>
       <c r="F162" t="str">
-        <f>+_xlfn.XLOOKUP(D162,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D162,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>LTS</v>
       </c>
       <c r="G162">
@@ -4367,7 +4348,7 @@
         <v>153</v>
       </c>
       <c r="F163" t="str">
-        <f>+_xlfn.XLOOKUP(D163,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D163,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KG</v>
       </c>
       <c r="G163">
@@ -4385,7 +4366,7 @@
         <v>154</v>
       </c>
       <c r="F164" t="str">
-        <f>+_xlfn.XLOOKUP(D164,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D164,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KG</v>
       </c>
       <c r="G164">
@@ -4403,7 +4384,7 @@
         <v>155</v>
       </c>
       <c r="F165" t="str">
-        <f>+_xlfn.XLOOKUP(D165,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D165,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G165">
@@ -4427,7 +4408,7 @@
         <v>157</v>
       </c>
       <c r="F166" t="str">
-        <f>+_xlfn.XLOOKUP(D166,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D166,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G166">
@@ -4445,7 +4426,7 @@
         <v>158</v>
       </c>
       <c r="F167" t="str">
-        <f>+_xlfn.XLOOKUP(D167,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D167,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G167">
@@ -4469,7 +4450,7 @@
         <v>161</v>
       </c>
       <c r="F168" t="str">
-        <f>+_xlfn.XLOOKUP(D168,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D168,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TRA</v>
       </c>
       <c r="G168">
@@ -4487,7 +4468,7 @@
         <v>162</v>
       </c>
       <c r="F169" t="str">
-        <f>+_xlfn.XLOOKUP(D169,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D169,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TRA</v>
       </c>
       <c r="G169">
@@ -4508,7 +4489,7 @@
         <v>164</v>
       </c>
       <c r="F170" t="str">
-        <f>+_xlfn.XLOOKUP(D170,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D170,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G170">
@@ -4526,7 +4507,7 @@
         <v>165</v>
       </c>
       <c r="F171">
-        <f>+_xlfn.XLOOKUP(D171,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D171,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>0</v>
       </c>
       <c r="G171">
@@ -4544,7 +4525,7 @@
         <v>166</v>
       </c>
       <c r="F172">
-        <f>+_xlfn.XLOOKUP(D172,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D172,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>0</v>
       </c>
       <c r="G172">
@@ -4565,7 +4546,7 @@
         <v>168</v>
       </c>
       <c r="F173" t="str">
-        <f>+_xlfn.XLOOKUP(D173,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D173,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G173">
@@ -4583,7 +4564,7 @@
         <v>169</v>
       </c>
       <c r="F174">
-        <f>+_xlfn.XLOOKUP(D174,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D174,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>0</v>
       </c>
       <c r="G174">
@@ -4601,7 +4582,7 @@
         <v>170</v>
       </c>
       <c r="F175">
-        <f>+_xlfn.XLOOKUP(D175,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D175,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>0</v>
       </c>
       <c r="G175">
@@ -4622,7 +4603,7 @@
         <v>172</v>
       </c>
       <c r="F176" t="str">
-        <f>+_xlfn.XLOOKUP(D176,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D176,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G176">
@@ -4646,7 +4627,7 @@
         <v>69</v>
       </c>
       <c r="F177" t="str">
-        <f>+_xlfn.XLOOKUP(D177,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D177,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G177">
@@ -4664,7 +4645,7 @@
         <v>175</v>
       </c>
       <c r="F178" t="str">
-        <f>+_xlfn.XLOOKUP(D178,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D178,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G178">
@@ -4682,7 +4663,7 @@
         <v>70</v>
       </c>
       <c r="F179" t="str">
-        <f>+_xlfn.XLOOKUP(D179,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D179,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G179">
@@ -4700,7 +4681,7 @@
         <v>176</v>
       </c>
       <c r="F180" t="str">
-        <f>+_xlfn.XLOOKUP(D180,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D180,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>M2</v>
       </c>
       <c r="G180">
@@ -4721,7 +4702,7 @@
         <v>32</v>
       </c>
       <c r="F181" t="str">
-        <f>+_xlfn.XLOOKUP(D181,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D181,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G181">
@@ -4739,7 +4720,7 @@
         <v>177</v>
       </c>
       <c r="F182" t="str">
-        <f>+_xlfn.XLOOKUP(D182,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D182,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G182">
@@ -4763,7 +4744,7 @@
         <v>180</v>
       </c>
       <c r="F183" t="str">
-        <f>+_xlfn.XLOOKUP(D183,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D183,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G183">
@@ -4781,7 +4762,7 @@
         <v>181</v>
       </c>
       <c r="F184">
-        <f>+_xlfn.XLOOKUP(D184,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D184,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>0</v>
       </c>
       <c r="G184">
@@ -4805,7 +4786,7 @@
         <v>184</v>
       </c>
       <c r="F185" t="str">
-        <f>+_xlfn.XLOOKUP(D185,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D185,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G185">
@@ -4823,7 +4804,7 @@
         <v>185</v>
       </c>
       <c r="F186" t="str">
-        <f>+_xlfn.XLOOKUP(D186,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D186,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G186">
@@ -4841,7 +4822,7 @@
         <v>186</v>
       </c>
       <c r="F187" t="str">
-        <f>+_xlfn.XLOOKUP(D187,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D187,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G187">
@@ -4859,7 +4840,7 @@
         <v>187</v>
       </c>
       <c r="F188" t="str">
-        <f>+_xlfn.XLOOKUP(D188,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D188,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G188">
@@ -4877,7 +4858,7 @@
         <v>188</v>
       </c>
       <c r="F189" t="str">
-        <f>+_xlfn.XLOOKUP(D189,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D189,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G189">
@@ -4895,7 +4876,7 @@
         <v>50</v>
       </c>
       <c r="F190" t="str">
-        <f>+_xlfn.XLOOKUP(D190,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D190,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G190">
@@ -4913,7 +4894,7 @@
         <v>189</v>
       </c>
       <c r="F191" t="str">
-        <f>+_xlfn.XLOOKUP(D191,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D191,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G191">
@@ -4931,7 +4912,7 @@
         <v>190</v>
       </c>
       <c r="F192" t="str">
-        <f>+_xlfn.XLOOKUP(D192,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D192,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G192">
@@ -4955,7 +4936,7 @@
         <v>192</v>
       </c>
       <c r="F193" t="str">
-        <f>+_xlfn.XLOOKUP(D193,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D193,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G193">
@@ -4973,7 +4954,7 @@
         <v>193</v>
       </c>
       <c r="F194" t="str">
-        <f>+_xlfn.XLOOKUP(D194,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D194,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G194">
@@ -4991,7 +4972,7 @@
         <v>194</v>
       </c>
       <c r="F195" t="str">
-        <f>+_xlfn.XLOOKUP(D195,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D195,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G195">
@@ -5009,7 +4990,7 @@
         <v>195</v>
       </c>
       <c r="F196" t="str">
-        <f>+_xlfn.XLOOKUP(D196,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D196,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G196">
@@ -5033,7 +5014,7 @@
         <v>198</v>
       </c>
       <c r="F197" t="str">
-        <f>+_xlfn.XLOOKUP(D197,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D197,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G197">
@@ -5051,7 +5032,7 @@
         <v>199</v>
       </c>
       <c r="F198" t="str">
-        <f>+_xlfn.XLOOKUP(D198,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D198,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G198">
@@ -5069,7 +5050,7 @@
         <v>200</v>
       </c>
       <c r="F199" t="str">
-        <f>+_xlfn.XLOOKUP(D199,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D199,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G199">
@@ -5093,7 +5074,7 @@
         <v>203</v>
       </c>
       <c r="F200" t="str">
-        <f>+_xlfn.XLOOKUP(D200,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D200,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TRA</v>
       </c>
       <c r="G200">
@@ -5114,7 +5095,7 @@
         <v>204</v>
       </c>
       <c r="F201" t="str">
-        <f>+_xlfn.XLOOKUP(D201,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D201,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G201">
@@ -5132,7 +5113,7 @@
         <v>205</v>
       </c>
       <c r="F202" t="str">
-        <f>+_xlfn.XLOOKUP(D202,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D202,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G202">
@@ -5150,7 +5131,7 @@
         <v>72</v>
       </c>
       <c r="F203" t="str">
-        <f>+_xlfn.XLOOKUP(D203,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D203,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G203">
@@ -5168,8 +5149,8 @@
         <v>207</v>
       </c>
       <c r="F204" t="str">
-        <f>+_xlfn.XLOOKUP(D204,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
-        <v>PL</v>
+        <f>+_xlfn.XLOOKUP(D204,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
+        <v/>
       </c>
       <c r="G204">
         <v>268</v>
@@ -5192,7 +5173,7 @@
         <v>209</v>
       </c>
       <c r="F205" t="str">
-        <f>+_xlfn.XLOOKUP(D205,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D205,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G205">
@@ -5213,7 +5194,7 @@
         <v>210</v>
       </c>
       <c r="F206" t="str">
-        <f>+_xlfn.XLOOKUP(D206,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D206,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G206">
@@ -5231,7 +5212,7 @@
         <v>211</v>
       </c>
       <c r="F207" t="str">
-        <f>+_xlfn.XLOOKUP(D207,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D207,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G207">
@@ -5249,7 +5230,7 @@
         <v>212</v>
       </c>
       <c r="F208" t="str">
-        <f>+_xlfn.XLOOKUP(D208,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D208,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TRA</v>
       </c>
       <c r="G208">
@@ -5270,7 +5251,7 @@
         <v>213</v>
       </c>
       <c r="F209" t="str">
-        <f>+_xlfn.XLOOKUP(D209,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D209,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G209">
@@ -5288,7 +5269,7 @@
         <v>214</v>
       </c>
       <c r="F210" t="str">
-        <f>+_xlfn.XLOOKUP(D210,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D210,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G210">
@@ -5306,7 +5287,7 @@
         <v>215</v>
       </c>
       <c r="F211" t="str">
-        <f>+_xlfn.XLOOKUP(D211,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D211,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TIN</v>
       </c>
       <c r="G211">
@@ -5327,7 +5308,7 @@
         <v>216</v>
       </c>
       <c r="F212" t="str">
-        <f>+_xlfn.XLOOKUP(D212,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D212,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>TRA</v>
       </c>
       <c r="G212">
@@ -5348,7 +5329,7 @@
         <v>204</v>
       </c>
       <c r="F213" t="str">
-        <f>+_xlfn.XLOOKUP(D213,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D213,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G213">
@@ -5372,7 +5353,7 @@
         <v>111</v>
       </c>
       <c r="F214" t="str">
-        <f>+_xlfn.XLOOKUP(D214,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D214,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G214">
@@ -5390,7 +5371,7 @@
         <v>218</v>
       </c>
       <c r="F215" t="str">
-        <f>+_xlfn.XLOOKUP(D215,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D215,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G215">
@@ -5408,7 +5389,7 @@
         <v>219</v>
       </c>
       <c r="F216" t="str">
-        <f>+_xlfn.XLOOKUP(D216,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D216,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>RLL</v>
       </c>
       <c r="G216">
@@ -5426,7 +5407,7 @@
         <v>221</v>
       </c>
       <c r="F217" t="str">
-        <f>+_xlfn.XLOOKUP(D217,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D217,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G217">
@@ -5444,7 +5425,7 @@
         <v>223</v>
       </c>
       <c r="F218" t="str">
-        <f>+_xlfn.XLOOKUP(D218,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D218,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G218">
@@ -5462,7 +5443,7 @@
         <v>225</v>
       </c>
       <c r="F219" t="str">
-        <f>+_xlfn.XLOOKUP(D219,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D219,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G219">
@@ -5486,7 +5467,7 @@
         <v>32</v>
       </c>
       <c r="F220" t="str">
-        <f>+_xlfn.XLOOKUP(D220,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D220,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>PL</v>
       </c>
       <c r="G220">
@@ -5510,7 +5491,7 @@
         <v>228</v>
       </c>
       <c r="F221" t="str">
-        <f>+_xlfn.XLOOKUP(D221,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D221,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G221">
@@ -5528,7 +5509,7 @@
         <v>229</v>
       </c>
       <c r="F222" t="str">
-        <f>+_xlfn.XLOOKUP(D222,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D222,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>ML</v>
       </c>
       <c r="G222">
@@ -5549,7 +5530,7 @@
         <v>231</v>
       </c>
       <c r="F223" t="str">
-        <f>+_xlfn.XLOOKUP(D223,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D223,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G223">
@@ -5567,7 +5548,7 @@
         <v>232</v>
       </c>
       <c r="F224" t="str">
-        <f>+_xlfn.XLOOKUP(D224,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D224,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G224">
@@ -5585,7 +5566,7 @@
         <v>233</v>
       </c>
       <c r="F225" t="str">
-        <f>+_xlfn.XLOOKUP(D225,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D225,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G225">
@@ -5603,7 +5584,7 @@
         <v>234</v>
       </c>
       <c r="F226" t="str">
-        <f>+_xlfn.XLOOKUP(D226,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D226,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>JGO</v>
       </c>
       <c r="G226">
@@ -5621,7 +5602,7 @@
         <v>235</v>
       </c>
       <c r="F227" t="str">
-        <f>+_xlfn.XLOOKUP(D227,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D227,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>JGO</v>
       </c>
       <c r="G227">
@@ -5639,7 +5620,7 @@
         <v>236</v>
       </c>
       <c r="F228" t="str">
-        <f>+_xlfn.XLOOKUP(D228,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D228,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G228">
@@ -5660,7 +5641,7 @@
         <v>238</v>
       </c>
       <c r="F229" t="str">
-        <f>+_xlfn.XLOOKUP(D229,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D229,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G229">
@@ -5678,7 +5659,7 @@
         <v>239</v>
       </c>
       <c r="F230" t="str">
-        <f>+_xlfn.XLOOKUP(D230,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D230,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G230">
@@ -5702,7 +5683,7 @@
         <v>241</v>
       </c>
       <c r="F231" t="str">
-        <f>+_xlfn.XLOOKUP(D231,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D231,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G231">
@@ -5723,7 +5704,7 @@
         <v>111</v>
       </c>
       <c r="F232" t="str">
-        <f>+_xlfn.XLOOKUP(D232,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D232,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G232">
@@ -5747,7 +5728,7 @@
         <v>232</v>
       </c>
       <c r="F233" t="str">
-        <f>+_xlfn.XLOOKUP(D233,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D233,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G233">
@@ -5765,7 +5746,7 @@
         <v>233</v>
       </c>
       <c r="F234" t="str">
-        <f>+_xlfn.XLOOKUP(D234,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D234,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G234">
@@ -5783,7 +5764,7 @@
         <v>234</v>
       </c>
       <c r="F235" t="str">
-        <f>+_xlfn.XLOOKUP(D235,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D235,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>JGO</v>
       </c>
       <c r="G235">
@@ -5801,7 +5782,7 @@
         <v>235</v>
       </c>
       <c r="F236" t="str">
-        <f>+_xlfn.XLOOKUP(D236,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D236,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>JGO</v>
       </c>
       <c r="G236">
@@ -5822,7 +5803,7 @@
         <v>244</v>
       </c>
       <c r="F237" t="str">
-        <f>+_xlfn.XLOOKUP(D237,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D237,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G237">
@@ -5840,7 +5821,7 @@
         <v>245</v>
       </c>
       <c r="F238" t="str">
-        <f>+_xlfn.XLOOKUP(D238,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D238,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G238">
@@ -5864,7 +5845,7 @@
         <v>247</v>
       </c>
       <c r="F239" t="str">
-        <f>+_xlfn.XLOOKUP(D239,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D239,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G239">
@@ -5885,7 +5866,7 @@
         <v>248</v>
       </c>
       <c r="F240" t="str">
-        <f>+_xlfn.XLOOKUP(D240,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D240,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G240">
@@ -5903,7 +5884,7 @@
         <v>249</v>
       </c>
       <c r="F241" t="str">
-        <f>+_xlfn.XLOOKUP(D241,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D241,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G241">
@@ -5927,7 +5908,7 @@
         <v>251</v>
       </c>
       <c r="F242" t="str">
-        <f>+_xlfn.XLOOKUP(D242,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D242,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G242">
@@ -5945,7 +5926,7 @@
         <v>247</v>
       </c>
       <c r="F243" t="str">
-        <f>+_xlfn.XLOOKUP(D243,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D243,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>UND</v>
       </c>
       <c r="G243">
@@ -5966,7 +5947,7 @@
         <v>248</v>
       </c>
       <c r="F244" t="str">
-        <f>+_xlfn.XLOOKUP(D244,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D244,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G244">
@@ -5984,7 +5965,7 @@
         <v>249</v>
       </c>
       <c r="F245" t="str">
-        <f>+_xlfn.XLOOKUP(D245,Tabla1[PARTIDA],Tabla1[UNIDAD],"",0)</f>
+        <f>+_xlfn.XLOOKUP(D245,Tabla1[CODIGO],Tabla1[UNIDAD],"",0)</f>
         <v>KIT</v>
       </c>
       <c r="G245">
@@ -6001,27 +5982,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D21CD9-5B6C-44F0-BB08-EDDC057A186D}">
-  <dimension ref="A1:D611"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="108" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1" t="s">
         <v>254</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>255</v>
       </c>
-      <c r="C1" t="s">
-        <v>256</v>
-      </c>
       <c r="D1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="E1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>106022</v>
       </c>
@@ -6029,13 +6015,16 @@
         <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D2">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.8250000000000002</v>
+      </c>
+      <c r="E2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>302010</v>
       </c>
@@ -6043,13 +6032,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D3">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34.912500000000001</v>
+      </c>
+      <c r="E3">
+        <v>34.912500000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>302028</v>
       </c>
@@ -6057,55 +6049,67 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D4">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>172.72499999999999</v>
+      </c>
+      <c r="E4">
+        <v>138.17500000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>302046</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D5">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34.65</v>
+      </c>
+      <c r="E5">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>302048</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D6">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35.174999999999997</v>
+      </c>
+      <c r="E6">
+        <v>35.174999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>302054</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D7">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>34.543750000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>302248</v>
       </c>
@@ -6113,13 +6117,16 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D8">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8.9250000000000007</v>
+      </c>
+      <c r="E8">
+        <v>8.9250000000000007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>302249</v>
       </c>
@@ -6127,13 +6134,16 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D9">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.3</v>
+      </c>
+      <c r="E9">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>304002</v>
       </c>
@@ -6141,13 +6151,16 @@
         <v>204</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D10">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23.296875</v>
+      </c>
+      <c r="E10">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>304007</v>
       </c>
@@ -6155,13 +6168,16 @@
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D11">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8.6624999999999996</v>
+      </c>
+      <c r="E11">
+        <v>8.2687500000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>304012</v>
       </c>
@@ -6169,13 +6185,16 @@
         <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D12">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>304049</v>
       </c>
@@ -6183,13 +6202,16 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D13">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23.273125</v>
+      </c>
+      <c r="E13">
+        <v>24.323125000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>304101</v>
       </c>
@@ -6197,13 +6219,16 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D14">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47.643749999999997</v>
+      </c>
+      <c r="E14">
+        <v>46.987499999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>307030</v>
       </c>
@@ -6211,13 +6236,16 @@
         <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D15">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.35</v>
+      </c>
+      <c r="E15">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>307031</v>
       </c>
@@ -6225,13 +6253,16 @@
         <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D16">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15.865625</v>
+      </c>
+      <c r="E16">
+        <v>15.865625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>307032</v>
       </c>
@@ -6239,13 +6270,16 @@
         <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D17">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8.4</v>
+      </c>
+      <c r="E17">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>307033</v>
       </c>
@@ -6253,13 +6287,16 @@
         <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D18">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.875</v>
+      </c>
+      <c r="E18">
+        <v>7.875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>307096</v>
       </c>
@@ -6267,2769 +6304,2667 @@
         <v>162</v>
       </c>
       <c r="C19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="E19">
+        <v>65.099999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>404252</v>
+      </c>
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>3.6749999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>404745</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D21">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E21">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>404793</v>
+      </c>
+      <c r="B22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D22">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E22">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>407010</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>256</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>65.625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>407011</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>256</v>
+      </c>
+      <c r="D24">
+        <v>588</v>
+      </c>
+      <c r="E24">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>407049</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25">
+        <v>52.5</v>
+      </c>
+      <c r="E25">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>407115</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>256</v>
+      </c>
+      <c r="D26">
+        <v>4.2</v>
+      </c>
+      <c r="E26">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>407170</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="E27">
+        <v>151.19999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>407185</v>
+      </c>
+      <c r="B28" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28">
+        <v>966</v>
+      </c>
+      <c r="E28">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>407307</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29">
+        <v>18.375</v>
+      </c>
+      <c r="E29">
+        <v>65.625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>407423</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30">
+        <v>788.55</v>
+      </c>
+      <c r="E30">
+        <v>788.55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>407427</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>263</v>
+      </c>
+      <c r="D31">
+        <v>0.105</v>
+      </c>
+      <c r="E31">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>407795</v>
+      </c>
+      <c r="B32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>408014</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D33">
+        <v>0.51437500000000003</v>
+      </c>
+      <c r="E33">
+        <v>0.14281250000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>408017</v>
+      </c>
+      <c r="B34" t="s">
         <v>264</v>
       </c>
-      <c r="D19">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>403024</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C34" t="s">
+        <v>263</v>
+      </c>
+      <c r="D34">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="E34">
+        <v>5.2499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>408034</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" t="s">
+        <v>263</v>
+      </c>
+      <c r="D35">
+        <v>7.1249999999999994E-2</v>
+      </c>
+      <c r="E35">
+        <v>7.1249999999999994E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>408042</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36">
+        <v>0.958125</v>
+      </c>
+      <c r="E36">
+        <v>1.17875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>408088</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>263</v>
+      </c>
+      <c r="D37">
+        <v>0.12593750000000001</v>
+      </c>
+      <c r="E37">
+        <v>0.12593750000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>409011</v>
+      </c>
+      <c r="B38" t="s">
+        <v>216</v>
+      </c>
+      <c r="C38" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>410045</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39">
+        <v>16.8</v>
+      </c>
+      <c r="E39">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>410046</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="s">
+        <v>256</v>
+      </c>
+      <c r="D40">
+        <v>8.4</v>
+      </c>
+      <c r="E40">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>410126</v>
+      </c>
+      <c r="B41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
+        <v>256</v>
+      </c>
+      <c r="D41">
+        <v>10.5</v>
+      </c>
+      <c r="E41">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>412016</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>256</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>412132</v>
+      </c>
+      <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>412260</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>256</v>
+      </c>
+      <c r="D44">
+        <v>5.7750000000000004</v>
+      </c>
+      <c r="E44">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>412280</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45">
+        <v>7.875</v>
+      </c>
+      <c r="E45">
+        <v>8.9250000000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>412281</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D46">
+        <v>2.1</v>
+      </c>
+      <c r="E46">
+        <v>1.8374999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>412301</v>
+      </c>
+      <c r="B47" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s">
+        <v>256</v>
+      </c>
+      <c r="D47">
+        <v>21</v>
+      </c>
+      <c r="E47">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>412302</v>
+      </c>
+      <c r="B48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" t="s">
+        <v>256</v>
+      </c>
+      <c r="D48">
+        <v>1.05</v>
+      </c>
+      <c r="E48">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>412313</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>263</v>
+      </c>
+      <c r="D49">
+        <v>0.203125</v>
+      </c>
+      <c r="E49">
+        <v>0.86531250000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>412630</v>
+      </c>
+      <c r="B50" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" t="s">
+        <v>256</v>
+      </c>
+      <c r="D50">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E50">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>601047</v>
+      </c>
+      <c r="B51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" t="s">
         <v>265</v>
       </c>
-      <c r="C20" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>404252</v>
-      </c>
-      <c r="B21" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" t="s">
-        <v>258</v>
-      </c>
-      <c r="D21">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>404745</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" t="s">
-        <v>258</v>
-      </c>
-      <c r="D22">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>404793</v>
-      </c>
-      <c r="B23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C23" t="s">
-        <v>258</v>
-      </c>
-      <c r="D23">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>407010</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>407011</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" t="s">
-        <v>258</v>
-      </c>
-      <c r="D25">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>407049</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>258</v>
-      </c>
-      <c r="D26">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>407115</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>258</v>
-      </c>
-      <c r="D27">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>407170</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" t="s">
-        <v>258</v>
-      </c>
-      <c r="D28">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>407185</v>
-      </c>
-      <c r="B29" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" t="s">
-        <v>258</v>
-      </c>
-      <c r="D29">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>407307</v>
-      </c>
-      <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" t="s">
-        <v>258</v>
-      </c>
-      <c r="D30">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>407423</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>258</v>
-      </c>
-      <c r="D31">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>407427</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>266</v>
-      </c>
-      <c r="D32">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>407795</v>
-      </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" t="s">
-        <v>258</v>
-      </c>
-      <c r="D33">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>408014</v>
-      </c>
-      <c r="B34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" t="s">
-        <v>266</v>
-      </c>
-      <c r="D34">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>408017</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0.1575</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>602254</v>
+      </c>
+      <c r="B52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52">
+        <v>0.35906250000000001</v>
+      </c>
+      <c r="E52">
+        <v>0.57750000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>602255</v>
+      </c>
+      <c r="B53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" t="s">
+        <v>265</v>
+      </c>
+      <c r="D53">
+        <v>0.301875</v>
+      </c>
+      <c r="E53">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>602256</v>
+      </c>
+      <c r="B54" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54">
+        <v>2.3125E-2</v>
+      </c>
+      <c r="E54">
+        <v>2.6249999999999999E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>602257</v>
+      </c>
+      <c r="B55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" t="s">
+        <v>265</v>
+      </c>
+      <c r="D55">
+        <v>0.18625</v>
+      </c>
+      <c r="E55">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>602258</v>
+      </c>
+      <c r="B56" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" t="s">
+        <v>265</v>
+      </c>
+      <c r="D56">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="E56">
+        <v>9.1874999999999998E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>608013</v>
+      </c>
+      <c r="B57" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57">
+        <v>0.105</v>
+      </c>
+      <c r="E57">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>609008</v>
+      </c>
+      <c r="B58" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" t="s">
         <v>267</v>
       </c>
-      <c r="C35" t="s">
-        <v>266</v>
-      </c>
-      <c r="D35">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>408034</v>
-      </c>
-      <c r="B36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" t="s">
-        <v>266</v>
-      </c>
-      <c r="D36">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>408042</v>
-      </c>
-      <c r="B37" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" t="s">
-        <v>266</v>
-      </c>
-      <c r="D37">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>408088</v>
-      </c>
-      <c r="B38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" t="s">
-        <v>266</v>
-      </c>
-      <c r="D38">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>409011</v>
-      </c>
-      <c r="B39" t="s">
-        <v>216</v>
-      </c>
-      <c r="C39" t="s">
-        <v>264</v>
-      </c>
-      <c r="D39">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>410045</v>
-      </c>
-      <c r="B40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" t="s">
-        <v>258</v>
-      </c>
-      <c r="D40">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>410046</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="s">
-        <v>258</v>
-      </c>
-      <c r="D41">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>410126</v>
-      </c>
-      <c r="B42" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" t="s">
-        <v>258</v>
-      </c>
-      <c r="D42">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>412016</v>
-      </c>
-      <c r="B43" t="s">
-        <v>99</v>
-      </c>
-      <c r="C43" t="s">
-        <v>258</v>
-      </c>
-      <c r="D43">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>412132</v>
-      </c>
-      <c r="B44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" t="s">
-        <v>258</v>
-      </c>
-      <c r="D44">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>412260</v>
-      </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>258</v>
-      </c>
-      <c r="D45">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>412280</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>258</v>
-      </c>
-      <c r="D46">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>412281</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>258</v>
-      </c>
-      <c r="D47">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>412301</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>258</v>
-      </c>
-      <c r="D48">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>412302</v>
-      </c>
-      <c r="B49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>258</v>
-      </c>
-      <c r="D49">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>412313</v>
-      </c>
-      <c r="B50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" t="s">
-        <v>266</v>
-      </c>
-      <c r="D50">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>412630</v>
-      </c>
-      <c r="B51" t="s">
-        <v>218</v>
-      </c>
-      <c r="C51" t="s">
-        <v>258</v>
-      </c>
-      <c r="D51">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>601047</v>
-      </c>
-      <c r="B52" t="s">
-        <v>184</v>
-      </c>
-      <c r="C52" t="s">
-        <v>268</v>
-      </c>
-      <c r="D52">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>601121</v>
-      </c>
-      <c r="B53" t="s">
-        <v>269</v>
-      </c>
-      <c r="C53" t="s">
-        <v>270</v>
-      </c>
-      <c r="D53">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>602254</v>
-      </c>
-      <c r="B54" t="s">
-        <v>185</v>
-      </c>
-      <c r="C54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D54">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>602255</v>
-      </c>
-      <c r="B55" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" t="s">
-        <v>268</v>
-      </c>
-      <c r="D55">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>602256</v>
-      </c>
-      <c r="B56" t="s">
-        <v>213</v>
-      </c>
-      <c r="C56" t="s">
-        <v>268</v>
-      </c>
-      <c r="D56">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>602257</v>
-      </c>
-      <c r="B57" t="s">
-        <v>214</v>
-      </c>
-      <c r="C57" t="s">
-        <v>268</v>
-      </c>
-      <c r="D57">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>602258</v>
-      </c>
-      <c r="B58" t="s">
-        <v>215</v>
-      </c>
-      <c r="C58" t="s">
-        <v>268</v>
-      </c>
       <c r="D58">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>608013</v>
+        <v>617016</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D59">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>609008</v>
+        <v>617055</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="C60" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D60">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>617016</v>
+        <v>617057</v>
       </c>
       <c r="B61" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D61">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>1.575</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>617055</v>
+        <v>701015</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>46</v>
       </c>
       <c r="C62" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D62">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="E62">
+        <v>4.7249999999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>617057</v>
+        <v>701040</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D63">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.2840625000000001</v>
+      </c>
+      <c r="E63">
+        <v>2.8875000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>701015</v>
+        <v>701043</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D64">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.0875000000000004</v>
+      </c>
+      <c r="E64">
+        <v>7.0875000000000004</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>701040</v>
+        <v>701084</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.698125</v>
+      </c>
+      <c r="E65">
+        <v>0.698125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>701043</v>
+        <v>701096</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31.237500000000001</v>
+      </c>
+      <c r="E66">
+        <v>31.237500000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>701084</v>
+        <v>704021</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" t="s">
-        <v>263</v>
+        <v>181</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="E67">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>701096</v>
+        <v>704022</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" t="s">
-        <v>263</v>
+        <v>165</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14.175000000000001</v>
+      </c>
+      <c r="E68">
+        <v>14.175000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>704021</v>
+        <v>704023</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23.625</v>
+      </c>
+      <c r="E69">
+        <v>23.625</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>704022</v>
+        <v>704024</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.2</v>
+      </c>
+      <c r="E70">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>704023</v>
+        <v>704025</v>
       </c>
       <c r="B71" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.2</v>
+      </c>
+      <c r="E71">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>704024</v>
+        <v>704046</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
-      </c>
-      <c r="C72">
+        <v>219</v>
+      </c>
+      <c r="C72" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72">
+        <v>0.42</v>
+      </c>
+      <c r="E72">
+        <v>0.88468749999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>704079</v>
+      </c>
+      <c r="B73" t="s">
+        <v>189</v>
+      </c>
+      <c r="C73" t="s">
+        <v>268</v>
+      </c>
+      <c r="D73">
         <v>0</v>
       </c>
-      <c r="D72">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>704025</v>
-      </c>
-      <c r="B73" t="s">
-        <v>170</v>
-      </c>
-      <c r="C73">
+      <c r="E73">
+        <v>0.44843749999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>705028</v>
+      </c>
+      <c r="B74" t="s">
+        <v>192</v>
+      </c>
+      <c r="C74" t="s">
+        <v>261</v>
+      </c>
+      <c r="D74">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="E74">
+        <v>3.3468749999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>707023</v>
+      </c>
+      <c r="B75" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" t="s">
+        <v>256</v>
+      </c>
+      <c r="D75">
+        <v>3.15</v>
+      </c>
+      <c r="E75">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>810007</v>
+      </c>
+      <c r="B76" t="s">
+        <v>51</v>
+      </c>
+      <c r="C76" t="s">
+        <v>262</v>
+      </c>
+      <c r="D76">
+        <v>1.05</v>
+      </c>
+      <c r="E76">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>907031</v>
+      </c>
+      <c r="B77" t="s">
+        <v>157</v>
+      </c>
+      <c r="C77" t="s">
+        <v>268</v>
+      </c>
+      <c r="D77">
+        <v>0.71125000000000005</v>
+      </c>
+      <c r="E77">
+        <v>0.71125000000000005</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1003500</v>
+      </c>
+      <c r="B78" t="s">
+        <v>203</v>
+      </c>
+      <c r="C78" t="s">
+        <v>262</v>
+      </c>
+      <c r="D78">
+        <v>13.65</v>
+      </c>
+      <c r="E78">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1101307</v>
+      </c>
+      <c r="B79" t="s">
+        <v>229</v>
+      </c>
+      <c r="C79" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79">
         <v>0</v>
       </c>
-      <c r="D73">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>704046</v>
-      </c>
-      <c r="B74" t="s">
-        <v>219</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="E79">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1103074</v>
+      </c>
+      <c r="B80" t="s">
+        <v>193</v>
+      </c>
+      <c r="C80" t="s">
+        <v>256</v>
+      </c>
+      <c r="D80">
+        <v>1.05</v>
+      </c>
+      <c r="E80">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1103076</v>
+      </c>
+      <c r="B81" t="s">
+        <v>194</v>
+      </c>
+      <c r="C81" t="s">
+        <v>256</v>
+      </c>
+      <c r="D81">
+        <v>1.05</v>
+      </c>
+      <c r="E81">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1103086</v>
+      </c>
+      <c r="B82" t="s">
+        <v>270</v>
+      </c>
+      <c r="C82" t="s">
+        <v>256</v>
+      </c>
+      <c r="D82">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E82">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1103087</v>
+      </c>
+      <c r="B83" t="s">
+        <v>271</v>
+      </c>
+      <c r="C83" t="s">
+        <v>256</v>
+      </c>
+      <c r="D83">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E83">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1103088</v>
+      </c>
+      <c r="B84" t="s">
+        <v>212</v>
+      </c>
+      <c r="C84" t="s">
+        <v>262</v>
+      </c>
+      <c r="D84">
+        <v>1.05</v>
+      </c>
+      <c r="E84">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1206002</v>
+      </c>
+      <c r="B85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C85" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E85">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1405006</v>
+      </c>
+      <c r="B86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" t="s">
+        <v>256</v>
+      </c>
+      <c r="D86">
+        <v>30.45</v>
+      </c>
+      <c r="E86">
+        <v>30.45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1405025</v>
+      </c>
+      <c r="B87" t="s">
+        <v>231</v>
+      </c>
+      <c r="C87" t="s">
+        <v>256</v>
+      </c>
+      <c r="D87">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E87">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1405039</v>
+      </c>
+      <c r="B88" t="s">
+        <v>251</v>
+      </c>
+      <c r="C88" t="s">
+        <v>256</v>
+      </c>
+      <c r="D88">
+        <v>1.575</v>
+      </c>
+      <c r="E88">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1405040</v>
+      </c>
+      <c r="B89" t="s">
+        <v>247</v>
+      </c>
+      <c r="C89" t="s">
+        <v>256</v>
+      </c>
+      <c r="D89">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E89">
+        <v>1.575</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1610007</v>
+      </c>
+      <c r="B90" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1610023</v>
+      </c>
+      <c r="B91" t="s">
+        <v>154</v>
+      </c>
+      <c r="C91" t="s">
+        <v>273</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1701154</v>
+      </c>
+      <c r="B92" t="s">
+        <v>127</v>
+      </c>
+      <c r="C92" t="s">
+        <v>256</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1703006</v>
+      </c>
+      <c r="B93" t="s">
+        <v>136</v>
+      </c>
+      <c r="C93" t="s">
+        <v>256</v>
+      </c>
+      <c r="D93">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E93">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1801229</v>
+      </c>
+      <c r="B94" t="s">
+        <v>112</v>
+      </c>
+      <c r="C94" t="s">
+        <v>256</v>
+      </c>
+      <c r="D94">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E94">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1801230</v>
+      </c>
+      <c r="B95" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E95">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1801735</v>
+      </c>
+      <c r="B96" t="s">
+        <v>114</v>
+      </c>
+      <c r="C96" t="s">
+        <v>256</v>
+      </c>
+      <c r="D96">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E96">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1802162</v>
+      </c>
+      <c r="B97" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" t="s">
+        <v>256</v>
+      </c>
+      <c r="D97">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E97">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1802164</v>
+      </c>
+      <c r="B98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C98" t="s">
+        <v>256</v>
+      </c>
+      <c r="D98">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E98">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1802165</v>
+      </c>
+      <c r="B99" t="s">
+        <v>128</v>
+      </c>
+      <c r="C99" t="s">
+        <v>256</v>
+      </c>
+      <c r="D99">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E99">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1802166</v>
+      </c>
+      <c r="B100" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100" t="s">
+        <v>256</v>
+      </c>
+      <c r="D100">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E100">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1802167</v>
+      </c>
+      <c r="B101" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" t="s">
+        <v>256</v>
+      </c>
+      <c r="D101">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E101">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1802169</v>
+      </c>
+      <c r="B102" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" t="s">
+        <v>256</v>
+      </c>
+      <c r="D102">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E102">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1802170</v>
+      </c>
+      <c r="B103" t="s">
+        <v>120</v>
+      </c>
+      <c r="C103" t="s">
+        <v>256</v>
+      </c>
+      <c r="D103">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E103">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1802171</v>
+      </c>
+      <c r="B104" t="s">
+        <v>102</v>
+      </c>
+      <c r="C104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D104">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E104">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1802172</v>
+      </c>
+      <c r="B105" t="s">
+        <v>103</v>
+      </c>
+      <c r="C105" t="s">
+        <v>256</v>
+      </c>
+      <c r="D105">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E105">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1802173</v>
+      </c>
+      <c r="B106" t="s">
+        <v>124</v>
+      </c>
+      <c r="C106" t="s">
+        <v>256</v>
+      </c>
+      <c r="D106">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E106">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1802174</v>
+      </c>
+      <c r="B107" t="s">
+        <v>125</v>
+      </c>
+      <c r="C107" t="s">
+        <v>256</v>
+      </c>
+      <c r="D107">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E107">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1802175</v>
+      </c>
+      <c r="B108" t="s">
+        <v>126</v>
+      </c>
+      <c r="C108" t="s">
+        <v>256</v>
+      </c>
+      <c r="D108">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E108">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1802176</v>
+      </c>
+      <c r="B109" t="s">
+        <v>129</v>
+      </c>
+      <c r="C109" t="s">
+        <v>256</v>
+      </c>
+      <c r="D109">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E109">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1802517</v>
+      </c>
+      <c r="B110" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110" t="s">
+        <v>256</v>
+      </c>
+      <c r="D110">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E110">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1802659</v>
+      </c>
+      <c r="B111" t="s">
+        <v>198</v>
+      </c>
+      <c r="C111" t="s">
+        <v>256</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1803044</v>
+      </c>
+      <c r="B112" t="s">
+        <v>248</v>
+      </c>
+      <c r="C112" t="s">
         <v>272</v>
       </c>
-      <c r="D74">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>704079</v>
-      </c>
-      <c r="B75" t="s">
-        <v>189</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="D112">
+        <v>1.05</v>
+      </c>
+      <c r="E112">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1803045</v>
+      </c>
+      <c r="B113" t="s">
+        <v>249</v>
+      </c>
+      <c r="C113" t="s">
         <v>272</v>
       </c>
-      <c r="D75">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>705028</v>
-      </c>
-      <c r="B76" t="s">
-        <v>192</v>
-      </c>
-      <c r="C76" t="s">
-        <v>263</v>
-      </c>
-      <c r="D76">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>707023</v>
-      </c>
-      <c r="B77" t="s">
-        <v>37</v>
-      </c>
-      <c r="C77" t="s">
-        <v>258</v>
-      </c>
-      <c r="D77">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>810007</v>
-      </c>
-      <c r="B78" t="s">
-        <v>51</v>
-      </c>
-      <c r="C78" t="s">
-        <v>264</v>
-      </c>
-      <c r="D78">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>907031</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="D113">
+        <v>1.05</v>
+      </c>
+      <c r="E113">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1805340</v>
+      </c>
+      <c r="B114" t="s">
+        <v>199</v>
+      </c>
+      <c r="C114" t="s">
+        <v>256</v>
+      </c>
+      <c r="D114">
+        <v>1.05</v>
+      </c>
+      <c r="E114">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1808003</v>
+      </c>
+      <c r="B115" t="s">
+        <v>105</v>
+      </c>
+      <c r="C115" t="s">
+        <v>256</v>
+      </c>
+      <c r="D115">
+        <v>0.91874999999999996</v>
+      </c>
+      <c r="E115">
+        <v>0.91874999999999996</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1808006</v>
+      </c>
+      <c r="B116" t="s">
+        <v>106</v>
+      </c>
+      <c r="C116" t="s">
+        <v>256</v>
+      </c>
+      <c r="D116">
+        <v>0.65625</v>
+      </c>
+      <c r="E116">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1808144</v>
+      </c>
+      <c r="B117" t="s">
+        <v>141</v>
+      </c>
+      <c r="C117" t="s">
+        <v>256</v>
+      </c>
+      <c r="D117">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E117">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1808145</v>
+      </c>
+      <c r="B118" t="s">
+        <v>142</v>
+      </c>
+      <c r="C118" t="s">
+        <v>256</v>
+      </c>
+      <c r="D118">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E118">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1808146</v>
+      </c>
+      <c r="B119" t="s">
+        <v>107</v>
+      </c>
+      <c r="C119" t="s">
+        <v>256</v>
+      </c>
+      <c r="D119">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E119">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1808147</v>
+      </c>
+      <c r="B120" t="s">
+        <v>143</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+      <c r="D120">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E120">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1808148</v>
+      </c>
+      <c r="B121" t="s">
+        <v>144</v>
+      </c>
+      <c r="C121" t="s">
+        <v>256</v>
+      </c>
+      <c r="D121">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E121">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1808156</v>
+      </c>
+      <c r="B122" t="s">
+        <v>108</v>
+      </c>
+      <c r="C122" t="s">
+        <v>256</v>
+      </c>
+      <c r="D122">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E122">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1901008</v>
+      </c>
+      <c r="B123" t="s">
+        <v>69</v>
+      </c>
+      <c r="C123" t="s">
+        <v>274</v>
+      </c>
+      <c r="D123">
+        <v>62.430312499999999</v>
+      </c>
+      <c r="E123">
+        <v>62.430312499999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1901038</v>
+      </c>
+      <c r="B124" t="s">
+        <v>175</v>
+      </c>
+      <c r="C124" t="s">
+        <v>274</v>
+      </c>
+      <c r="D124">
+        <v>40.010312499999998</v>
+      </c>
+      <c r="E124">
+        <v>17.010000000000002</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>1901086</v>
+      </c>
+      <c r="B125" t="s">
+        <v>70</v>
+      </c>
+      <c r="C125" t="s">
+        <v>274</v>
+      </c>
+      <c r="D125">
+        <v>31.794374999999999</v>
+      </c>
+      <c r="E125">
+        <v>31.794374999999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>1901466</v>
+      </c>
+      <c r="B126" t="s">
+        <v>176</v>
+      </c>
+      <c r="C126" t="s">
+        <v>274</v>
+      </c>
+      <c r="D126">
+        <v>29.529375000000002</v>
+      </c>
+      <c r="E126">
+        <v>29.529375000000002</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>1901505</v>
+      </c>
+      <c r="B127" t="s">
+        <v>71</v>
+      </c>
+      <c r="C127" t="s">
+        <v>273</v>
+      </c>
+      <c r="D127">
+        <v>1.2368749999999999</v>
+      </c>
+      <c r="E127">
+        <v>1.2337499999999999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>1902003</v>
+      </c>
+      <c r="B128" t="s">
+        <v>72</v>
+      </c>
+      <c r="C128" t="s">
+        <v>268</v>
+      </c>
+      <c r="D128">
+        <v>0.41468749999999999</v>
+      </c>
+      <c r="E128">
+        <v>0.41468749999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>1902013</v>
+      </c>
+      <c r="B129" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" t="s">
+        <v>268</v>
+      </c>
+      <c r="D129">
+        <v>2.1722447916666665</v>
+      </c>
+      <c r="E129">
+        <v>2.1078125000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>1902014</v>
+      </c>
+      <c r="B130" t="s">
+        <v>73</v>
+      </c>
+      <c r="C130" t="s">
+        <v>261</v>
+      </c>
+      <c r="D130">
+        <v>5.5125000000000002</v>
+      </c>
+      <c r="E130">
+        <v>5.8615624999999998</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>2302017</v>
+      </c>
+      <c r="B131" t="s">
+        <v>158</v>
+      </c>
+      <c r="C131" t="s">
+        <v>265</v>
+      </c>
+      <c r="D131">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="E131">
+        <v>0.78749999999999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>2302024</v>
+      </c>
+      <c r="B132" t="s">
+        <v>52</v>
+      </c>
+      <c r="C132" t="s">
+        <v>266</v>
+      </c>
+      <c r="D132">
+        <v>0.13125000000000001</v>
+      </c>
+      <c r="E132">
+        <v>0.78749999999999998</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>2302044</v>
+      </c>
+      <c r="B133" t="s">
+        <v>53</v>
+      </c>
+      <c r="C133" t="s">
+        <v>275</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>6.6875000000000004E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>2302045</v>
+      </c>
+      <c r="B134" t="s">
+        <v>54</v>
+      </c>
+      <c r="C134" t="s">
+        <v>265</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>6.6875000000000004E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>2302098</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135" t="s">
+        <v>265</v>
+      </c>
+      <c r="D135">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E135">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>2302118</v>
+      </c>
+      <c r="B136" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" t="s">
+        <v>256</v>
+      </c>
+      <c r="D136">
+        <v>0.31187500000000001</v>
+      </c>
+      <c r="E136">
+        <v>0.31187500000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>2302119</v>
+      </c>
+      <c r="B137" t="s">
+        <v>177</v>
+      </c>
+      <c r="C137" t="s">
+        <v>256</v>
+      </c>
+      <c r="D137">
+        <v>1.575</v>
+      </c>
+      <c r="E137">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>2304002</v>
+      </c>
+      <c r="B138" t="s">
+        <v>96</v>
+      </c>
+      <c r="C138" t="s">
+        <v>256</v>
+      </c>
+      <c r="D138">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E138">
+        <v>2.9312499999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>2304003</v>
+      </c>
+      <c r="B139" t="s">
+        <v>138</v>
+      </c>
+      <c r="C139" t="s">
+        <v>256</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>5.6875000000000002E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>2304008</v>
+      </c>
+      <c r="B140" t="s">
+        <v>195</v>
+      </c>
+      <c r="C140" t="s">
+        <v>256</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>2304053</v>
+      </c>
+      <c r="B141" t="s">
+        <v>190</v>
+      </c>
+      <c r="C141" t="s">
+        <v>256</v>
+      </c>
+      <c r="D141">
+        <v>2.1</v>
+      </c>
+      <c r="E141">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>2304056</v>
+      </c>
+      <c r="B142" t="s">
+        <v>56</v>
+      </c>
+      <c r="C142" t="s">
+        <v>256</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0.78749999999999998</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>2505058</v>
+      </c>
+      <c r="B143" t="s">
+        <v>200</v>
+      </c>
+      <c r="C143" t="s">
+        <v>256</v>
+      </c>
+      <c r="D143">
+        <v>2.1</v>
+      </c>
+      <c r="E143">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>2505426</v>
+      </c>
+      <c r="B144" t="s">
+        <v>130</v>
+      </c>
+      <c r="C144" t="s">
+        <v>256</v>
+      </c>
+      <c r="D144">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E144">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>2508169</v>
+      </c>
+      <c r="B145" t="s">
+        <v>92</v>
+      </c>
+      <c r="C145" t="s">
+        <v>256</v>
+      </c>
+      <c r="D145">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E145">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>2508985</v>
+      </c>
+      <c r="B146" t="s">
+        <v>238</v>
+      </c>
+      <c r="C146" t="s">
         <v>272</v>
       </c>
-      <c r="D79">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>1003500</v>
-      </c>
-      <c r="B80" t="s">
-        <v>203</v>
-      </c>
-      <c r="C80" t="s">
-        <v>264</v>
-      </c>
-      <c r="D80">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>1101307</v>
-      </c>
-      <c r="B81" t="s">
-        <v>229</v>
-      </c>
-      <c r="C81" t="s">
-        <v>273</v>
-      </c>
-      <c r="D81">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>1103074</v>
-      </c>
-      <c r="B82" t="s">
-        <v>193</v>
-      </c>
-      <c r="C82" t="s">
-        <v>258</v>
-      </c>
-      <c r="D82">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>1103076</v>
-      </c>
-      <c r="B83" t="s">
-        <v>194</v>
-      </c>
-      <c r="C83" t="s">
-        <v>258</v>
-      </c>
-      <c r="D83">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>1103086</v>
-      </c>
-      <c r="B84" t="s">
-        <v>274</v>
-      </c>
-      <c r="C84" t="s">
-        <v>258</v>
-      </c>
-      <c r="D84">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>1103087</v>
-      </c>
-      <c r="B85" t="s">
-        <v>275</v>
-      </c>
-      <c r="C85" t="s">
-        <v>258</v>
-      </c>
-      <c r="D85">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>1103088</v>
-      </c>
-      <c r="B86" t="s">
-        <v>212</v>
-      </c>
-      <c r="C86" t="s">
-        <v>264</v>
-      </c>
-      <c r="D86">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>1206002</v>
-      </c>
-      <c r="B87" t="s">
-        <v>101</v>
-      </c>
-      <c r="C87" t="s">
-        <v>258</v>
-      </c>
-      <c r="D87">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>1405006</v>
-      </c>
-      <c r="B88" t="s">
-        <v>19</v>
-      </c>
-      <c r="C88" t="s">
-        <v>258</v>
-      </c>
-      <c r="D88">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>1405025</v>
-      </c>
-      <c r="B89" t="s">
-        <v>231</v>
-      </c>
-      <c r="C89" t="s">
-        <v>258</v>
-      </c>
-      <c r="D89">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>1405026</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="D146">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="E146">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>2508986</v>
+      </c>
+      <c r="B147" t="s">
+        <v>239</v>
+      </c>
+      <c r="C147" t="s">
+        <v>272</v>
+      </c>
+      <c r="D147">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="E147">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>2508987</v>
+      </c>
+      <c r="B148" t="s">
+        <v>244</v>
+      </c>
+      <c r="C148" t="s">
+        <v>272</v>
+      </c>
+      <c r="D148">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="E148">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>2508988</v>
+      </c>
+      <c r="B149" t="s">
+        <v>245</v>
+      </c>
+      <c r="C149" t="s">
+        <v>272</v>
+      </c>
+      <c r="D149">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="E149">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>2508990</v>
+      </c>
+      <c r="B150" t="s">
+        <v>232</v>
+      </c>
+      <c r="C150" t="s">
+        <v>256</v>
+      </c>
+      <c r="D150">
+        <v>1.05</v>
+      </c>
+      <c r="E150">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>2508991</v>
+      </c>
+      <c r="B151" t="s">
+        <v>233</v>
+      </c>
+      <c r="C151" t="s">
+        <v>256</v>
+      </c>
+      <c r="D151">
+        <v>1.05</v>
+      </c>
+      <c r="E151">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>2508992</v>
+      </c>
+      <c r="B152" t="s">
+        <v>234</v>
+      </c>
+      <c r="C152" t="s">
         <v>276</v>
       </c>
-      <c r="C90" t="s">
-        <v>277</v>
-      </c>
-      <c r="D90">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>1405027</v>
-      </c>
-      <c r="B91" t="s">
-        <v>278</v>
-      </c>
-      <c r="C91" t="s">
-        <v>277</v>
-      </c>
-      <c r="D91">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>1405039</v>
-      </c>
-      <c r="B92" t="s">
-        <v>251</v>
-      </c>
-      <c r="C92" t="s">
-        <v>258</v>
-      </c>
-      <c r="D92">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>1405040</v>
-      </c>
-      <c r="B93" t="s">
-        <v>247</v>
-      </c>
-      <c r="C93" t="s">
-        <v>258</v>
-      </c>
-      <c r="D93">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>1610007</v>
-      </c>
-      <c r="B94" t="s">
-        <v>153</v>
-      </c>
-      <c r="C94" t="s">
-        <v>279</v>
-      </c>
-      <c r="D94">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>1610023</v>
-      </c>
-      <c r="B95" t="s">
-        <v>154</v>
-      </c>
-      <c r="C95" t="s">
-        <v>279</v>
-      </c>
-      <c r="D95">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>1701071</v>
-      </c>
-      <c r="B96" t="s">
-        <v>280</v>
-      </c>
-      <c r="C96" t="s">
-        <v>258</v>
-      </c>
-      <c r="D96">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>1701154</v>
-      </c>
-      <c r="B97" t="s">
-        <v>127</v>
-      </c>
-      <c r="C97" t="s">
-        <v>258</v>
-      </c>
-      <c r="D97">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>1703006</v>
-      </c>
-      <c r="B98" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" t="s">
-        <v>258</v>
-      </c>
-      <c r="D98">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>1801161</v>
-      </c>
-      <c r="B99" t="s">
-        <v>281</v>
-      </c>
-      <c r="C99" t="s">
-        <v>258</v>
-      </c>
-      <c r="D99">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>1801229</v>
-      </c>
-      <c r="B100" t="s">
-        <v>112</v>
-      </c>
-      <c r="C100" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>1801230</v>
-      </c>
-      <c r="B101" t="s">
-        <v>113</v>
-      </c>
-      <c r="C101" t="s">
-        <v>258</v>
-      </c>
-      <c r="D101">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>1801735</v>
-      </c>
-      <c r="B102" t="s">
-        <v>114</v>
-      </c>
-      <c r="C102" t="s">
-        <v>258</v>
-      </c>
-      <c r="D102">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>1802162</v>
-      </c>
-      <c r="B103" t="s">
-        <v>115</v>
-      </c>
-      <c r="C103" t="s">
-        <v>258</v>
-      </c>
-      <c r="D103">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>1802164</v>
-      </c>
-      <c r="B104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" t="s">
-        <v>258</v>
-      </c>
-      <c r="D104">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>1802165</v>
-      </c>
-      <c r="B105" t="s">
-        <v>128</v>
-      </c>
-      <c r="C105" t="s">
-        <v>258</v>
-      </c>
-      <c r="D105">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>1802166</v>
-      </c>
-      <c r="B106" t="s">
-        <v>137</v>
-      </c>
-      <c r="C106" t="s">
-        <v>258</v>
-      </c>
-      <c r="D106">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>1802167</v>
-      </c>
-      <c r="B107" t="s">
-        <v>117</v>
-      </c>
-      <c r="C107" t="s">
-        <v>258</v>
-      </c>
-      <c r="D107">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>1802169</v>
-      </c>
-      <c r="B108" t="s">
-        <v>119</v>
-      </c>
-      <c r="C108" t="s">
-        <v>258</v>
-      </c>
-      <c r="D108">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>1802170</v>
-      </c>
-      <c r="B109" t="s">
-        <v>120</v>
-      </c>
-      <c r="C109" t="s">
-        <v>258</v>
-      </c>
-      <c r="D109">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>1802171</v>
-      </c>
-      <c r="B110" t="s">
-        <v>102</v>
-      </c>
-      <c r="C110" t="s">
-        <v>258</v>
-      </c>
-      <c r="D110">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>1802172</v>
-      </c>
-      <c r="B111" t="s">
-        <v>103</v>
-      </c>
-      <c r="C111" t="s">
-        <v>258</v>
-      </c>
-      <c r="D111">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>1802173</v>
-      </c>
-      <c r="B112" t="s">
-        <v>124</v>
-      </c>
-      <c r="C112" t="s">
-        <v>258</v>
-      </c>
-      <c r="D112">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>1802174</v>
-      </c>
-      <c r="B113" t="s">
-        <v>125</v>
-      </c>
-      <c r="C113" t="s">
-        <v>258</v>
-      </c>
-      <c r="D113">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>1802175</v>
-      </c>
-      <c r="B114" t="s">
-        <v>126</v>
-      </c>
-      <c r="C114" t="s">
-        <v>258</v>
-      </c>
-      <c r="D114">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>1802176</v>
-      </c>
-      <c r="B115" t="s">
-        <v>129</v>
-      </c>
-      <c r="C115" t="s">
-        <v>258</v>
-      </c>
-      <c r="D115">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>1802177</v>
-      </c>
-      <c r="B116" t="s">
-        <v>282</v>
-      </c>
-      <c r="C116" t="s">
-        <v>258</v>
-      </c>
-      <c r="D116">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>1802517</v>
-      </c>
-      <c r="B117" t="s">
-        <v>104</v>
-      </c>
-      <c r="C117" t="s">
-        <v>258</v>
-      </c>
-      <c r="D117">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>1802659</v>
-      </c>
-      <c r="B118" t="s">
-        <v>198</v>
-      </c>
-      <c r="C118" t="s">
-        <v>258</v>
-      </c>
-      <c r="D118">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>1803044</v>
-      </c>
-      <c r="B119" t="s">
-        <v>248</v>
-      </c>
-      <c r="C119" t="s">
-        <v>277</v>
-      </c>
-      <c r="D119">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>1803045</v>
-      </c>
-      <c r="B120" t="s">
-        <v>249</v>
-      </c>
-      <c r="C120" t="s">
-        <v>277</v>
-      </c>
-      <c r="D120">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>1805340</v>
-      </c>
-      <c r="B121" t="s">
-        <v>199</v>
-      </c>
-      <c r="C121" t="s">
-        <v>258</v>
-      </c>
-      <c r="D121">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>1808003</v>
-      </c>
-      <c r="B122" t="s">
-        <v>105</v>
-      </c>
-      <c r="C122" t="s">
-        <v>258</v>
-      </c>
-      <c r="D122">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>1808006</v>
-      </c>
-      <c r="B123" t="s">
-        <v>106</v>
-      </c>
-      <c r="C123" t="s">
-        <v>258</v>
-      </c>
-      <c r="D123">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>1808083</v>
-      </c>
-      <c r="B124" t="s">
-        <v>283</v>
-      </c>
-      <c r="C124" t="s">
-        <v>258</v>
-      </c>
-      <c r="D124">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>1808144</v>
-      </c>
-      <c r="B125" t="s">
-        <v>141</v>
-      </c>
-      <c r="C125" t="s">
-        <v>258</v>
-      </c>
-      <c r="D125">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>1808145</v>
-      </c>
-      <c r="B126" t="s">
-        <v>142</v>
-      </c>
-      <c r="C126" t="s">
-        <v>258</v>
-      </c>
-      <c r="D126">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>1808146</v>
-      </c>
-      <c r="B127" t="s">
-        <v>107</v>
-      </c>
-      <c r="C127" t="s">
-        <v>258</v>
-      </c>
-      <c r="D127">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>1808147</v>
-      </c>
-      <c r="B128" t="s">
-        <v>143</v>
-      </c>
-      <c r="C128" t="s">
-        <v>258</v>
-      </c>
-      <c r="D128">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>1808148</v>
-      </c>
-      <c r="B129" t="s">
-        <v>144</v>
-      </c>
-      <c r="C129" t="s">
-        <v>258</v>
-      </c>
-      <c r="D129">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>1808156</v>
-      </c>
-      <c r="B130" t="s">
-        <v>108</v>
-      </c>
-      <c r="C130" t="s">
-        <v>258</v>
-      </c>
-      <c r="D130">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>1901008</v>
-      </c>
-      <c r="B131" t="s">
-        <v>69</v>
-      </c>
-      <c r="C131" t="s">
-        <v>284</v>
-      </c>
-      <c r="D131">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>1901038</v>
-      </c>
-      <c r="B132" t="s">
-        <v>175</v>
-      </c>
-      <c r="C132" t="s">
-        <v>284</v>
-      </c>
-      <c r="D132">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>1901086</v>
-      </c>
-      <c r="B133" t="s">
-        <v>70</v>
-      </c>
-      <c r="C133" t="s">
-        <v>284</v>
-      </c>
-      <c r="D133">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>1901466</v>
-      </c>
-      <c r="B134" t="s">
-        <v>176</v>
-      </c>
-      <c r="C134" t="s">
-        <v>284</v>
-      </c>
-      <c r="D134">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>1901505</v>
-      </c>
-      <c r="B135" t="s">
-        <v>71</v>
-      </c>
-      <c r="C135" t="s">
-        <v>279</v>
-      </c>
-      <c r="D135">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>1902003</v>
-      </c>
-      <c r="B136" t="s">
-        <v>72</v>
-      </c>
-      <c r="C136" t="s">
-        <v>272</v>
-      </c>
-      <c r="D136">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>1902013</v>
-      </c>
-      <c r="B137" t="s">
-        <v>20</v>
-      </c>
-      <c r="C137" t="s">
-        <v>272</v>
-      </c>
-      <c r="D137">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>1902014</v>
-      </c>
-      <c r="B138" t="s">
-        <v>73</v>
-      </c>
-      <c r="C138" t="s">
-        <v>263</v>
-      </c>
-      <c r="D138">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>2302017</v>
-      </c>
-      <c r="B139" t="s">
-        <v>158</v>
-      </c>
-      <c r="C139" t="s">
-        <v>268</v>
-      </c>
-      <c r="D139">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>2302024</v>
-      </c>
-      <c r="B140" t="s">
-        <v>52</v>
-      </c>
-      <c r="C140" t="s">
-        <v>270</v>
-      </c>
-      <c r="D140">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>2302044</v>
-      </c>
-      <c r="B141" t="s">
-        <v>53</v>
-      </c>
-      <c r="C141" t="s">
-        <v>285</v>
-      </c>
-      <c r="D141">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>2302045</v>
-      </c>
-      <c r="B142" t="s">
-        <v>54</v>
-      </c>
-      <c r="C142" t="s">
-        <v>268</v>
-      </c>
-      <c r="D142">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>2302098</v>
-      </c>
-      <c r="B143" t="s">
-        <v>74</v>
-      </c>
-      <c r="C143" t="s">
-        <v>268</v>
-      </c>
-      <c r="D143">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>2302118</v>
-      </c>
-      <c r="B144" t="s">
-        <v>55</v>
-      </c>
-      <c r="C144" t="s">
-        <v>258</v>
-      </c>
-      <c r="D144">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>2302119</v>
-      </c>
-      <c r="B145" t="s">
-        <v>177</v>
-      </c>
-      <c r="C145" t="s">
-        <v>258</v>
-      </c>
-      <c r="D145">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>2304002</v>
-      </c>
-      <c r="B146" t="s">
-        <v>96</v>
-      </c>
-      <c r="C146" t="s">
-        <v>258</v>
-      </c>
-      <c r="D146">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>2304003</v>
-      </c>
-      <c r="B147" t="s">
-        <v>138</v>
-      </c>
-      <c r="C147" t="s">
-        <v>258</v>
-      </c>
-      <c r="D147">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>2304008</v>
-      </c>
-      <c r="B148" t="s">
-        <v>195</v>
-      </c>
-      <c r="C148" t="s">
-        <v>258</v>
-      </c>
-      <c r="D148">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>2304053</v>
-      </c>
-      <c r="B149" t="s">
-        <v>190</v>
-      </c>
-      <c r="C149" t="s">
-        <v>258</v>
-      </c>
-      <c r="D149">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>2304056</v>
-      </c>
-      <c r="B150" t="s">
-        <v>56</v>
-      </c>
-      <c r="C150" t="s">
-        <v>258</v>
-      </c>
-      <c r="D150">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151">
-        <v>2505058</v>
-      </c>
-      <c r="B151" t="s">
-        <v>200</v>
-      </c>
-      <c r="C151" t="s">
-        <v>258</v>
-      </c>
-      <c r="D151">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152">
-        <v>2505426</v>
-      </c>
-      <c r="B152" t="s">
-        <v>130</v>
-      </c>
-      <c r="C152" t="s">
-        <v>258</v>
-      </c>
       <c r="D152">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="E152">
+        <v>0.78749999999999998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>2508169</v>
+        <v>2508993</v>
       </c>
       <c r="B153" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="C153" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D153">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.05</v>
+      </c>
+      <c r="E153">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>2508985</v>
+        <v>2508994</v>
       </c>
       <c r="B154" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C154" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="D154">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E154">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>2508986</v>
+        <v>4212234</v>
       </c>
       <c r="B155" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="C155" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="D155">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E155">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>2508987</v>
+        <v>4212254</v>
       </c>
       <c r="B156" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="C156" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="D156">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E156">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>2508988</v>
+        <v>5309018</v>
       </c>
       <c r="B157" t="s">
-        <v>245</v>
+        <v>38</v>
       </c>
       <c r="C157" t="s">
         <v>277</v>
       </c>
       <c r="D157">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34.65</v>
+      </c>
+      <c r="E157">
+        <v>34.65</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>2508990</v>
+        <v>5314002</v>
       </c>
       <c r="B158" t="s">
-        <v>232</v>
+        <v>155</v>
       </c>
       <c r="C158" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D158">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>2508991</v>
+        <v>5316483</v>
       </c>
       <c r="B159" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="C159" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D159">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E159">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>2508992</v>
+        <v>5316484</v>
       </c>
       <c r="B160" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="C160" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="D160">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E160">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>2508993</v>
+        <v>5316507</v>
       </c>
       <c r="B161" t="s">
-        <v>235</v>
+        <v>133</v>
       </c>
       <c r="C161" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="D161">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E161">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>2508994</v>
+        <v>5316508</v>
       </c>
       <c r="B162" t="s">
-        <v>236</v>
+        <v>134</v>
       </c>
       <c r="C162" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D162">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="E162">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>4212234</v>
+        <v>5316509</v>
       </c>
       <c r="B163" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="C163" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D163">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>4212254</v>
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="E163">
+        <v>0.26250000000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>75</v>
       </c>
       <c r="B164" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C164" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D164">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>5309018</v>
+        <v>6.3</v>
+      </c>
+      <c r="E164">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>77</v>
       </c>
       <c r="B165" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C165" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="D165">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>5314002</v>
+        <v>0.68843750000000004</v>
+      </c>
+      <c r="E165">
+        <v>0.68843750000000004</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>21</v>
       </c>
       <c r="B166" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="C166" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D166">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>5316483</v>
+        <v>1.0625000000000001E-2</v>
+      </c>
+      <c r="E166">
+        <v>8.3750000000000005E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>79</v>
       </c>
       <c r="B167" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="C167" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D167">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168">
-        <v>5316484</v>
+        <v>5.46875E-2</v>
+      </c>
+      <c r="E167">
+        <v>5.46875E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>23</v>
       </c>
       <c r="B168" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="C168" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D168">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>5316507</v>
+        <v>3.4540625</v>
+      </c>
+      <c r="E168">
+        <v>3.4540625</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>57</v>
       </c>
       <c r="B169" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="C169" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="D169">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>5316508</v>
+        <v>7.6124999999999998</v>
+      </c>
+      <c r="E169">
+        <v>7.6124999999999998</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>59</v>
       </c>
       <c r="B170" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="C170" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="D170">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171">
-        <v>5316509</v>
+        <v>0.315</v>
+      </c>
+      <c r="E170">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>240</v>
       </c>
       <c r="B171" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C171" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D171">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3.15</v>
+      </c>
+      <c r="E171">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>75</v>
-      </c>
-      <c r="B172" t="s">
-        <v>76</v>
+        <v>61</v>
+      </c>
+      <c r="B172" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C172" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D172">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9.0624999999999994E-3</v>
+      </c>
+      <c r="E172">
+        <v>9.0624999999999994E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>77</v>
-      </c>
-      <c r="B173" t="s">
-        <v>78</v>
+        <v>220</v>
+      </c>
+      <c r="B173" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C173" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D173">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.575</v>
+      </c>
+      <c r="E173">
+        <v>1.575</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>21</v>
-      </c>
-      <c r="B174" t="s">
-        <v>22</v>
+        <v>222</v>
+      </c>
+      <c r="B174" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C174" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D174">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E174">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>79</v>
-      </c>
-      <c r="B175" t="s">
-        <v>80</v>
+        <v>224</v>
+      </c>
+      <c r="B175" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C175" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D175">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>23</v>
-      </c>
-      <c r="B176" t="s">
-        <v>24</v>
-      </c>
-      <c r="C176" t="s">
-        <v>266</v>
-      </c>
-      <c r="D176">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>288</v>
-      </c>
-      <c r="B177" t="s">
-        <v>289</v>
-      </c>
-      <c r="C177" t="s">
-        <v>272</v>
-      </c>
-      <c r="D177">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>57</v>
-      </c>
-      <c r="B178" t="s">
-        <v>58</v>
-      </c>
-      <c r="C178" t="s">
-        <v>284</v>
-      </c>
-      <c r="D178">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>59</v>
-      </c>
-      <c r="B179" t="s">
-        <v>60</v>
-      </c>
-      <c r="C179" t="s">
-        <v>273</v>
-      </c>
-      <c r="D179">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>240</v>
-      </c>
-      <c r="B180" t="s">
-        <v>241</v>
-      </c>
-      <c r="C180" t="s">
-        <v>258</v>
-      </c>
-      <c r="D180">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>61</v>
-      </c>
-      <c r="B181" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C181" t="s">
-        <v>272</v>
-      </c>
-      <c r="D181">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>290</v>
-      </c>
-      <c r="B182" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C182" t="s">
-        <v>270</v>
-      </c>
-      <c r="D182">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>220</v>
-      </c>
-      <c r="B183" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C183" t="s">
-        <v>258</v>
-      </c>
-      <c r="D183">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>222</v>
-      </c>
-      <c r="B184" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C184" t="s">
-        <v>258</v>
-      </c>
-      <c r="D184">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>224</v>
-      </c>
-      <c r="B185" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C185" t="s">
-        <v>258</v>
-      </c>
-      <c r="D185">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>206</v>
-      </c>
-      <c r="B186" t="s">
-        <v>207</v>
-      </c>
-      <c r="C186" t="s">
-        <v>263</v>
-      </c>
-      <c r="D186">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="193" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="194" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="195" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="196" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="197" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="198" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="199" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="200" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="201" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="202" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="203" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="204" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="205" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="206" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="207" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="208" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="209" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="210" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="211" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="212" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="213" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="214" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="215" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="216" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="217" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="218" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="219" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="220" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="221" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="222" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="223" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="224" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="225" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="226" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="227" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="228" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="229" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="230" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="231" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="232" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="233" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="234" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="235" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="236" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="237" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="238" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="239" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="240" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="241" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="242" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="243" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="244" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="245" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="246" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="247" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="248" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="249" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="250" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="251" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="252" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="253" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="254" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="255" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="256" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="257" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="258" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="259" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="260" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="261" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="262" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="263" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="264" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="265" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="266" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="267" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="268" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="269" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="270" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="271" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="272" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="273" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="274" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="275" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="276" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="277" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="278" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="279" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="280" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="281" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="282" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="283" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="284" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="285" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="286" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="287" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="288" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="289" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="290" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="291" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="292" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="293" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="294" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="295" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="296" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="297" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="298" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="299" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="300" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="301" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="302" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="303" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="304" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="305" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="306" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="307" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="308" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="309" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="310" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="311" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="312" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="313" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="314" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="315" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="316" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="317" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="318" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="319" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="320" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="321" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="322" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="323" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="324" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="325" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="326" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="327" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="328" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="329" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="330" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="331" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="332" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="333" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="334" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="335" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="336" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="337" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="338" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="339" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="340" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="341" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="342" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="343" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="344" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="345" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="346" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="347" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="348" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="349" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="350" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="351" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="352" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="353" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="354" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="355" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="356" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="357" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="358" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="359" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="360" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="361" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="362" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="363" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="364" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="365" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="366" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="367" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="368" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="369" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="370" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="371" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="372" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="373" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="374" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="375" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="376" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="377" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="378" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="379" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="380" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="381" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="382" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="383" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="384" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="385" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="386" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="387" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="388" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="389" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="390" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="391" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="392" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="393" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="394" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="395" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="396" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="397" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="398" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="399" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="400" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="401" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="402" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="403" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="404" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="405" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="406" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="407" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="408" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="409" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="410" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="411" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="412" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="413" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="414" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="415" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="416" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="417" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="418" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="419" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="420" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="421" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="422" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="423" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="424" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="425" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="426" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="427" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="428" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="429" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="430" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="431" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="432" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="433" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="434" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="435" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="436" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="437" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="438" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="439" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="440" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="441" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="442" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="443" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="444" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="445" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="446" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="447" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="448" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="449" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="450" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="451" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="452" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="453" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="454" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="455" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="456" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="457" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="458" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="459" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="460" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="461" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="462" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="463" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="464" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="465" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="466" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="467" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="468" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="469" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="470" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="471" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="472" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="473" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="474" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="475" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="476" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="477" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="478" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="479" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="480" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="481" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="482" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="483" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="484" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="485" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="486" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="487" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="488" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="489" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="490" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="491" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="492" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="493" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="494" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="495" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="496" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="497" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="498" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="499" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="500" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="501" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="502" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="503" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="504" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="505" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="506" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="507" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="508" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="509" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="510" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="511" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="512" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="513" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="514" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="515" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="516" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="517" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="518" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="519" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="520" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="521" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="522" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="523" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="524" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="525" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="526" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="527" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="528" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="529" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="530" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="531" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="532" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="533" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="534" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="535" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="536" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="537" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="538" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="539" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="540" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="541" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="542" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="543" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="544" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="545" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="546" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="547" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="548" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="549" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="550" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="551" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="552" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="553" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="554" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="555" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="556" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="557" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="558" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="559" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="560" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="561" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="562" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="563" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="564" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="565" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="566" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="567" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="568" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="569" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="570" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="571" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="572" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="573" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="574" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="575" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="576" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="577" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="578" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="579" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="580" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="581" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="582" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="583" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="584" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="585" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="586" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="587" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="588" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="589" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="590" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="591" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="592" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="593" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="594" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="595" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="596" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="597" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="598" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="599" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="600" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="601" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="602" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="603" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="604" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="605" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="606" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="607" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="608" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="609" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="610" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="611" customFormat="1" x14ac:dyDescent="0.25"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E175">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
